--- a/repair/back/doc/estimate/program-periodic2.xlsx
+++ b/repair/back/doc/estimate/program-periodic2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seongjaehyeon/anb_origin2/repair/back/doc/estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8585B251-3A53-904B-A186-D37576750C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA89693D-89A4-A54C-B285-D626572855D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="18300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="19800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="1" r:id="rId1"/>
@@ -378,7 +378,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="196">
   <si>
     <t xml:space="preserve">㈜ 에 이 앤 비 </t>
   </si>
@@ -653,9 +653,6 @@
     <t>보고서 납품</t>
   </si>
   <si>
-    <t xml:space="preserve">시설물통합정보시스템(FMS)등록 후 정기안전점검 보고서 1부 </t>
-  </si>
-  <si>
     <t>기 타 사 항</t>
   </si>
   <si>
@@ -834,18 +831,6 @@
       </rPr>
       <t>붙임 1&gt;</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">① 시설물명 : </t>
-  </si>
-  <si>
-    <t xml:space="preserve">② 위      치 : </t>
-  </si>
-  <si>
-    <t xml:space="preserve">③ 용      도 : </t>
-  </si>
-  <si>
-    <t>공동주택</t>
   </si>
   <si>
     <t>③ 제3조 제2항에 따라 정기안전점검 업무의 일부 또는 전부의 변경이 불가피한 경우 "발주자"와 "수주자"는 협의하여 변경할 수 있다.</t>
@@ -1013,45 +998,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제공자"는 프로그램을 얻은 정보 또는 성과품 및 자료를 계약이행의 전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후를 막론하고 "시용자"의 사전승인 없이 외부에 누설할 수 없다.</t>
-    </r>
-  </si>
-  <si>
     <t>② 이 계약에 명시되지 아니한 사항은 기획재정부가 회계예규로 정한 기술용역계약 일반조건과 관계법령에 의한다.</t>
-  </si>
-  <si>
-    <t>상반기:</t>
   </si>
   <si>
     <t>※총액(연2회)</t>
@@ -1066,25 +1013,13 @@
     <t>(VAT별도)</t>
   </si>
   <si>
-    <t>하반기:</t>
-  </si>
-  <si>
     <t xml:space="preserve">상기 금액은 </t>
-  </si>
-  <si>
-    <t>점검 프로그램 사용 견적건</t>
   </si>
   <si>
     <t>점검프로그램 사용계약서</t>
   </si>
   <si>
-    <t>점검프로그램 사용 대가임</t>
-  </si>
-  <si>
     <t>총 사용료</t>
-  </si>
-  <si>
-    <t xml:space="preserve">④ 점검 대상시설물의 범위 : </t>
   </si>
   <si>
     <t>외업인건비의 0%</t>
@@ -1100,9 +1035,6 @@
   </si>
   <si>
     <t>※ 첨    부 :  1. 점검 프로그램 사용 견적서 1부 끝.</t>
-  </si>
-  <si>
-    <t>점검프로그램 사용</t>
   </si>
   <si>
     <t>점검 프로그램 사용 대가 내역(1회 적용금액)</t>
@@ -1130,9 +1062,6 @@
   </si>
   <si>
     <t>총  사  용  료</t>
-  </si>
-  <si>
-    <t>입주자대표회의(이하 "사용자"라 한다) 와</t>
   </si>
   <si>
     <t>본 계약의 유효기간 만료 3개월 전까지 당사자 쌍방 간에 계약의 종료 또는 조건변경에 관한 서면 의사표시가 없는 경우, 본 계약은 종전과 동일한 조건으로 자동 연장된 것으로 본다.</t>
@@ -1176,36 +1105,6 @@
   </si>
   <si>
     <t>나. 점검프로그램 사용 기간 - 2026년 연간(2회)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">점검프로그램 제공자인 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>㈜에이앤비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(이하 "제공자"라 한다)는 다음과 같이 계약을 체결한다.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">사용자 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1270,10 +1169,6 @@
     <t>제11조(기타사항)</t>
   </si>
   <si>
-    <t xml:space="preserve">         6. 용    역    비    :</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>●   주 소 : 경기도 용인시 기흥구 마북로 159 한성프라자 207호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1291,10 +1186,6 @@
   </si>
   <si>
     <t xml:space="preserve">           4. 시설물 개요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">           5. 용  역   범  위   : </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1389,6 +1280,60 @@
   </si>
   <si>
     <t>가. 내업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상반기 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하반기 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">           5. 용  역   범  위  : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">         6. 용   역   비  :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">시설물통합정보시스템(FMS)등록 후 e-보고서 1부 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>③ 용      도 : 공동주택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"제공자"는 프로그램을 얻은 정보 또는 성과품 및 자료를 계약이행의 전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후를 막론하고 "사용자"의 사전승인 없이 외부에 누설할 수 없다.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제공자인 ㈜에이앤비(이하 "제공자"라 한다)는 다음과 같이 계약을 체결한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1468,7 +1413,7 @@
     <numFmt numFmtId="243" formatCode="_-&quot;₩&quot;* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0.00_-;_-&quot;₩&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="244" formatCode="&quot;₩&quot;#,##0.00;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-#,##0.00"/>
   </numFmts>
-  <fonts count="116">
+  <fonts count="114">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2102,14 +2047,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="11.5"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
@@ -2226,14 +2163,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="돋움"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="바탕체"/>
@@ -3279,7 +3208,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
@@ -11679,7 +11608,7 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="102" fillId="0" borderId="55">
+    <xf numFmtId="182" fontId="101" fillId="0" borderId="55">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="230" fontId="75" fillId="0" borderId="0">
@@ -11706,7 +11635,7 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="102" fillId="0" borderId="1" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="3" fontId="101" fillId="0" borderId="1" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
@@ -12633,7 +12562,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" applyFill="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
@@ -12660,14 +12589,14 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="326">
+  <cellXfs count="319">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -12958,13 +12887,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyAlignment="1">
@@ -13018,42 +12947,36 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="104" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -13061,18 +12984,422 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="73" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="73" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="73" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="71" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="74" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="71" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="11" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="11" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="102" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="108" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -13203,440 +13530,23 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="16" fillId="5" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="180" fontId="16" fillId="5" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="109" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="115" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="115" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="67" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="68" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="73" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="71" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="74" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="11" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="11" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="103" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="71" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3116">
@@ -17284,36 +17194,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="6:34" s="2" customFormat="1" ht="42" customHeight="1">
-      <c r="F1" s="212" t="s">
+      <c r="F1" s="267" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="212"/>
-      <c r="O1" s="212"/>
-      <c r="P1" s="212"/>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="212"/>
-      <c r="Y1" s="212"/>
-      <c r="Z1" s="212"/>
-      <c r="AA1" s="212"/>
-      <c r="AB1" s="212"/>
-      <c r="AC1" s="212"/>
-      <c r="AD1" s="212"/>
-      <c r="AE1" s="212"/>
-      <c r="AF1" s="212"/>
-      <c r="AG1" s="212"/>
+      <c r="G1" s="267"/>
+      <c r="H1" s="267"/>
+      <c r="I1" s="267"/>
+      <c r="J1" s="267"/>
+      <c r="K1" s="267"/>
+      <c r="L1" s="267"/>
+      <c r="M1" s="267"/>
+      <c r="N1" s="267"/>
+      <c r="O1" s="267"/>
+      <c r="P1" s="267"/>
+      <c r="Q1" s="267"/>
+      <c r="R1" s="267"/>
+      <c r="S1" s="267"/>
+      <c r="T1" s="267"/>
+      <c r="U1" s="267"/>
+      <c r="V1" s="267"/>
+      <c r="W1" s="267"/>
+      <c r="X1" s="267"/>
+      <c r="Y1" s="267"/>
+      <c r="Z1" s="267"/>
+      <c r="AA1" s="267"/>
+      <c r="AB1" s="267"/>
+      <c r="AC1" s="267"/>
+      <c r="AD1" s="267"/>
+      <c r="AE1" s="267"/>
+      <c r="AF1" s="267"/>
+      <c r="AG1" s="267"/>
       <c r="AH1" s="1"/>
     </row>
     <row r="2" spans="6:34" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17348,36 +17258,36 @@
       <c r="AH2" s="1"/>
     </row>
     <row r="3" spans="6:34" s="2" customFormat="1" ht="18" customHeight="1">
-      <c r="F3" s="213" t="s">
-        <v>136</v>
-      </c>
-      <c r="G3" s="213"/>
-      <c r="H3" s="213"/>
-      <c r="I3" s="213"/>
-      <c r="J3" s="213"/>
-      <c r="K3" s="213"/>
-      <c r="L3" s="213"/>
-      <c r="M3" s="213"/>
-      <c r="N3" s="213"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="213"/>
-      <c r="Q3" s="213"/>
-      <c r="R3" s="213"/>
-      <c r="S3" s="213"/>
-      <c r="T3" s="213"/>
-      <c r="U3" s="213"/>
-      <c r="V3" s="213"/>
-      <c r="W3" s="213"/>
-      <c r="X3" s="213"/>
-      <c r="Y3" s="213"/>
-      <c r="Z3" s="213"/>
-      <c r="AA3" s="213"/>
-      <c r="AB3" s="213"/>
-      <c r="AC3" s="213"/>
-      <c r="AD3" s="213"/>
-      <c r="AE3" s="213"/>
-      <c r="AF3" s="213"/>
-      <c r="AG3" s="213"/>
+      <c r="F3" s="268" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="268"/>
+      <c r="H3" s="268"/>
+      <c r="I3" s="268"/>
+      <c r="J3" s="268"/>
+      <c r="K3" s="268"/>
+      <c r="L3" s="268"/>
+      <c r="M3" s="268"/>
+      <c r="N3" s="268"/>
+      <c r="O3" s="268"/>
+      <c r="P3" s="268"/>
+      <c r="Q3" s="268"/>
+      <c r="R3" s="268"/>
+      <c r="S3" s="268"/>
+      <c r="T3" s="268"/>
+      <c r="U3" s="268"/>
+      <c r="V3" s="268"/>
+      <c r="W3" s="268"/>
+      <c r="X3" s="268"/>
+      <c r="Y3" s="268"/>
+      <c r="Z3" s="268"/>
+      <c r="AA3" s="268"/>
+      <c r="AB3" s="268"/>
+      <c r="AC3" s="268"/>
+      <c r="AD3" s="268"/>
+      <c r="AE3" s="268"/>
+      <c r="AF3" s="268"/>
+      <c r="AG3" s="268"/>
       <c r="AH3" s="1"/>
     </row>
     <row r="4" spans="6:34" s="2" customFormat="1" ht="7.5" customHeight="1">
@@ -17443,180 +17353,178 @@
       <c r="AH5" s="1"/>
     </row>
     <row r="6" spans="6:34" s="2" customFormat="1" ht="22" customHeight="1">
-      <c r="F6" s="211" t="s">
+      <c r="F6" s="266" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="211"/>
-      <c r="H6" s="211"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="199" t="s">
+      <c r="G6" s="266"/>
+      <c r="H6" s="266"/>
+      <c r="I6" s="266"/>
+      <c r="J6" s="258" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="199"/>
-      <c r="L6" s="199"/>
-      <c r="M6" s="199"/>
-      <c r="N6" s="199"/>
-      <c r="O6" s="199"/>
-      <c r="P6" s="199"/>
-      <c r="Q6" s="199"/>
-      <c r="R6" s="199"/>
-      <c r="S6" s="199"/>
-      <c r="T6" s="199"/>
-      <c r="U6" s="199"/>
-      <c r="V6" s="122"/>
-      <c r="W6" s="122"/>
-      <c r="X6" s="122"/>
-      <c r="Y6" s="122"/>
-      <c r="Z6" s="122"/>
-      <c r="AA6" s="122"/>
-      <c r="AB6" s="122"/>
-      <c r="AC6" s="122"/>
-      <c r="AD6" s="122"/>
-      <c r="AE6" s="122"/>
+      <c r="K6" s="258"/>
+      <c r="L6" s="258"/>
+      <c r="M6" s="258"/>
+      <c r="N6" s="258"/>
+      <c r="O6" s="258"/>
+      <c r="P6" s="258"/>
+      <c r="Q6" s="258"/>
+      <c r="R6" s="258"/>
+      <c r="S6" s="258"/>
+      <c r="T6" s="258"/>
+      <c r="U6" s="258"/>
+      <c r="V6" s="121"/>
+      <c r="W6" s="121"/>
+      <c r="X6" s="121"/>
+      <c r="Y6" s="121"/>
+      <c r="Z6" s="121"/>
+      <c r="AA6" s="121"/>
+      <c r="AB6" s="121"/>
+      <c r="AC6" s="121"/>
+      <c r="AD6" s="121"/>
+      <c r="AE6" s="121"/>
       <c r="AF6" s="117"/>
       <c r="AG6" s="117"/>
       <c r="AH6" s="1"/>
     </row>
     <row r="7" spans="6:34" s="2" customFormat="1" ht="22" customHeight="1">
-      <c r="F7" s="211" t="s">
+      <c r="F7" s="266" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="211"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="214" t="s">
+      <c r="G7" s="266"/>
+      <c r="H7" s="266"/>
+      <c r="I7" s="266"/>
+      <c r="J7" s="269" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="214"/>
-      <c r="L7" s="214"/>
-      <c r="M7" s="214"/>
-      <c r="N7" s="214"/>
-      <c r="O7" s="214"/>
-      <c r="P7" s="214"/>
-      <c r="Q7" s="214"/>
-      <c r="R7" s="214"/>
-      <c r="S7" s="214"/>
-      <c r="T7" s="214"/>
-      <c r="U7" s="214"/>
-      <c r="V7" s="122"/>
-      <c r="W7" s="122"/>
-      <c r="X7" s="122"/>
-      <c r="Y7" s="122"/>
-      <c r="Z7" s="122"/>
-      <c r="AA7" s="122"/>
-      <c r="AB7" s="122"/>
-      <c r="AC7" s="122"/>
-      <c r="AD7" s="122"/>
-      <c r="AE7" s="122"/>
+      <c r="K7" s="269"/>
+      <c r="L7" s="269"/>
+      <c r="M7" s="269"/>
+      <c r="N7" s="269"/>
+      <c r="O7" s="269"/>
+      <c r="P7" s="269"/>
+      <c r="Q7" s="269"/>
+      <c r="R7" s="269"/>
+      <c r="S7" s="269"/>
+      <c r="T7" s="269"/>
+      <c r="U7" s="269"/>
+      <c r="V7" s="121"/>
+      <c r="W7" s="121"/>
+      <c r="X7" s="121"/>
+      <c r="Y7" s="121"/>
+      <c r="Z7" s="121"/>
+      <c r="AA7" s="121"/>
+      <c r="AB7" s="121"/>
+      <c r="AC7" s="121"/>
+      <c r="AD7" s="121"/>
+      <c r="AE7" s="121"/>
       <c r="AF7" s="117"/>
       <c r="AG7" s="117"/>
       <c r="AH7" s="1"/>
     </row>
     <row r="8" spans="6:34" s="2" customFormat="1" ht="22" customHeight="1">
-      <c r="F8" s="211" t="s">
+      <c r="F8" s="266" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="211"/>
-      <c r="H8" s="211"/>
-      <c r="I8" s="211"/>
-      <c r="J8" s="199" t="s">
-        <v>157</v>
-      </c>
-      <c r="K8" s="199"/>
-      <c r="L8" s="199"/>
-      <c r="M8" s="199"/>
-      <c r="N8" s="199"/>
-      <c r="O8" s="199"/>
-      <c r="P8" s="199"/>
-      <c r="Q8" s="199"/>
-      <c r="R8" s="199"/>
-      <c r="S8" s="199"/>
-      <c r="T8" s="199"/>
-      <c r="U8" s="199"/>
-      <c r="V8" s="199"/>
-      <c r="W8" s="199"/>
-      <c r="X8" s="199"/>
-      <c r="Y8" s="199"/>
-      <c r="Z8" s="199"/>
-      <c r="AA8" s="199"/>
-      <c r="AB8" s="199"/>
-      <c r="AC8" s="199"/>
-      <c r="AD8" s="199"/>
-      <c r="AE8" s="199"/>
+      <c r="G8" s="266"/>
+      <c r="H8" s="266"/>
+      <c r="I8" s="266"/>
+      <c r="J8" s="258" t="s">
+        <v>144</v>
+      </c>
+      <c r="K8" s="258"/>
+      <c r="L8" s="258"/>
+      <c r="M8" s="258"/>
+      <c r="N8" s="258"/>
+      <c r="O8" s="258"/>
+      <c r="P8" s="258"/>
+      <c r="Q8" s="258"/>
+      <c r="R8" s="258"/>
+      <c r="S8" s="258"/>
+      <c r="T8" s="258"/>
+      <c r="U8" s="258"/>
+      <c r="V8" s="258"/>
+      <c r="W8" s="258"/>
+      <c r="X8" s="258"/>
+      <c r="Y8" s="258"/>
+      <c r="Z8" s="258"/>
+      <c r="AA8" s="258"/>
+      <c r="AB8" s="258"/>
+      <c r="AC8" s="258"/>
+      <c r="AD8" s="258"/>
+      <c r="AE8" s="258"/>
       <c r="AF8" s="117"/>
       <c r="AG8" s="117"/>
       <c r="AH8" s="1"/>
     </row>
     <row r="9" spans="6:34" s="2" customFormat="1" ht="22" customHeight="1">
-      <c r="F9" s="211" t="s">
+      <c r="F9" s="266" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="211"/>
-      <c r="H9" s="211"/>
-      <c r="I9" s="211"/>
-      <c r="J9" s="122" t="s">
+      <c r="G9" s="266"/>
+      <c r="H9" s="266"/>
+      <c r="I9" s="266"/>
+      <c r="J9" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="122"/>
-      <c r="L9" s="122"/>
-      <c r="M9" s="122"/>
-      <c r="N9" s="122"/>
-      <c r="O9" s="122"/>
-      <c r="P9" s="122"/>
-      <c r="Q9" s="122"/>
-      <c r="R9" s="122"/>
-      <c r="S9" s="122"/>
-      <c r="T9" s="122"/>
-      <c r="U9" s="122"/>
-      <c r="V9" s="122"/>
-      <c r="W9" s="122"/>
-      <c r="X9" s="122"/>
-      <c r="Y9" s="122"/>
-      <c r="Z9" s="122"/>
-      <c r="AA9" s="122"/>
-      <c r="AB9" s="122"/>
-      <c r="AC9" s="122"/>
-      <c r="AD9" s="122"/>
-      <c r="AE9" s="122"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="121"/>
+      <c r="R9" s="121"/>
+      <c r="S9" s="121"/>
+      <c r="T9" s="121"/>
+      <c r="U9" s="121"/>
+      <c r="V9" s="121"/>
+      <c r="W9" s="121"/>
+      <c r="X9" s="121"/>
+      <c r="Y9" s="121"/>
+      <c r="Z9" s="121"/>
+      <c r="AA9" s="121"/>
+      <c r="AB9" s="121"/>
+      <c r="AC9" s="121"/>
+      <c r="AD9" s="121"/>
+      <c r="AE9" s="121"/>
       <c r="AF9" s="117"/>
       <c r="AG9" s="117"/>
       <c r="AH9" s="1"/>
     </row>
     <row r="10" spans="6:34" s="2" customFormat="1" ht="22" customHeight="1">
-      <c r="F10" s="211" t="s">
+      <c r="F10" s="266" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="211"/>
-      <c r="H10" s="211"/>
-      <c r="I10" s="211"/>
-      <c r="J10" s="199" t="s">
-        <v>137</v>
-      </c>
-      <c r="K10" s="199"/>
-      <c r="L10" s="199"/>
-      <c r="M10" s="199"/>
-      <c r="N10" s="199"/>
-      <c r="O10" s="122" t="s">
-        <v>129</v>
-      </c>
-      <c r="P10" s="122"/>
-      <c r="Q10" s="122"/>
-      <c r="R10" s="122"/>
-      <c r="S10" s="122"/>
-      <c r="T10" s="122"/>
-      <c r="U10" s="122"/>
-      <c r="V10" s="122"/>
-      <c r="W10" s="122"/>
-      <c r="X10" s="122"/>
-      <c r="Y10" s="122"/>
-      <c r="Z10" s="122"/>
-      <c r="AA10" s="122"/>
-      <c r="AB10" s="122"/>
-      <c r="AC10" s="122"/>
-      <c r="AD10" s="122"/>
-      <c r="AE10" s="122"/>
-      <c r="AF10" s="117"/>
-      <c r="AG10" s="117"/>
+      <c r="G10" s="266"/>
+      <c r="H10" s="266"/>
+      <c r="I10" s="266"/>
+      <c r="J10" s="258" t="s">
+        <v>126</v>
+      </c>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
+      <c r="M10" s="258"/>
+      <c r="N10" s="258"/>
+      <c r="O10" s="258"/>
+      <c r="P10" s="258"/>
+      <c r="Q10" s="258"/>
+      <c r="R10" s="258"/>
+      <c r="S10" s="258"/>
+      <c r="T10" s="258"/>
+      <c r="U10" s="258"/>
+      <c r="V10" s="258"/>
+      <c r="W10" s="258"/>
+      <c r="X10" s="258"/>
+      <c r="Y10" s="258"/>
+      <c r="Z10" s="258"/>
+      <c r="AA10" s="258"/>
+      <c r="AB10" s="258"/>
+      <c r="AC10" s="258"/>
+      <c r="AD10" s="258"/>
+      <c r="AE10" s="258"/>
+      <c r="AF10" s="258"/>
+      <c r="AG10" s="258"/>
       <c r="AH10" s="1"/>
     </row>
     <row r="11" spans="6:34" s="2" customFormat="1" ht="7.5" customHeight="1">
@@ -17682,36 +17590,36 @@
       <c r="AH12" s="1"/>
     </row>
     <row r="13" spans="6:34" s="2" customFormat="1" ht="19.5" customHeight="1">
-      <c r="F13" s="188" t="s">
-        <v>182</v>
-      </c>
-      <c r="G13" s="188"/>
-      <c r="H13" s="188"/>
-      <c r="I13" s="188"/>
-      <c r="J13" s="188"/>
-      <c r="K13" s="188"/>
-      <c r="L13" s="188"/>
-      <c r="M13" s="188"/>
-      <c r="N13" s="188"/>
-      <c r="O13" s="188"/>
-      <c r="P13" s="188"/>
-      <c r="Q13" s="188"/>
-      <c r="R13" s="188"/>
-      <c r="S13" s="188"/>
-      <c r="T13" s="188"/>
-      <c r="U13" s="188"/>
-      <c r="V13" s="188"/>
-      <c r="W13" s="188"/>
-      <c r="X13" s="188"/>
-      <c r="Y13" s="188"/>
-      <c r="Z13" s="188"/>
-      <c r="AA13" s="188"/>
-      <c r="AB13" s="188"/>
-      <c r="AC13" s="188"/>
-      <c r="AD13" s="188"/>
-      <c r="AE13" s="188"/>
-      <c r="AF13" s="188"/>
-      <c r="AG13" s="188"/>
+      <c r="F13" s="244" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" s="244"/>
+      <c r="H13" s="244"/>
+      <c r="I13" s="244"/>
+      <c r="J13" s="244"/>
+      <c r="K13" s="244"/>
+      <c r="L13" s="244"/>
+      <c r="M13" s="244"/>
+      <c r="N13" s="244"/>
+      <c r="O13" s="244"/>
+      <c r="P13" s="244"/>
+      <c r="Q13" s="244"/>
+      <c r="R13" s="244"/>
+      <c r="S13" s="244"/>
+      <c r="T13" s="244"/>
+      <c r="U13" s="244"/>
+      <c r="V13" s="244"/>
+      <c r="W13" s="244"/>
+      <c r="X13" s="244"/>
+      <c r="Y13" s="244"/>
+      <c r="Z13" s="244"/>
+      <c r="AA13" s="244"/>
+      <c r="AB13" s="244"/>
+      <c r="AC13" s="244"/>
+      <c r="AD13" s="244"/>
+      <c r="AE13" s="244"/>
+      <c r="AF13" s="244"/>
+      <c r="AG13" s="244"/>
       <c r="AH13" s="1"/>
     </row>
     <row r="14" spans="6:34" s="2" customFormat="1" ht="9.75" customHeight="1">
@@ -17746,36 +17654,36 @@
       <c r="AH14" s="1"/>
     </row>
     <row r="15" spans="6:34" s="2" customFormat="1" ht="59.25" customHeight="1">
-      <c r="F15" s="208" t="s">
-        <v>183</v>
-      </c>
-      <c r="G15" s="208"/>
-      <c r="H15" s="208"/>
-      <c r="I15" s="208"/>
-      <c r="J15" s="208"/>
-      <c r="K15" s="208"/>
-      <c r="L15" s="208"/>
-      <c r="M15" s="208"/>
-      <c r="N15" s="208"/>
-      <c r="O15" s="208"/>
-      <c r="P15" s="208"/>
-      <c r="Q15" s="208"/>
-      <c r="R15" s="208"/>
-      <c r="S15" s="208"/>
-      <c r="T15" s="208"/>
-      <c r="U15" s="208"/>
-      <c r="V15" s="208"/>
-      <c r="W15" s="208"/>
-      <c r="X15" s="208"/>
-      <c r="Y15" s="208"/>
-      <c r="Z15" s="208"/>
-      <c r="AA15" s="208"/>
-      <c r="AB15" s="208"/>
-      <c r="AC15" s="208"/>
-      <c r="AD15" s="208"/>
-      <c r="AE15" s="208"/>
-      <c r="AF15" s="208"/>
-      <c r="AG15" s="208"/>
+      <c r="F15" s="263" t="s">
+        <v>167</v>
+      </c>
+      <c r="G15" s="263"/>
+      <c r="H15" s="263"/>
+      <c r="I15" s="263"/>
+      <c r="J15" s="263"/>
+      <c r="K15" s="263"/>
+      <c r="L15" s="263"/>
+      <c r="M15" s="263"/>
+      <c r="N15" s="263"/>
+      <c r="O15" s="263"/>
+      <c r="P15" s="263"/>
+      <c r="Q15" s="263"/>
+      <c r="R15" s="263"/>
+      <c r="S15" s="263"/>
+      <c r="T15" s="263"/>
+      <c r="U15" s="263"/>
+      <c r="V15" s="263"/>
+      <c r="W15" s="263"/>
+      <c r="X15" s="263"/>
+      <c r="Y15" s="263"/>
+      <c r="Z15" s="263"/>
+      <c r="AA15" s="263"/>
+      <c r="AB15" s="263"/>
+      <c r="AC15" s="263"/>
+      <c r="AD15" s="263"/>
+      <c r="AE15" s="263"/>
+      <c r="AF15" s="263"/>
+      <c r="AG15" s="263"/>
       <c r="AH15" s="1"/>
     </row>
     <row r="16" spans="6:34" s="2" customFormat="1" ht="9.75" customHeight="1">
@@ -17810,36 +17718,36 @@
       <c r="AH16" s="1"/>
     </row>
     <row r="17" spans="6:60" s="10" customFormat="1" ht="33.75" customHeight="1">
-      <c r="F17" s="209" t="s">
-        <v>184</v>
-      </c>
-      <c r="G17" s="209"/>
-      <c r="H17" s="209"/>
-      <c r="I17" s="209"/>
-      <c r="J17" s="209"/>
-      <c r="K17" s="209"/>
-      <c r="L17" s="209"/>
-      <c r="M17" s="209"/>
-      <c r="N17" s="209"/>
-      <c r="O17" s="209"/>
-      <c r="P17" s="209"/>
-      <c r="Q17" s="209"/>
-      <c r="R17" s="209"/>
-      <c r="S17" s="209"/>
-      <c r="T17" s="209"/>
-      <c r="U17" s="209"/>
-      <c r="V17" s="209"/>
-      <c r="W17" s="209"/>
-      <c r="X17" s="209"/>
-      <c r="Y17" s="209"/>
-      <c r="Z17" s="209"/>
-      <c r="AA17" s="209"/>
-      <c r="AB17" s="209"/>
-      <c r="AC17" s="209"/>
-      <c r="AD17" s="209"/>
-      <c r="AE17" s="209"/>
-      <c r="AF17" s="209"/>
-      <c r="AG17" s="209"/>
+      <c r="F17" s="264" t="s">
+        <v>168</v>
+      </c>
+      <c r="G17" s="264"/>
+      <c r="H17" s="264"/>
+      <c r="I17" s="264"/>
+      <c r="J17" s="264"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
+      <c r="M17" s="264"/>
+      <c r="N17" s="264"/>
+      <c r="O17" s="264"/>
+      <c r="P17" s="264"/>
+      <c r="Q17" s="264"/>
+      <c r="R17" s="264"/>
+      <c r="S17" s="264"/>
+      <c r="T17" s="264"/>
+      <c r="U17" s="264"/>
+      <c r="V17" s="264"/>
+      <c r="W17" s="264"/>
+      <c r="X17" s="264"/>
+      <c r="Y17" s="264"/>
+      <c r="Z17" s="264"/>
+      <c r="AA17" s="264"/>
+      <c r="AB17" s="264"/>
+      <c r="AC17" s="264"/>
+      <c r="AD17" s="264"/>
+      <c r="AE17" s="264"/>
+      <c r="AF17" s="264"/>
+      <c r="AG17" s="264"/>
       <c r="AH17" s="3"/>
     </row>
     <row r="18" spans="6:60" s="2" customFormat="1" ht="9.75" customHeight="1">
@@ -17874,546 +17782,546 @@
       <c r="AH18" s="1"/>
     </row>
     <row r="19" spans="6:60" s="2" customFormat="1" ht="19.5" customHeight="1">
-      <c r="F19" s="188" t="s">
-        <v>185</v>
-      </c>
-      <c r="G19" s="188"/>
-      <c r="H19" s="188"/>
-      <c r="I19" s="188"/>
-      <c r="J19" s="188"/>
-      <c r="K19" s="188"/>
-      <c r="L19" s="188"/>
-      <c r="M19" s="188"/>
-      <c r="N19" s="188"/>
-      <c r="O19" s="188"/>
-      <c r="P19" s="188"/>
-      <c r="Q19" s="188"/>
-      <c r="R19" s="188"/>
-      <c r="S19" s="188"/>
-      <c r="T19" s="188"/>
-      <c r="U19" s="188"/>
-      <c r="V19" s="188"/>
-      <c r="W19" s="188"/>
-      <c r="X19" s="188"/>
-      <c r="Y19" s="188"/>
-      <c r="Z19" s="188"/>
-      <c r="AA19" s="188"/>
-      <c r="AB19" s="188"/>
-      <c r="AC19" s="188"/>
-      <c r="AD19" s="188"/>
-      <c r="AE19" s="188"/>
-      <c r="AF19" s="188"/>
-      <c r="AG19" s="188"/>
+      <c r="F19" s="244" t="s">
+        <v>169</v>
+      </c>
+      <c r="G19" s="244"/>
+      <c r="H19" s="244"/>
+      <c r="I19" s="244"/>
+      <c r="J19" s="244"/>
+      <c r="K19" s="244"/>
+      <c r="L19" s="244"/>
+      <c r="M19" s="244"/>
+      <c r="N19" s="244"/>
+      <c r="O19" s="244"/>
+      <c r="P19" s="244"/>
+      <c r="Q19" s="244"/>
+      <c r="R19" s="244"/>
+      <c r="S19" s="244"/>
+      <c r="T19" s="244"/>
+      <c r="U19" s="244"/>
+      <c r="V19" s="244"/>
+      <c r="W19" s="244"/>
+      <c r="X19" s="244"/>
+      <c r="Y19" s="244"/>
+      <c r="Z19" s="244"/>
+      <c r="AA19" s="244"/>
+      <c r="AB19" s="244"/>
+      <c r="AC19" s="244"/>
+      <c r="AD19" s="244"/>
+      <c r="AE19" s="244"/>
+      <c r="AF19" s="244"/>
+      <c r="AG19" s="244"/>
       <c r="AH19" s="1"/>
-      <c r="AM19" s="210"/>
-      <c r="AN19" s="210"/>
-      <c r="AO19" s="210"/>
-      <c r="AP19" s="210"/>
-      <c r="AQ19" s="210"/>
-      <c r="AR19" s="210"/>
-      <c r="AS19" s="210"/>
-      <c r="AT19" s="210"/>
-      <c r="AU19" s="210"/>
-      <c r="AV19" s="210"/>
-      <c r="AW19" s="210"/>
-      <c r="AX19" s="210"/>
-      <c r="AY19" s="210"/>
-      <c r="AZ19" s="210"/>
-      <c r="BA19" s="210"/>
-      <c r="BB19" s="210"/>
-      <c r="BC19" s="210"/>
-      <c r="BD19" s="210"/>
-      <c r="BE19" s="210"/>
-      <c r="BF19" s="210"/>
-      <c r="BG19" s="210"/>
-      <c r="BH19" s="210"/>
+      <c r="AM19" s="265"/>
+      <c r="AN19" s="265"/>
+      <c r="AO19" s="265"/>
+      <c r="AP19" s="265"/>
+      <c r="AQ19" s="265"/>
+      <c r="AR19" s="265"/>
+      <c r="AS19" s="265"/>
+      <c r="AT19" s="265"/>
+      <c r="AU19" s="265"/>
+      <c r="AV19" s="265"/>
+      <c r="AW19" s="265"/>
+      <c r="AX19" s="265"/>
+      <c r="AY19" s="265"/>
+      <c r="AZ19" s="265"/>
+      <c r="BA19" s="265"/>
+      <c r="BB19" s="265"/>
+      <c r="BC19" s="265"/>
+      <c r="BD19" s="265"/>
+      <c r="BE19" s="265"/>
+      <c r="BF19" s="265"/>
+      <c r="BG19" s="265"/>
+      <c r="BH19" s="265"/>
     </row>
     <row r="20" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
-      <c r="F20" s="122"/>
-      <c r="G20" s="122"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="206" t="s">
+      <c r="F20" s="121"/>
+      <c r="G20" s="121"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="121"/>
+      <c r="J20" s="261" t="s">
+        <v>171</v>
+      </c>
+      <c r="K20" s="261"/>
+      <c r="L20" s="261"/>
+      <c r="M20" s="261"/>
+      <c r="N20" s="261"/>
+      <c r="O20" s="261"/>
+      <c r="P20" s="258" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="258"/>
+      <c r="R20" s="258"/>
+      <c r="S20" s="258"/>
+      <c r="T20" s="258"/>
+      <c r="U20" s="258"/>
+      <c r="V20" s="258"/>
+      <c r="W20" s="258"/>
+      <c r="X20" s="258"/>
+      <c r="Y20" s="258"/>
+      <c r="Z20" s="258"/>
+      <c r="AA20" s="258"/>
+      <c r="AB20" s="258"/>
+      <c r="AC20" s="258"/>
+      <c r="AD20" s="258"/>
+      <c r="AE20" s="258"/>
+      <c r="AF20" s="258"/>
+      <c r="AG20" s="258"/>
+      <c r="AH20" s="11"/>
+      <c r="AM20" s="262"/>
+      <c r="AN20" s="262"/>
+      <c r="AO20" s="262"/>
+      <c r="AP20" s="262"/>
+      <c r="AQ20" s="262"/>
+      <c r="AR20" s="262"/>
+      <c r="AS20" s="262"/>
+      <c r="AT20" s="262"/>
+      <c r="AU20" s="262"/>
+      <c r="AV20" s="262"/>
+      <c r="AW20" s="262"/>
+      <c r="AX20" s="262"/>
+      <c r="AY20" s="262"/>
+      <c r="AZ20" s="262"/>
+      <c r="BA20" s="262"/>
+      <c r="BB20" s="262"/>
+      <c r="BC20" s="262"/>
+      <c r="BD20" s="262"/>
+      <c r="BE20" s="262"/>
+      <c r="BF20" s="262"/>
+      <c r="BG20" s="262"/>
+      <c r="BH20" s="262"/>
+    </row>
+    <row r="21" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
+      <c r="F21" s="121"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="121"/>
+      <c r="J21" s="261" t="s">
+        <v>172</v>
+      </c>
+      <c r="K21" s="261"/>
+      <c r="L21" s="261"/>
+      <c r="M21" s="261"/>
+      <c r="N21" s="261"/>
+      <c r="O21" s="261"/>
+      <c r="P21" s="258" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q21" s="258"/>
+      <c r="R21" s="258"/>
+      <c r="S21" s="258"/>
+      <c r="T21" s="258"/>
+      <c r="U21" s="258"/>
+      <c r="V21" s="258"/>
+      <c r="W21" s="258"/>
+      <c r="X21" s="258"/>
+      <c r="Y21" s="258"/>
+      <c r="Z21" s="258"/>
+      <c r="AA21" s="258"/>
+      <c r="AB21" s="258"/>
+      <c r="AC21" s="258"/>
+      <c r="AD21" s="258"/>
+      <c r="AE21" s="258"/>
+      <c r="AF21" s="258"/>
+      <c r="AG21" s="258"/>
+      <c r="AH21" s="11"/>
+    </row>
+    <row r="22" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
+      <c r="F22" s="121"/>
+      <c r="G22" s="121"/>
+      <c r="H22" s="121"/>
+      <c r="I22" s="121"/>
+      <c r="J22" s="261" t="s">
+        <v>173</v>
+      </c>
+      <c r="K22" s="261"/>
+      <c r="L22" s="261"/>
+      <c r="M22" s="261"/>
+      <c r="N22" s="261"/>
+      <c r="O22" s="261"/>
+      <c r="P22" s="258" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q22" s="258"/>
+      <c r="R22" s="258"/>
+      <c r="S22" s="258"/>
+      <c r="T22" s="258"/>
+      <c r="U22" s="258"/>
+      <c r="V22" s="258"/>
+      <c r="W22" s="258"/>
+      <c r="X22" s="258"/>
+      <c r="Y22" s="258"/>
+      <c r="Z22" s="258"/>
+      <c r="AA22" s="258"/>
+      <c r="AB22" s="258"/>
+      <c r="AC22" s="258"/>
+      <c r="AD22" s="258"/>
+      <c r="AE22" s="258"/>
+      <c r="AF22" s="258"/>
+      <c r="AG22" s="258"/>
+      <c r="AH22" s="11"/>
+    </row>
+    <row r="23" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
+      <c r="F23" s="121"/>
+      <c r="G23" s="121"/>
+      <c r="H23" s="121"/>
+      <c r="I23" s="121"/>
+      <c r="J23" s="261" t="s">
+        <v>174</v>
+      </c>
+      <c r="K23" s="261"/>
+      <c r="L23" s="261"/>
+      <c r="M23" s="261"/>
+      <c r="N23" s="261"/>
+      <c r="O23" s="261"/>
+      <c r="P23" s="258" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q23" s="258"/>
+      <c r="R23" s="258"/>
+      <c r="S23" s="258"/>
+      <c r="T23" s="258"/>
+      <c r="U23" s="258"/>
+      <c r="V23" s="258"/>
+      <c r="W23" s="258"/>
+      <c r="X23" s="258"/>
+      <c r="Y23" s="258"/>
+      <c r="Z23" s="258"/>
+      <c r="AA23" s="258"/>
+      <c r="AB23" s="258"/>
+      <c r="AC23" s="258"/>
+      <c r="AD23" s="258"/>
+      <c r="AE23" s="258"/>
+      <c r="AF23" s="258"/>
+      <c r="AG23" s="258"/>
+      <c r="AH23" s="11"/>
+    </row>
+    <row r="24" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
+      <c r="F24" s="121"/>
+      <c r="G24" s="121"/>
+      <c r="H24" s="121"/>
+      <c r="I24" s="121"/>
+      <c r="J24" s="261" t="s">
+        <v>175</v>
+      </c>
+      <c r="K24" s="261"/>
+      <c r="L24" s="261"/>
+      <c r="M24" s="261"/>
+      <c r="N24" s="261"/>
+      <c r="O24" s="261"/>
+      <c r="P24" s="258" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q24" s="258"/>
+      <c r="R24" s="258"/>
+      <c r="S24" s="258"/>
+      <c r="T24" s="258"/>
+      <c r="U24" s="258"/>
+      <c r="V24" s="258"/>
+      <c r="W24" s="258"/>
+      <c r="X24" s="258"/>
+      <c r="Y24" s="258"/>
+      <c r="Z24" s="258"/>
+      <c r="AA24" s="258"/>
+      <c r="AB24" s="258"/>
+      <c r="AC24" s="258"/>
+      <c r="AD24" s="258"/>
+      <c r="AE24" s="258"/>
+      <c r="AF24" s="258"/>
+      <c r="AG24" s="258"/>
+      <c r="AH24" s="13"/>
+    </row>
+    <row r="25" spans="6:60" s="2" customFormat="1" ht="9.75" customHeight="1">
+      <c r="F25" s="121"/>
+      <c r="G25" s="121"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="121"/>
+      <c r="J25" s="121"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="121"/>
+      <c r="R25" s="121"/>
+      <c r="S25" s="121"/>
+      <c r="T25" s="121"/>
+      <c r="U25" s="121"/>
+      <c r="V25" s="121"/>
+      <c r="W25" s="121"/>
+      <c r="X25" s="121"/>
+      <c r="Y25" s="121"/>
+      <c r="Z25" s="121"/>
+      <c r="AA25" s="121"/>
+      <c r="AB25" s="121"/>
+      <c r="AC25" s="121"/>
+      <c r="AD25" s="121"/>
+      <c r="AE25" s="121"/>
+      <c r="AF25" s="121"/>
+      <c r="AG25" s="121"/>
+      <c r="AH25" s="1"/>
+    </row>
+    <row r="26" spans="6:60" s="2" customFormat="1" ht="19.5" customHeight="1">
+      <c r="F26" s="258" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
+      <c r="M26" s="258"/>
+      <c r="N26" s="258"/>
+      <c r="O26" s="258"/>
+      <c r="P26" s="258" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="258"/>
+      <c r="R26" s="258"/>
+      <c r="S26" s="258"/>
+      <c r="T26" s="258"/>
+      <c r="U26" s="258"/>
+      <c r="V26" s="258"/>
+      <c r="W26" s="258"/>
+      <c r="X26" s="258"/>
+      <c r="Y26" s="258"/>
+      <c r="Z26" s="258"/>
+      <c r="AA26" s="258"/>
+      <c r="AB26" s="258"/>
+      <c r="AC26" s="258"/>
+      <c r="AD26" s="258"/>
+      <c r="AE26" s="258"/>
+      <c r="AF26" s="258"/>
+      <c r="AG26" s="258"/>
+      <c r="AH26" s="1"/>
+    </row>
+    <row r="27" spans="6:60" s="12" customFormat="1" ht="39" customHeight="1">
+      <c r="F27" s="121"/>
+      <c r="G27" s="121"/>
+      <c r="H27" s="121"/>
+      <c r="I27" s="121"/>
+      <c r="J27" s="259" t="s">
+        <v>143</v>
+      </c>
+      <c r="K27" s="259"/>
+      <c r="L27" s="259"/>
+      <c r="M27" s="259"/>
+      <c r="N27" s="259"/>
+      <c r="O27" s="259"/>
+      <c r="P27" s="259"/>
+      <c r="Q27" s="259"/>
+      <c r="R27" s="259"/>
+      <c r="S27" s="259"/>
+      <c r="T27" s="259"/>
+      <c r="U27" s="259"/>
+      <c r="V27" s="259"/>
+      <c r="W27" s="259"/>
+      <c r="X27" s="259"/>
+      <c r="Y27" s="259"/>
+      <c r="Z27" s="259"/>
+      <c r="AA27" s="259"/>
+      <c r="AB27" s="259"/>
+      <c r="AC27" s="259"/>
+      <c r="AD27" s="259"/>
+      <c r="AE27" s="259"/>
+      <c r="AF27" s="259"/>
+      <c r="AG27" s="259"/>
+      <c r="AH27" s="11"/>
+    </row>
+    <row r="28" spans="6:60" s="2" customFormat="1" ht="9.75" customHeight="1">
+      <c r="F28" s="121"/>
+      <c r="G28" s="121"/>
+      <c r="H28" s="121"/>
+      <c r="I28" s="121"/>
+      <c r="J28" s="121"/>
+      <c r="K28" s="121"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="121"/>
+      <c r="Q28" s="121"/>
+      <c r="R28" s="121"/>
+      <c r="S28" s="121"/>
+      <c r="T28" s="121"/>
+      <c r="U28" s="121"/>
+      <c r="V28" s="121"/>
+      <c r="W28" s="121"/>
+      <c r="X28" s="121"/>
+      <c r="Y28" s="121"/>
+      <c r="Z28" s="121"/>
+      <c r="AA28" s="121"/>
+      <c r="AB28" s="121"/>
+      <c r="AC28" s="121"/>
+      <c r="AD28" s="121"/>
+      <c r="AE28" s="121"/>
+      <c r="AF28" s="121"/>
+      <c r="AG28" s="121"/>
+      <c r="AH28" s="1"/>
+    </row>
+    <row r="29" spans="6:60" s="12" customFormat="1" ht="19.5" customHeight="1">
+      <c r="F29" s="257" t="s">
+        <v>191</v>
+      </c>
+      <c r="G29" s="257"/>
+      <c r="H29" s="257"/>
+      <c r="I29" s="257"/>
+      <c r="J29" s="257"/>
+      <c r="K29" s="257"/>
+      <c r="L29" s="257"/>
+      <c r="M29" s="257"/>
+      <c r="N29" s="257"/>
+      <c r="O29" s="257"/>
+      <c r="P29" s="260" t="str">
+        <f>"일금"&amp;NUMBERSTRING(대가산출!H25,1)&amp;"원정 (₩"&amp;TEXT(대가산출!H25,"#,##0")&amp;")"</f>
+        <v>일금칠십만원정 (₩700,000)</v>
+      </c>
+      <c r="Q29" s="260"/>
+      <c r="R29" s="260"/>
+      <c r="S29" s="260"/>
+      <c r="T29" s="260"/>
+      <c r="U29" s="260"/>
+      <c r="V29" s="260"/>
+      <c r="W29" s="260"/>
+      <c r="X29" s="260"/>
+      <c r="Y29" s="260"/>
+      <c r="Z29" s="260"/>
+      <c r="AA29" s="260"/>
+      <c r="AB29" s="260"/>
+      <c r="AC29" s="254" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD29" s="255"/>
+      <c r="AE29" s="255"/>
+      <c r="AF29" s="256" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG29" s="256"/>
+      <c r="AH29" s="11"/>
+    </row>
+    <row r="30" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
+      <c r="F30" s="122"/>
+      <c r="G30" s="122"/>
+      <c r="H30" s="122"/>
+      <c r="I30" s="122"/>
+      <c r="J30" s="252" t="s">
         <v>188</v>
       </c>
-      <c r="K20" s="206"/>
-      <c r="L20" s="206"/>
-      <c r="M20" s="206"/>
-      <c r="N20" s="206"/>
-      <c r="O20" s="206"/>
-      <c r="P20" s="206"/>
-      <c r="Q20" s="206"/>
-      <c r="R20" s="199" t="s">
-        <v>10</v>
-      </c>
-      <c r="S20" s="199"/>
-      <c r="T20" s="199"/>
-      <c r="U20" s="199"/>
-      <c r="V20" s="199"/>
-      <c r="W20" s="199"/>
-      <c r="X20" s="199"/>
-      <c r="Y20" s="199"/>
-      <c r="Z20" s="199"/>
-      <c r="AA20" s="199"/>
-      <c r="AB20" s="199"/>
-      <c r="AC20" s="199"/>
-      <c r="AD20" s="199"/>
-      <c r="AE20" s="199"/>
-      <c r="AF20" s="199"/>
-      <c r="AG20" s="199"/>
-      <c r="AH20" s="11"/>
-      <c r="AM20" s="207"/>
-      <c r="AN20" s="207"/>
-      <c r="AO20" s="207"/>
-      <c r="AP20" s="207"/>
-      <c r="AQ20" s="207"/>
-      <c r="AR20" s="207"/>
-      <c r="AS20" s="207"/>
-      <c r="AT20" s="207"/>
-      <c r="AU20" s="207"/>
-      <c r="AV20" s="207"/>
-      <c r="AW20" s="207"/>
-      <c r="AX20" s="207"/>
-      <c r="AY20" s="207"/>
-      <c r="AZ20" s="207"/>
-      <c r="BA20" s="207"/>
-      <c r="BB20" s="207"/>
-      <c r="BC20" s="207"/>
-      <c r="BD20" s="207"/>
-      <c r="BE20" s="207"/>
-      <c r="BF20" s="207"/>
-      <c r="BG20" s="207"/>
-      <c r="BH20" s="207"/>
-    </row>
-    <row r="21" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
-      <c r="F21" s="122"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="206" t="s">
-        <v>189</v>
-      </c>
-      <c r="K21" s="206"/>
-      <c r="L21" s="206"/>
-      <c r="M21" s="206"/>
-      <c r="N21" s="206"/>
-      <c r="O21" s="206"/>
-      <c r="P21" s="206"/>
-      <c r="Q21" s="206"/>
-      <c r="R21" s="199" t="s">
-        <v>11</v>
-      </c>
-      <c r="S21" s="199"/>
-      <c r="T21" s="199"/>
-      <c r="U21" s="199"/>
-      <c r="V21" s="199"/>
-      <c r="W21" s="199"/>
-      <c r="X21" s="199"/>
-      <c r="Y21" s="199"/>
-      <c r="Z21" s="199"/>
-      <c r="AA21" s="199"/>
-      <c r="AB21" s="199"/>
-      <c r="AC21" s="199"/>
-      <c r="AD21" s="199"/>
-      <c r="AE21" s="199"/>
-      <c r="AF21" s="199"/>
-      <c r="AG21" s="199"/>
-      <c r="AH21" s="11"/>
-    </row>
-    <row r="22" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
-      <c r="F22" s="122"/>
-      <c r="G22" s="122"/>
-      <c r="H22" s="122"/>
-      <c r="I22" s="122"/>
-      <c r="J22" s="206" t="s">
-        <v>190</v>
-      </c>
-      <c r="K22" s="206"/>
-      <c r="L22" s="206"/>
-      <c r="M22" s="206"/>
-      <c r="N22" s="206"/>
-      <c r="O22" s="206"/>
-      <c r="P22" s="206"/>
-      <c r="Q22" s="206"/>
-      <c r="R22" s="199" t="s">
-        <v>12</v>
-      </c>
-      <c r="S22" s="199"/>
-      <c r="T22" s="199"/>
-      <c r="U22" s="199"/>
-      <c r="V22" s="199"/>
-      <c r="W22" s="199"/>
-      <c r="X22" s="199"/>
-      <c r="Y22" s="199"/>
-      <c r="Z22" s="199"/>
-      <c r="AA22" s="199"/>
-      <c r="AB22" s="199"/>
-      <c r="AC22" s="199"/>
-      <c r="AD22" s="199"/>
-      <c r="AE22" s="199"/>
-      <c r="AF22" s="199"/>
-      <c r="AG22" s="199"/>
-      <c r="AH22" s="11"/>
-    </row>
-    <row r="23" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
-      <c r="F23" s="122"/>
-      <c r="G23" s="122"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="206" t="s">
-        <v>191</v>
-      </c>
-      <c r="K23" s="206"/>
-      <c r="L23" s="206"/>
-      <c r="M23" s="206"/>
-      <c r="N23" s="206"/>
-      <c r="O23" s="206"/>
-      <c r="P23" s="206"/>
-      <c r="Q23" s="206"/>
-      <c r="R23" s="199" t="s">
-        <v>13</v>
-      </c>
-      <c r="S23" s="199"/>
-      <c r="T23" s="199"/>
-      <c r="U23" s="199"/>
-      <c r="V23" s="199"/>
-      <c r="W23" s="199"/>
-      <c r="X23" s="199"/>
-      <c r="Y23" s="199"/>
-      <c r="Z23" s="199"/>
-      <c r="AA23" s="199"/>
-      <c r="AB23" s="199"/>
-      <c r="AC23" s="199"/>
-      <c r="AD23" s="199"/>
-      <c r="AE23" s="199"/>
-      <c r="AF23" s="199"/>
-      <c r="AG23" s="199"/>
-      <c r="AH23" s="11"/>
-    </row>
-    <row r="24" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
-      <c r="F24" s="122"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="206" t="s">
-        <v>192</v>
-      </c>
-      <c r="K24" s="206"/>
-      <c r="L24" s="206"/>
-      <c r="M24" s="206"/>
-      <c r="N24" s="206"/>
-      <c r="O24" s="206"/>
-      <c r="P24" s="206"/>
-      <c r="Q24" s="206"/>
-      <c r="R24" s="199" t="s">
-        <v>193</v>
-      </c>
-      <c r="S24" s="199"/>
-      <c r="T24" s="199"/>
-      <c r="U24" s="199"/>
-      <c r="V24" s="199"/>
-      <c r="W24" s="199"/>
-      <c r="X24" s="199"/>
-      <c r="Y24" s="199"/>
-      <c r="Z24" s="199"/>
-      <c r="AA24" s="122"/>
-      <c r="AB24" s="122"/>
-      <c r="AC24" s="122"/>
-      <c r="AD24" s="122"/>
-      <c r="AE24" s="122"/>
-      <c r="AF24" s="122"/>
-      <c r="AG24" s="122"/>
-      <c r="AH24" s="13"/>
-    </row>
-    <row r="25" spans="6:60" s="2" customFormat="1" ht="9.75" customHeight="1">
-      <c r="F25" s="122"/>
-      <c r="G25" s="122"/>
-      <c r="H25" s="122"/>
-      <c r="I25" s="122"/>
-      <c r="J25" s="122"/>
-      <c r="K25" s="122"/>
-      <c r="L25" s="122"/>
-      <c r="M25" s="122"/>
-      <c r="N25" s="122"/>
-      <c r="O25" s="122"/>
-      <c r="P25" s="122"/>
-      <c r="Q25" s="122"/>
-      <c r="R25" s="122"/>
-      <c r="S25" s="122"/>
-      <c r="T25" s="122"/>
-      <c r="U25" s="122"/>
-      <c r="V25" s="122"/>
-      <c r="W25" s="122"/>
-      <c r="X25" s="122"/>
-      <c r="Y25" s="122"/>
-      <c r="Z25" s="122"/>
-      <c r="AA25" s="122"/>
-      <c r="AB25" s="122"/>
-      <c r="AC25" s="122"/>
-      <c r="AD25" s="122"/>
-      <c r="AE25" s="122"/>
-      <c r="AF25" s="122"/>
-      <c r="AG25" s="122"/>
-      <c r="AH25" s="1"/>
-    </row>
-    <row r="26" spans="6:60" s="2" customFormat="1" ht="19.5" customHeight="1">
-      <c r="F26" s="199" t="s">
-        <v>186</v>
-      </c>
-      <c r="G26" s="199"/>
-      <c r="H26" s="199"/>
-      <c r="I26" s="199"/>
-      <c r="J26" s="199"/>
-      <c r="K26" s="199"/>
-      <c r="L26" s="199"/>
-      <c r="M26" s="199"/>
-      <c r="N26" s="199"/>
-      <c r="O26" s="199"/>
-      <c r="P26" s="199"/>
-      <c r="Q26" s="199"/>
-      <c r="R26" s="121" t="s">
-        <v>8</v>
-      </c>
-      <c r="S26" s="121"/>
-      <c r="T26" s="121"/>
-      <c r="U26" s="124"/>
-      <c r="V26" s="124"/>
-      <c r="W26" s="124"/>
-      <c r="X26" s="124"/>
-      <c r="Y26" s="124"/>
-      <c r="Z26" s="124"/>
-      <c r="AA26" s="124"/>
-      <c r="AB26" s="124"/>
-      <c r="AC26" s="124"/>
-      <c r="AD26" s="124"/>
-      <c r="AE26" s="124"/>
-      <c r="AF26" s="124"/>
-      <c r="AG26" s="122"/>
-      <c r="AH26" s="1"/>
-    </row>
-    <row r="27" spans="6:60" s="12" customFormat="1" ht="39" customHeight="1">
-      <c r="F27" s="122"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="122"/>
-      <c r="I27" s="122"/>
-      <c r="J27" s="124"/>
-      <c r="K27" s="200" t="s">
-        <v>156</v>
-      </c>
-      <c r="L27" s="200"/>
-      <c r="M27" s="200"/>
-      <c r="N27" s="200"/>
-      <c r="O27" s="200"/>
-      <c r="P27" s="200"/>
-      <c r="Q27" s="200"/>
-      <c r="R27" s="200"/>
-      <c r="S27" s="200"/>
-      <c r="T27" s="200"/>
-      <c r="U27" s="200"/>
-      <c r="V27" s="200"/>
-      <c r="W27" s="200"/>
-      <c r="X27" s="200"/>
-      <c r="Y27" s="200"/>
-      <c r="Z27" s="200"/>
-      <c r="AA27" s="200"/>
-      <c r="AB27" s="200"/>
-      <c r="AC27" s="200"/>
-      <c r="AD27" s="200"/>
-      <c r="AE27" s="200"/>
-      <c r="AF27" s="200"/>
-      <c r="AG27" s="200"/>
-      <c r="AH27" s="11"/>
-    </row>
-    <row r="28" spans="6:60" s="2" customFormat="1" ht="9.75" customHeight="1">
-      <c r="F28" s="122"/>
-      <c r="G28" s="122"/>
-      <c r="H28" s="122"/>
-      <c r="I28" s="122"/>
-      <c r="J28" s="122"/>
-      <c r="K28" s="122"/>
-      <c r="L28" s="122"/>
-      <c r="M28" s="122"/>
-      <c r="N28" s="122"/>
-      <c r="O28" s="122"/>
-      <c r="P28" s="122"/>
-      <c r="Q28" s="122"/>
-      <c r="R28" s="122"/>
-      <c r="S28" s="122"/>
-      <c r="T28" s="122"/>
-      <c r="U28" s="122"/>
-      <c r="V28" s="122"/>
-      <c r="W28" s="122"/>
-      <c r="X28" s="122"/>
-      <c r="Y28" s="122"/>
-      <c r="Z28" s="122"/>
-      <c r="AA28" s="122"/>
-      <c r="AB28" s="122"/>
-      <c r="AC28" s="122"/>
-      <c r="AD28" s="122"/>
-      <c r="AE28" s="122"/>
-      <c r="AF28" s="122"/>
-      <c r="AG28" s="122"/>
-      <c r="AH28" s="1"/>
-    </row>
-    <row r="29" spans="6:60" s="12" customFormat="1" ht="19.5" customHeight="1">
-      <c r="F29" s="201" t="s">
-        <v>180</v>
-      </c>
-      <c r="G29" s="201"/>
-      <c r="H29" s="201"/>
-      <c r="I29" s="201"/>
-      <c r="J29" s="201"/>
-      <c r="K29" s="201"/>
-      <c r="L29" s="201"/>
-      <c r="M29" s="201"/>
-      <c r="N29" s="201"/>
-      <c r="O29" s="201"/>
-      <c r="P29" s="201"/>
-      <c r="Q29" s="201"/>
-      <c r="R29" s="202" t="str">
-        <f>대가산출!D3</f>
-        <v>일금칠십만원정 (₩700,000)</v>
-      </c>
-      <c r="S29" s="202"/>
-      <c r="T29" s="202"/>
-      <c r="U29" s="202"/>
-      <c r="V29" s="202"/>
-      <c r="W29" s="202"/>
-      <c r="X29" s="202"/>
-      <c r="Y29" s="202"/>
-      <c r="Z29" s="202"/>
-      <c r="AA29" s="202"/>
-      <c r="AB29" s="202"/>
-      <c r="AC29" s="203" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD29" s="204"/>
-      <c r="AE29" s="204"/>
-      <c r="AF29" s="205" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG29" s="205"/>
-      <c r="AH29" s="11"/>
-    </row>
-    <row r="30" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
-      <c r="F30" s="123"/>
-      <c r="G30" s="123"/>
-      <c r="H30" s="123"/>
-      <c r="I30" s="123"/>
-      <c r="J30" s="123"/>
-      <c r="K30" s="123"/>
-      <c r="L30" s="195" t="s">
-        <v>122</v>
-      </c>
-      <c r="M30" s="195"/>
-      <c r="N30" s="195"/>
-      <c r="O30" s="195"/>
-      <c r="P30" s="195"/>
-      <c r="Q30" s="195"/>
-      <c r="R30" s="196">
+      <c r="K30" s="252"/>
+      <c r="L30" s="252"/>
+      <c r="M30" s="252"/>
+      <c r="N30" s="252"/>
+      <c r="O30" s="252"/>
+      <c r="P30" s="253">
         <f>대가산출!H27</f>
         <v>700000</v>
       </c>
-      <c r="S30" s="195"/>
-      <c r="T30" s="195"/>
-      <c r="U30" s="195"/>
-      <c r="V30" s="195"/>
-      <c r="W30" s="197"/>
-      <c r="X30" s="198"/>
-      <c r="Y30" s="198"/>
-      <c r="Z30" s="198"/>
-      <c r="AA30" s="198"/>
-      <c r="AB30" s="125" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC30" s="198" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD30" s="198"/>
-      <c r="AE30" s="198"/>
-      <c r="AF30" s="126"/>
+      <c r="Q30" s="253"/>
+      <c r="R30" s="253"/>
+      <c r="S30" s="253"/>
+      <c r="T30" s="253"/>
+      <c r="U30" s="253"/>
+      <c r="V30" s="253"/>
+      <c r="W30" s="253"/>
+      <c r="X30" s="253"/>
+      <c r="Y30" s="253"/>
+      <c r="Z30" s="253"/>
+      <c r="AA30" s="253"/>
+      <c r="AB30" s="123" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC30" s="251" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD30" s="251"/>
+      <c r="AE30" s="251"/>
+      <c r="AF30" s="124"/>
       <c r="AG30" s="104"/>
       <c r="AH30" s="104"/>
       <c r="AI30" s="104"/>
     </row>
     <row r="31" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
-      <c r="F31" s="123"/>
-      <c r="G31" s="123"/>
-      <c r="H31" s="123"/>
-      <c r="I31" s="123"/>
-      <c r="J31" s="123"/>
-      <c r="K31" s="123"/>
-      <c r="L31" s="195" t="s">
-        <v>127</v>
-      </c>
-      <c r="M31" s="195"/>
-      <c r="N31" s="195"/>
-      <c r="O31" s="195"/>
-      <c r="P31" s="195"/>
-      <c r="Q31" s="195"/>
-      <c r="R31" s="196">
-        <f>R30</f>
+      <c r="F31" s="122"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="122"/>
+      <c r="I31" s="122"/>
+      <c r="J31" s="252" t="s">
+        <v>189</v>
+      </c>
+      <c r="K31" s="252"/>
+      <c r="L31" s="252"/>
+      <c r="M31" s="252"/>
+      <c r="N31" s="252"/>
+      <c r="O31" s="252"/>
+      <c r="P31" s="253">
+        <f>P30</f>
         <v>700000</v>
       </c>
-      <c r="S31" s="195"/>
-      <c r="T31" s="195"/>
-      <c r="U31" s="195"/>
-      <c r="V31" s="195"/>
-      <c r="W31" s="197"/>
-      <c r="X31" s="198"/>
-      <c r="Y31" s="198"/>
-      <c r="Z31" s="198"/>
-      <c r="AA31" s="198"/>
-      <c r="AB31" s="125" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC31" s="198" t="s">
-        <v>126</v>
-      </c>
-      <c r="AD31" s="198"/>
-      <c r="AE31" s="198"/>
-      <c r="AF31" s="126"/>
+      <c r="Q31" s="253"/>
+      <c r="R31" s="253"/>
+      <c r="S31" s="253"/>
+      <c r="T31" s="253"/>
+      <c r="U31" s="253"/>
+      <c r="V31" s="253"/>
+      <c r="W31" s="253"/>
+      <c r="X31" s="253"/>
+      <c r="Y31" s="253"/>
+      <c r="Z31" s="253"/>
+      <c r="AA31" s="253"/>
+      <c r="AB31" s="123" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC31" s="251" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD31" s="251"/>
+      <c r="AE31" s="251"/>
+      <c r="AF31" s="124"/>
       <c r="AG31" s="104"/>
       <c r="AH31" s="104"/>
       <c r="AI31" s="104"/>
     </row>
     <row r="32" spans="6:60" s="12" customFormat="1" ht="16.5" customHeight="1">
-      <c r="F32" s="123"/>
-      <c r="G32" s="123"/>
-      <c r="H32" s="123"/>
-      <c r="I32" s="123"/>
-      <c r="J32" s="123"/>
-      <c r="K32" s="123"/>
-      <c r="L32" s="190" t="s">
-        <v>123</v>
-      </c>
-      <c r="M32" s="190"/>
-      <c r="N32" s="190"/>
-      <c r="O32" s="190"/>
-      <c r="P32" s="190"/>
-      <c r="Q32" s="190"/>
-      <c r="R32" s="191">
-        <f>R31+R30</f>
+      <c r="F32" s="122"/>
+      <c r="G32" s="122"/>
+      <c r="H32" s="122"/>
+      <c r="I32" s="122"/>
+      <c r="J32" s="249" t="s">
+        <v>116</v>
+      </c>
+      <c r="K32" s="249"/>
+      <c r="L32" s="249"/>
+      <c r="M32" s="249"/>
+      <c r="N32" s="249"/>
+      <c r="O32" s="249"/>
+      <c r="P32" s="250">
+        <f>P31+P30</f>
         <v>1400000</v>
       </c>
-      <c r="S32" s="191"/>
-      <c r="T32" s="191"/>
-      <c r="U32" s="191"/>
-      <c r="V32" s="191"/>
-      <c r="W32" s="192"/>
-      <c r="X32" s="193"/>
-      <c r="Y32" s="193"/>
-      <c r="Z32" s="193"/>
-      <c r="AA32" s="193"/>
-      <c r="AB32" s="136" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC32" s="194" t="s">
-        <v>124</v>
-      </c>
-      <c r="AD32" s="194"/>
-      <c r="AE32" s="194"/>
-      <c r="AF32" s="194"/>
+      <c r="Q32" s="250"/>
+      <c r="R32" s="250"/>
+      <c r="S32" s="250"/>
+      <c r="T32" s="250"/>
+      <c r="U32" s="250"/>
+      <c r="V32" s="250"/>
+      <c r="W32" s="250"/>
+      <c r="X32" s="250"/>
+      <c r="Y32" s="250"/>
+      <c r="Z32" s="250"/>
+      <c r="AA32" s="250"/>
+      <c r="AB32" s="132" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC32" s="248" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD32" s="248"/>
+      <c r="AE32" s="248"/>
+      <c r="AF32" s="248"/>
       <c r="AG32" s="104"/>
       <c r="AH32" s="104"/>
       <c r="AI32" s="104"/>
@@ -18450,36 +18358,36 @@
       <c r="AH33" s="1"/>
     </row>
     <row r="34" spans="6:37" s="2" customFormat="1" ht="19.5" customHeight="1">
-      <c r="F34" s="188" t="s">
-        <v>187</v>
-      </c>
-      <c r="G34" s="188"/>
-      <c r="H34" s="188"/>
-      <c r="I34" s="188"/>
-      <c r="J34" s="188"/>
-      <c r="K34" s="188"/>
-      <c r="L34" s="188"/>
-      <c r="M34" s="188"/>
-      <c r="N34" s="188"/>
-      <c r="O34" s="188"/>
-      <c r="P34" s="188"/>
-      <c r="Q34" s="188"/>
+      <c r="F34" s="244" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="244"/>
+      <c r="H34" s="244"/>
+      <c r="I34" s="244"/>
+      <c r="J34" s="244"/>
+      <c r="K34" s="244"/>
+      <c r="L34" s="244"/>
+      <c r="M34" s="244"/>
+      <c r="N34" s="244"/>
+      <c r="O34" s="244"/>
+      <c r="P34" s="244"/>
+      <c r="Q34" s="244"/>
       <c r="R34" s="117"/>
-      <c r="S34" s="127"/>
-      <c r="T34" s="127"/>
-      <c r="U34" s="127"/>
-      <c r="V34" s="127"/>
-      <c r="W34" s="127"/>
-      <c r="X34" s="127"/>
-      <c r="Y34" s="127"/>
-      <c r="Z34" s="127"/>
-      <c r="AA34" s="127"/>
-      <c r="AB34" s="127"/>
-      <c r="AC34" s="127"/>
-      <c r="AD34" s="127"/>
-      <c r="AE34" s="127"/>
-      <c r="AF34" s="127"/>
-      <c r="AG34" s="127"/>
+      <c r="S34" s="125"/>
+      <c r="T34" s="125"/>
+      <c r="U34" s="125"/>
+      <c r="V34" s="125"/>
+      <c r="W34" s="125"/>
+      <c r="X34" s="125"/>
+      <c r="Y34" s="125"/>
+      <c r="Z34" s="125"/>
+      <c r="AA34" s="125"/>
+      <c r="AB34" s="125"/>
+      <c r="AC34" s="125"/>
+      <c r="AD34" s="125"/>
+      <c r="AE34" s="125"/>
+      <c r="AF34" s="125"/>
+      <c r="AG34" s="125"/>
       <c r="AH34" s="1"/>
     </row>
     <row r="35" spans="6:37" s="2" customFormat="1" ht="16.5" customHeight="1">
@@ -18487,32 +18395,32 @@
       <c r="G35" s="117"/>
       <c r="H35" s="117"/>
       <c r="I35" s="117"/>
-      <c r="J35" s="117"/>
-      <c r="K35" s="185" t="s">
-        <v>153</v>
-      </c>
-      <c r="L35" s="185"/>
-      <c r="M35" s="185"/>
-      <c r="N35" s="185"/>
-      <c r="O35" s="185"/>
-      <c r="P35" s="185"/>
-      <c r="Q35" s="185"/>
-      <c r="R35" s="185"/>
-      <c r="S35" s="185"/>
-      <c r="T35" s="185"/>
-      <c r="U35" s="185"/>
-      <c r="V35" s="185"/>
-      <c r="W35" s="185"/>
-      <c r="X35" s="185"/>
-      <c r="Y35" s="185"/>
-      <c r="Z35" s="185"/>
-      <c r="AA35" s="185"/>
-      <c r="AB35" s="185"/>
-      <c r="AC35" s="185"/>
-      <c r="AD35" s="185"/>
-      <c r="AE35" s="185"/>
-      <c r="AF35" s="185"/>
-      <c r="AG35" s="185"/>
+      <c r="J35" s="246" t="s">
+        <v>140</v>
+      </c>
+      <c r="K35" s="246"/>
+      <c r="L35" s="246"/>
+      <c r="M35" s="246"/>
+      <c r="N35" s="246"/>
+      <c r="O35" s="246"/>
+      <c r="P35" s="246"/>
+      <c r="Q35" s="246"/>
+      <c r="R35" s="246"/>
+      <c r="S35" s="246"/>
+      <c r="T35" s="246"/>
+      <c r="U35" s="246"/>
+      <c r="V35" s="246"/>
+      <c r="W35" s="246"/>
+      <c r="X35" s="246"/>
+      <c r="Y35" s="246"/>
+      <c r="Z35" s="246"/>
+      <c r="AA35" s="246"/>
+      <c r="AB35" s="246"/>
+      <c r="AC35" s="246"/>
+      <c r="AD35" s="246"/>
+      <c r="AE35" s="246"/>
+      <c r="AF35" s="246"/>
+      <c r="AG35" s="246"/>
       <c r="AH35" s="14"/>
       <c r="AI35" s="15"/>
       <c r="AJ35" s="15"/>
@@ -18523,32 +18431,32 @@
       <c r="G36" s="117"/>
       <c r="H36" s="117"/>
       <c r="I36" s="117"/>
-      <c r="J36" s="117"/>
-      <c r="K36" s="185" t="s">
-        <v>158</v>
-      </c>
-      <c r="L36" s="185"/>
-      <c r="M36" s="185"/>
-      <c r="N36" s="185"/>
-      <c r="O36" s="185"/>
-      <c r="P36" s="185"/>
-      <c r="Q36" s="185"/>
-      <c r="R36" s="185"/>
-      <c r="S36" s="185"/>
-      <c r="T36" s="185"/>
-      <c r="U36" s="185"/>
-      <c r="V36" s="185"/>
-      <c r="W36" s="185"/>
-      <c r="X36" s="185"/>
-      <c r="Y36" s="185"/>
-      <c r="Z36" s="185"/>
-      <c r="AA36" s="185"/>
-      <c r="AB36" s="185"/>
-      <c r="AC36" s="185"/>
-      <c r="AD36" s="185"/>
-      <c r="AE36" s="185"/>
-      <c r="AF36" s="185"/>
-      <c r="AG36" s="185"/>
+      <c r="J36" s="246" t="s">
+        <v>145</v>
+      </c>
+      <c r="K36" s="246"/>
+      <c r="L36" s="246"/>
+      <c r="M36" s="246"/>
+      <c r="N36" s="246"/>
+      <c r="O36" s="246"/>
+      <c r="P36" s="246"/>
+      <c r="Q36" s="246"/>
+      <c r="R36" s="246"/>
+      <c r="S36" s="246"/>
+      <c r="T36" s="246"/>
+      <c r="U36" s="246"/>
+      <c r="V36" s="246"/>
+      <c r="W36" s="246"/>
+      <c r="X36" s="246"/>
+      <c r="Y36" s="246"/>
+      <c r="Z36" s="246"/>
+      <c r="AA36" s="246"/>
+      <c r="AB36" s="246"/>
+      <c r="AC36" s="246"/>
+      <c r="AD36" s="246"/>
+      <c r="AE36" s="246"/>
+      <c r="AF36" s="246"/>
+      <c r="AG36" s="246"/>
       <c r="AH36" s="1"/>
     </row>
     <row r="37" spans="6:37" s="2" customFormat="1" ht="16.5" customHeight="1">
@@ -18556,32 +18464,32 @@
       <c r="G37" s="117"/>
       <c r="H37" s="117"/>
       <c r="I37" s="117"/>
-      <c r="J37" s="117"/>
-      <c r="K37" s="186" t="s">
-        <v>155</v>
-      </c>
-      <c r="L37" s="186"/>
-      <c r="M37" s="186"/>
-      <c r="N37" s="186"/>
-      <c r="O37" s="186"/>
-      <c r="P37" s="186"/>
-      <c r="Q37" s="186"/>
-      <c r="R37" s="186"/>
-      <c r="S37" s="186"/>
-      <c r="T37" s="186"/>
-      <c r="U37" s="186"/>
-      <c r="V37" s="186"/>
-      <c r="W37" s="186"/>
-      <c r="X37" s="186"/>
-      <c r="Y37" s="186"/>
-      <c r="Z37" s="186"/>
-      <c r="AA37" s="186"/>
-      <c r="AB37" s="186"/>
-      <c r="AC37" s="186"/>
-      <c r="AD37" s="186"/>
-      <c r="AE37" s="186"/>
-      <c r="AF37" s="186"/>
-      <c r="AG37" s="186"/>
+      <c r="J37" s="244" t="s">
+        <v>142</v>
+      </c>
+      <c r="K37" s="244"/>
+      <c r="L37" s="244"/>
+      <c r="M37" s="244"/>
+      <c r="N37" s="244"/>
+      <c r="O37" s="244"/>
+      <c r="P37" s="244"/>
+      <c r="Q37" s="244"/>
+      <c r="R37" s="244"/>
+      <c r="S37" s="244"/>
+      <c r="T37" s="244"/>
+      <c r="U37" s="244"/>
+      <c r="V37" s="244"/>
+      <c r="W37" s="244"/>
+      <c r="X37" s="244"/>
+      <c r="Y37" s="244"/>
+      <c r="Z37" s="244"/>
+      <c r="AA37" s="244"/>
+      <c r="AB37" s="244"/>
+      <c r="AC37" s="244"/>
+      <c r="AD37" s="244"/>
+      <c r="AE37" s="244"/>
+      <c r="AF37" s="244"/>
+      <c r="AG37" s="244"/>
       <c r="AH37" s="1"/>
     </row>
     <row r="38" spans="6:37" s="2" customFormat="1" ht="16.5" customHeight="1">
@@ -18589,36 +18497,36 @@
       <c r="G38" s="117"/>
       <c r="H38" s="117"/>
       <c r="I38" s="117"/>
-      <c r="J38" s="117"/>
-      <c r="K38" s="187" t="s">
-        <v>154</v>
-      </c>
-      <c r="L38" s="187"/>
-      <c r="M38" s="187"/>
-      <c r="N38" s="187"/>
-      <c r="O38" s="187"/>
-      <c r="P38" s="187"/>
-      <c r="Q38" s="187"/>
-      <c r="R38" s="187"/>
-      <c r="S38" s="187"/>
-      <c r="T38" s="187"/>
-      <c r="U38" s="187"/>
-      <c r="V38" s="187"/>
-      <c r="W38" s="187"/>
-      <c r="X38" s="187"/>
-      <c r="Y38" s="187"/>
-      <c r="Z38" s="187"/>
-      <c r="AA38" s="187"/>
-      <c r="AB38" s="187"/>
-      <c r="AC38" s="187"/>
-      <c r="AD38" s="187"/>
-      <c r="AE38" s="187"/>
-      <c r="AF38" s="187"/>
-      <c r="AG38" s="187"/>
+      <c r="J38" s="247" t="s">
+        <v>141</v>
+      </c>
+      <c r="K38" s="247"/>
+      <c r="L38" s="247"/>
+      <c r="M38" s="247"/>
+      <c r="N38" s="247"/>
+      <c r="O38" s="247"/>
+      <c r="P38" s="247"/>
+      <c r="Q38" s="247"/>
+      <c r="R38" s="247"/>
+      <c r="S38" s="247"/>
+      <c r="T38" s="247"/>
+      <c r="U38" s="247"/>
+      <c r="V38" s="247"/>
+      <c r="W38" s="247"/>
+      <c r="X38" s="247"/>
+      <c r="Y38" s="247"/>
+      <c r="Z38" s="247"/>
+      <c r="AA38" s="247"/>
+      <c r="AB38" s="247"/>
+      <c r="AC38" s="247"/>
+      <c r="AD38" s="247"/>
+      <c r="AE38" s="247"/>
+      <c r="AF38" s="247"/>
+      <c r="AG38" s="247"/>
       <c r="AH38" s="1"/>
     </row>
     <row r="39" spans="6:37" s="2" customFormat="1" ht="12" customHeight="1">
-      <c r="F39" s="128"/>
+      <c r="F39" s="126"/>
       <c r="G39" s="117"/>
       <c r="H39" s="117"/>
       <c r="I39" s="117"/>
@@ -18649,131 +18557,131 @@
       <c r="AH39" s="1"/>
     </row>
     <row r="40" spans="6:37" s="2" customFormat="1" ht="19.5" customHeight="1">
-      <c r="F40" s="188" t="s">
-        <v>138</v>
-      </c>
-      <c r="G40" s="188"/>
-      <c r="H40" s="188"/>
-      <c r="I40" s="188"/>
-      <c r="J40" s="188"/>
-      <c r="K40" s="188"/>
-      <c r="L40" s="188"/>
-      <c r="M40" s="188"/>
-      <c r="N40" s="188"/>
-      <c r="O40" s="188"/>
-      <c r="P40" s="188"/>
-      <c r="Q40" s="188"/>
-      <c r="R40" s="188"/>
-      <c r="S40" s="188"/>
-      <c r="T40" s="188"/>
-      <c r="U40" s="188"/>
-      <c r="V40" s="188"/>
-      <c r="W40" s="188"/>
-      <c r="X40" s="188"/>
-      <c r="Y40" s="188"/>
-      <c r="Z40" s="188"/>
-      <c r="AA40" s="188"/>
-      <c r="AB40" s="188"/>
-      <c r="AC40" s="188"/>
-      <c r="AD40" s="188"/>
-      <c r="AE40" s="188"/>
-      <c r="AF40" s="188"/>
-      <c r="AG40" s="188"/>
+      <c r="F40" s="244" t="s">
+        <v>127</v>
+      </c>
+      <c r="G40" s="244"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="244"/>
+      <c r="L40" s="244"/>
+      <c r="M40" s="244"/>
+      <c r="N40" s="244"/>
+      <c r="O40" s="244"/>
+      <c r="P40" s="244"/>
+      <c r="Q40" s="244"/>
+      <c r="R40" s="244"/>
+      <c r="S40" s="244"/>
+      <c r="T40" s="244"/>
+      <c r="U40" s="244"/>
+      <c r="V40" s="244"/>
+      <c r="W40" s="244"/>
+      <c r="X40" s="244"/>
+      <c r="Y40" s="244"/>
+      <c r="Z40" s="244"/>
+      <c r="AA40" s="244"/>
+      <c r="AB40" s="244"/>
+      <c r="AC40" s="244"/>
+      <c r="AD40" s="244"/>
+      <c r="AE40" s="244"/>
+      <c r="AF40" s="244"/>
+      <c r="AG40" s="244"/>
       <c r="AH40" s="1"/>
     </row>
     <row r="41" spans="6:37" s="2" customFormat="1" ht="3.75" customHeight="1">
-      <c r="F41" s="129"/>
-      <c r="G41" s="129"/>
-      <c r="H41" s="129"/>
-      <c r="I41" s="129"/>
-      <c r="J41" s="129"/>
-      <c r="K41" s="129"/>
-      <c r="L41" s="129"/>
-      <c r="M41" s="129"/>
-      <c r="N41" s="129"/>
-      <c r="O41" s="129"/>
-      <c r="P41" s="129"/>
-      <c r="Q41" s="129"/>
-      <c r="R41" s="129"/>
-      <c r="S41" s="129"/>
-      <c r="T41" s="129"/>
-      <c r="U41" s="129"/>
-      <c r="V41" s="129"/>
-      <c r="W41" s="129"/>
-      <c r="X41" s="129"/>
-      <c r="Y41" s="129"/>
-      <c r="Z41" s="129"/>
-      <c r="AA41" s="129"/>
-      <c r="AB41" s="129"/>
-      <c r="AC41" s="129"/>
-      <c r="AD41" s="129"/>
-      <c r="AE41" s="129"/>
-      <c r="AF41" s="129"/>
-      <c r="AG41" s="129"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="127"/>
+      <c r="H41" s="127"/>
+      <c r="I41" s="127"/>
+      <c r="J41" s="127"/>
+      <c r="K41" s="127"/>
+      <c r="L41" s="127"/>
+      <c r="M41" s="127"/>
+      <c r="N41" s="127"/>
+      <c r="O41" s="127"/>
+      <c r="P41" s="127"/>
+      <c r="Q41" s="127"/>
+      <c r="R41" s="127"/>
+      <c r="S41" s="127"/>
+      <c r="T41" s="127"/>
+      <c r="U41" s="127"/>
+      <c r="V41" s="127"/>
+      <c r="W41" s="127"/>
+      <c r="X41" s="127"/>
+      <c r="Y41" s="127"/>
+      <c r="Z41" s="127"/>
+      <c r="AA41" s="127"/>
+      <c r="AB41" s="127"/>
+      <c r="AC41" s="127"/>
+      <c r="AD41" s="127"/>
+      <c r="AE41" s="127"/>
+      <c r="AF41" s="127"/>
+      <c r="AG41" s="127"/>
       <c r="AH41" s="1"/>
     </row>
     <row r="42" spans="6:37" s="2" customFormat="1" ht="39.75" customHeight="1">
-      <c r="F42" s="189" t="s">
+      <c r="F42" s="245" t="s">
         <v>7</v>
       </c>
-      <c r="G42" s="189"/>
-      <c r="H42" s="189"/>
-      <c r="I42" s="189"/>
-      <c r="J42" s="189"/>
-      <c r="K42" s="189"/>
-      <c r="L42" s="189"/>
-      <c r="M42" s="189"/>
-      <c r="N42" s="189"/>
-      <c r="O42" s="189"/>
-      <c r="P42" s="189"/>
-      <c r="Q42" s="189"/>
-      <c r="R42" s="189"/>
-      <c r="S42" s="189"/>
-      <c r="T42" s="189"/>
-      <c r="U42" s="189"/>
-      <c r="V42" s="189"/>
-      <c r="W42" s="189"/>
-      <c r="X42" s="189"/>
-      <c r="Y42" s="189"/>
-      <c r="Z42" s="189"/>
-      <c r="AA42" s="189"/>
-      <c r="AB42" s="189"/>
-      <c r="AC42" s="189"/>
-      <c r="AD42" s="189"/>
-      <c r="AE42" s="189"/>
-      <c r="AF42" s="189"/>
-      <c r="AG42" s="189"/>
+      <c r="G42" s="245"/>
+      <c r="H42" s="245"/>
+      <c r="I42" s="245"/>
+      <c r="J42" s="245"/>
+      <c r="K42" s="245"/>
+      <c r="L42" s="245"/>
+      <c r="M42" s="245"/>
+      <c r="N42" s="245"/>
+      <c r="O42" s="245"/>
+      <c r="P42" s="245"/>
+      <c r="Q42" s="245"/>
+      <c r="R42" s="245"/>
+      <c r="S42" s="245"/>
+      <c r="T42" s="245"/>
+      <c r="U42" s="245"/>
+      <c r="V42" s="245"/>
+      <c r="W42" s="245"/>
+      <c r="X42" s="245"/>
+      <c r="Y42" s="245"/>
+      <c r="Z42" s="245"/>
+      <c r="AA42" s="245"/>
+      <c r="AB42" s="245"/>
+      <c r="AC42" s="245"/>
+      <c r="AD42" s="245"/>
+      <c r="AE42" s="245"/>
+      <c r="AF42" s="245"/>
+      <c r="AG42" s="245"/>
       <c r="AH42" s="4"/>
     </row>
     <row r="43" spans="6:37" ht="6" customHeight="1">
-      <c r="F43" s="130"/>
-      <c r="G43" s="130"/>
-      <c r="H43" s="131"/>
-      <c r="I43" s="131"/>
-      <c r="J43" s="131"/>
-      <c r="K43" s="131"/>
-      <c r="L43" s="131"/>
-      <c r="M43" s="131"/>
-      <c r="N43" s="131"/>
-      <c r="O43" s="130"/>
-      <c r="P43" s="130"/>
-      <c r="Q43" s="130"/>
-      <c r="R43" s="130"/>
-      <c r="S43" s="130"/>
-      <c r="T43" s="130"/>
-      <c r="U43" s="130"/>
-      <c r="V43" s="130"/>
-      <c r="W43" s="130"/>
-      <c r="X43" s="130"/>
-      <c r="Y43" s="130"/>
-      <c r="Z43" s="130"/>
-      <c r="AA43" s="130"/>
-      <c r="AB43" s="130"/>
-      <c r="AC43" s="130"/>
-      <c r="AD43" s="130"/>
-      <c r="AE43" s="130"/>
-      <c r="AF43" s="130"/>
-      <c r="AG43" s="130"/>
+      <c r="F43" s="128"/>
+      <c r="G43" s="128"/>
+      <c r="H43" s="129"/>
+      <c r="I43" s="129"/>
+      <c r="J43" s="129"/>
+      <c r="K43" s="129"/>
+      <c r="L43" s="129"/>
+      <c r="M43" s="129"/>
+      <c r="N43" s="129"/>
+      <c r="O43" s="128"/>
+      <c r="P43" s="128"/>
+      <c r="Q43" s="128"/>
+      <c r="R43" s="128"/>
+      <c r="S43" s="128"/>
+      <c r="T43" s="128"/>
+      <c r="U43" s="128"/>
+      <c r="V43" s="128"/>
+      <c r="W43" s="128"/>
+      <c r="X43" s="128"/>
+      <c r="Y43" s="128"/>
+      <c r="Z43" s="128"/>
+      <c r="AA43" s="128"/>
+      <c r="AB43" s="128"/>
+      <c r="AC43" s="128"/>
+      <c r="AD43" s="128"/>
+      <c r="AE43" s="128"/>
+      <c r="AF43" s="128"/>
+      <c r="AG43" s="128"/>
     </row>
     <row r="44" spans="6:37">
       <c r="F44" s="5"/>
@@ -19455,7 +19363,7 @@
       <c r="N114" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="50">
     <mergeCell ref="F1:AG1"/>
     <mergeCell ref="F3:AG3"/>
     <mergeCell ref="F6:I6"/>
@@ -19466,45 +19374,46 @@
     <mergeCell ref="J8:AE8"/>
     <mergeCell ref="F9:I9"/>
     <mergeCell ref="F10:I10"/>
-    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="J10:AG10"/>
     <mergeCell ref="F13:AG13"/>
     <mergeCell ref="F15:AG15"/>
     <mergeCell ref="F17:AG17"/>
     <mergeCell ref="F19:AG19"/>
     <mergeCell ref="AM19:BH19"/>
-    <mergeCell ref="R20:AG20"/>
     <mergeCell ref="AM20:BH20"/>
-    <mergeCell ref="R21:AG21"/>
-    <mergeCell ref="J20:Q20"/>
-    <mergeCell ref="J21:Q21"/>
-    <mergeCell ref="R22:AG22"/>
-    <mergeCell ref="R23:AG23"/>
-    <mergeCell ref="R24:Z24"/>
-    <mergeCell ref="J22:Q22"/>
-    <mergeCell ref="J23:Q23"/>
-    <mergeCell ref="J24:Q24"/>
-    <mergeCell ref="F26:Q26"/>
-    <mergeCell ref="K27:AG27"/>
-    <mergeCell ref="F29:Q29"/>
-    <mergeCell ref="R29:AB29"/>
+    <mergeCell ref="J20:O20"/>
+    <mergeCell ref="J21:O21"/>
+    <mergeCell ref="P20:AG20"/>
+    <mergeCell ref="P21:AG21"/>
+    <mergeCell ref="J22:O22"/>
+    <mergeCell ref="J23:O23"/>
+    <mergeCell ref="J24:O24"/>
+    <mergeCell ref="P22:AG22"/>
+    <mergeCell ref="P23:AG23"/>
+    <mergeCell ref="P24:AG24"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF29:AG29"/>
-    <mergeCell ref="L30:Q30"/>
-    <mergeCell ref="R30:AA30"/>
+    <mergeCell ref="F29:O29"/>
+    <mergeCell ref="F26:O26"/>
+    <mergeCell ref="J27:AG27"/>
+    <mergeCell ref="P29:AB29"/>
+    <mergeCell ref="P26:AG26"/>
     <mergeCell ref="AC30:AE30"/>
-    <mergeCell ref="L31:Q31"/>
-    <mergeCell ref="R31:AA31"/>
     <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="L32:Q32"/>
-    <mergeCell ref="R32:AA32"/>
+    <mergeCell ref="J30:O30"/>
+    <mergeCell ref="J31:O31"/>
+    <mergeCell ref="P30:AA30"/>
+    <mergeCell ref="P31:AA31"/>
     <mergeCell ref="F34:Q34"/>
-    <mergeCell ref="K35:AG35"/>
     <mergeCell ref="AC32:AF32"/>
-    <mergeCell ref="K36:AG36"/>
-    <mergeCell ref="K37:AG37"/>
-    <mergeCell ref="K38:AG38"/>
+    <mergeCell ref="J32:O32"/>
+    <mergeCell ref="P32:AA32"/>
+    <mergeCell ref="J35:AG35"/>
     <mergeCell ref="F40:AG40"/>
     <mergeCell ref="F42:AG42"/>
+    <mergeCell ref="J36:AG36"/>
+    <mergeCell ref="J37:AG37"/>
+    <mergeCell ref="J38:AG38"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -19531,93 +19440,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" s="16" customFormat="1" ht="39" customHeight="1">
-      <c r="B1" s="176" t="s">
-        <v>140</v>
-      </c>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-    </row>
-    <row r="2" spans="2:9" s="16" customFormat="1" ht="18" customHeight="1">
+      <c r="B1" s="308" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="309"/>
+      <c r="D1" s="309"/>
+      <c r="E1" s="309"/>
+      <c r="F1" s="309"/>
+      <c r="G1" s="309"/>
+      <c r="H1" s="309"/>
+      <c r="I1" s="309"/>
+    </row>
+    <row r="2" spans="2:9" s="16" customFormat="1" ht="18" customHeight="1" thickBot="1">
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
-      <c r="H2" s="178"/>
-      <c r="I2" s="178"/>
-    </row>
-    <row r="3" spans="2:9" s="19" customFormat="1" ht="34.5" customHeight="1">
-      <c r="B3" s="179" t="s">
+      <c r="H2" s="310"/>
+      <c r="I2" s="310"/>
+    </row>
+    <row r="3" spans="2:9" s="19" customFormat="1" ht="34.5" customHeight="1" thickBot="1">
+      <c r="B3" s="311" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="180"/>
-      <c r="D3" s="181" t="str">
-        <f>"일금"&amp;NUMBERSTRING(H25,1)&amp;"원정 (₩"&amp;TEXT(H25,"#,##0")&amp;")"</f>
-        <v>일금칠십만원정 (₩700,000)</v>
-      </c>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="18" t="s">
-        <v>18</v>
-      </c>
+      <c r="C3" s="312"/>
+      <c r="D3" s="315" t="str">
+        <f>"일금"&amp;NUMBERSTRING(H25,1)&amp;"원정 (₩"&amp;TEXT(H25,"#,##0")&amp;") - VAT별도"</f>
+        <v>일금칠십만원정 (₩700,000) - VAT별도</v>
+      </c>
+      <c r="E3" s="317"/>
+      <c r="F3" s="317"/>
+      <c r="G3" s="317"/>
+      <c r="H3" s="317"/>
+      <c r="I3" s="318"/>
     </row>
     <row r="4" spans="2:9" s="19" customFormat="1" ht="38.25" hidden="1" customHeight="1">
-      <c r="B4" s="183" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="184"/>
-      <c r="D4" s="181" t="str">
+      <c r="B4" s="313" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="314"/>
+      <c r="D4" s="315" t="str">
         <f>"일금"&amp;NUMBERSTRING(H28,1)&amp;"원정 (₩"&amp;TEXT(H28,"#,##0")&amp;") - VAT별도"</f>
         <v>일금일백사십만원정 (₩1,400,000) - VAT별도</v>
       </c>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="182"/>
+      <c r="E4" s="316"/>
+      <c r="F4" s="316"/>
+      <c r="G4" s="316"/>
+      <c r="H4" s="316"/>
       <c r="I4" s="18" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="2:9" s="19" customFormat="1" ht="38.25" hidden="1" customHeight="1">
-      <c r="B5" s="165" t="s">
+      <c r="B5" s="297" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="166"/>
-      <c r="D5" s="167" t="e">
+      <c r="C5" s="298"/>
+      <c r="D5" s="299" t="e">
         <f>"일금 "&amp;NUMBERSTRING(H26,1)&amp;"원정"&amp;TEXT(H26,"(￦ #,##0)")&amp;" "</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
-      <c r="I5" s="168"/>
-    </row>
-    <row r="6" spans="2:9" s="19" customFormat="1" ht="31.5" customHeight="1">
-      <c r="B6" s="169" t="s">
+      <c r="E5" s="299"/>
+      <c r="F5" s="299"/>
+      <c r="G5" s="299"/>
+      <c r="H5" s="299"/>
+      <c r="I5" s="300"/>
+    </row>
+    <row r="6" spans="2:9" s="19" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
+      <c r="B6" s="301" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="170"/>
-      <c r="D6" s="170"/>
-      <c r="E6" s="170"/>
-      <c r="F6" s="170"/>
-      <c r="G6" s="170"/>
-      <c r="H6" s="170"/>
-      <c r="I6" s="171"/>
-    </row>
-    <row r="7" spans="2:9" s="22" customFormat="1" ht="30" customHeight="1">
-      <c r="B7" s="172" t="s">
+      <c r="C6" s="302"/>
+      <c r="D6" s="302"/>
+      <c r="E6" s="302"/>
+      <c r="F6" s="302"/>
+      <c r="G6" s="302"/>
+      <c r="H6" s="302"/>
+      <c r="I6" s="303"/>
+    </row>
+    <row r="7" spans="2:9" s="22" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="B7" s="304" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="173"/>
+      <c r="C7" s="305"/>
       <c r="D7" s="20" t="s">
         <v>22</v>
       </c>
@@ -19638,10 +19545,10 @@
       </c>
     </row>
     <row r="8" spans="2:9" s="22" customFormat="1" ht="28" customHeight="1">
-      <c r="B8" s="174" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="175"/>
+      <c r="B8" s="306" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="307"/>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -19655,7 +19562,7 @@
     <row r="9" spans="2:9" s="22" customFormat="1" ht="18" customHeight="1">
       <c r="B9" s="34"/>
       <c r="C9" s="35" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="D9" s="31" t="s">
         <v>28</v>
@@ -19739,10 +19646,10 @@
       <c r="I12" s="28"/>
     </row>
     <row r="13" spans="2:9" s="22" customFormat="1" ht="28" customHeight="1">
-      <c r="B13" s="161" t="s">
+      <c r="B13" s="293" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="162"/>
+      <c r="C13" s="294"/>
       <c r="D13" s="37"/>
       <c r="E13" s="38"/>
       <c r="F13" s="39" t="s">
@@ -19756,14 +19663,14 @@
         <v>0</v>
       </c>
       <c r="I13" s="41" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="2:9" s="22" customFormat="1" ht="28" customHeight="1">
-      <c r="B14" s="161" t="s">
+      <c r="B14" s="293" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="162"/>
+      <c r="C14" s="294"/>
       <c r="D14" s="37"/>
       <c r="E14" s="38"/>
       <c r="F14" s="39" t="s">
@@ -19777,14 +19684,14 @@
         <v>0</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="2:9" s="22" customFormat="1" ht="28" customHeight="1">
-      <c r="B15" s="161" t="s">
+      <c r="B15" s="293" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="162"/>
+      <c r="C15" s="294"/>
       <c r="D15" s="43"/>
       <c r="E15" s="44"/>
       <c r="F15" s="45"/>
@@ -19868,7 +19775,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="56" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="2:13" s="22" customFormat="1" ht="18" customHeight="1">
@@ -19889,7 +19796,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="56" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="2:13" s="22" customFormat="1" ht="18" customHeight="1">
@@ -19914,10 +19821,10 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="2:13" s="22" customFormat="1" ht="28" customHeight="1">
-      <c r="B22" s="161" t="s">
+      <c r="B22" s="293" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="162"/>
+      <c r="C22" s="294"/>
       <c r="D22" s="37"/>
       <c r="E22" s="70"/>
       <c r="F22" s="39"/>
@@ -19931,16 +19838,16 @@
       </c>
     </row>
     <row r="23" spans="2:13" s="22" customFormat="1" ht="28" customHeight="1">
-      <c r="B23" s="163" t="s">
-        <v>198</v>
-      </c>
-      <c r="C23" s="164"/>
-      <c r="D23" s="154" t="s">
+      <c r="B23" s="295" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" s="296"/>
+      <c r="D23" s="286" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="154"/>
-      <c r="F23" s="154"/>
-      <c r="G23" s="154"/>
+      <c r="E23" s="286"/>
+      <c r="F23" s="286"/>
+      <c r="G23" s="286"/>
       <c r="H23" s="73">
         <f>(SUM(H8,H13,H14,H15,H22))</f>
         <v>796056</v>
@@ -19948,14 +19855,14 @@
       <c r="I23" s="74"/>
     </row>
     <row r="24" spans="2:13" s="22" customFormat="1" ht="18" customHeight="1">
-      <c r="B24" s="153" t="s">
+      <c r="B24" s="285" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="154"/>
-      <c r="D24" s="154"/>
-      <c r="E24" s="154"/>
-      <c r="F24" s="154"/>
-      <c r="G24" s="154"/>
+      <c r="C24" s="286"/>
+      <c r="D24" s="286"/>
+      <c r="E24" s="286"/>
+      <c r="F24" s="286"/>
+      <c r="G24" s="286"/>
       <c r="H24" s="73">
         <f>H23-H25</f>
         <v>96056</v>
@@ -19963,42 +19870,42 @@
       <c r="I24" s="75"/>
     </row>
     <row r="25" spans="2:13" s="22" customFormat="1" ht="18" customHeight="1">
-      <c r="B25" s="160" t="s">
+      <c r="B25" s="292" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="157"/>
-      <c r="D25" s="157"/>
-      <c r="E25" s="157"/>
-      <c r="F25" s="157"/>
-      <c r="G25" s="157"/>
+      <c r="C25" s="289"/>
+      <c r="D25" s="289"/>
+      <c r="E25" s="289"/>
+      <c r="F25" s="289"/>
+      <c r="G25" s="289"/>
       <c r="H25" s="76">
         <v>700000</v>
       </c>
       <c r="I25" s="77"/>
     </row>
     <row r="26" spans="2:13" s="22" customFormat="1" ht="18" customHeight="1">
-      <c r="B26" s="153" t="s">
+      <c r="B26" s="285" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="154"/>
-      <c r="D26" s="154"/>
-      <c r="E26" s="154"/>
-      <c r="F26" s="154"/>
-      <c r="G26" s="154"/>
+      <c r="C26" s="286"/>
+      <c r="D26" s="286"/>
+      <c r="E26" s="286"/>
+      <c r="F26" s="286"/>
+      <c r="G26" s="286"/>
       <c r="H26" s="78" t="s">
         <v>52</v>
       </c>
       <c r="I26" s="75"/>
     </row>
     <row r="27" spans="2:13" s="22" customFormat="1" ht="27.75" customHeight="1">
-      <c r="B27" s="155" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="156"/>
-      <c r="D27" s="157"/>
-      <c r="E27" s="157"/>
-      <c r="F27" s="157"/>
-      <c r="G27" s="157"/>
+      <c r="B27" s="287" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="288"/>
+      <c r="D27" s="289"/>
+      <c r="E27" s="289"/>
+      <c r="F27" s="289"/>
+      <c r="G27" s="289"/>
       <c r="H27" s="105">
         <f>H25</f>
         <v>700000</v>
@@ -20023,10 +19930,10 @@
       <c r="I28" s="110"/>
     </row>
     <row r="29" spans="2:13" s="22" customFormat="1" ht="16" customHeight="1">
-      <c r="B29" s="158" t="s">
-        <v>200</v>
-      </c>
-      <c r="C29" s="159"/>
+      <c r="B29" s="290" t="s">
+        <v>183</v>
+      </c>
+      <c r="C29" s="291"/>
       <c r="D29" s="111"/>
       <c r="E29" s="111"/>
       <c r="F29" s="111"/>
@@ -20035,105 +19942,105 @@
       <c r="I29" s="113"/>
     </row>
     <row r="30" spans="2:13" s="22" customFormat="1" ht="32.25" customHeight="1">
-      <c r="B30" s="138" t="s">
-        <v>201</v>
-      </c>
-      <c r="C30" s="139"/>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="139"/>
-      <c r="H30" s="139"/>
-      <c r="I30" s="140"/>
+      <c r="B30" s="270" t="s">
+        <v>184</v>
+      </c>
+      <c r="C30" s="271"/>
+      <c r="D30" s="271"/>
+      <c r="E30" s="271"/>
+      <c r="F30" s="271"/>
+      <c r="G30" s="271"/>
+      <c r="H30" s="271"/>
+      <c r="I30" s="272"/>
     </row>
     <row r="31" spans="2:13" s="22" customFormat="1" ht="32" customHeight="1">
-      <c r="B31" s="138" t="s">
-        <v>202</v>
-      </c>
-      <c r="C31" s="139"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="139"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="140"/>
+      <c r="B31" s="270" t="s">
+        <v>185</v>
+      </c>
+      <c r="C31" s="271"/>
+      <c r="D31" s="271"/>
+      <c r="E31" s="271"/>
+      <c r="F31" s="271"/>
+      <c r="G31" s="271"/>
+      <c r="H31" s="271"/>
+      <c r="I31" s="272"/>
     </row>
     <row r="32" spans="2:13" s="22" customFormat="1" ht="16" customHeight="1">
-      <c r="B32" s="141" t="s">
-        <v>203</v>
-      </c>
-      <c r="C32" s="142"/>
-      <c r="D32" s="142"/>
-      <c r="E32" s="142"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="142"/>
-      <c r="I32" s="143"/>
+      <c r="B32" s="273" t="s">
+        <v>186</v>
+      </c>
+      <c r="C32" s="274"/>
+      <c r="D32" s="274"/>
+      <c r="E32" s="274"/>
+      <c r="F32" s="274"/>
+      <c r="G32" s="274"/>
+      <c r="H32" s="274"/>
+      <c r="I32" s="275"/>
     </row>
     <row r="33" spans="2:9" s="80" customFormat="1" ht="23" customHeight="1">
-      <c r="B33" s="144"/>
-      <c r="C33" s="145"/>
-      <c r="D33" s="150" t="s">
+      <c r="B33" s="276"/>
+      <c r="C33" s="277"/>
+      <c r="D33" s="282" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="150"/>
-      <c r="F33" s="150"/>
-      <c r="G33" s="150"/>
-      <c r="H33" s="150"/>
+      <c r="E33" s="282"/>
+      <c r="F33" s="282"/>
+      <c r="G33" s="282"/>
+      <c r="H33" s="282"/>
       <c r="I33" s="79"/>
     </row>
     <row r="34" spans="2:9" s="80" customFormat="1" ht="23" customHeight="1">
-      <c r="B34" s="146"/>
-      <c r="C34" s="147"/>
-      <c r="D34" s="151" t="s">
+      <c r="B34" s="278"/>
+      <c r="C34" s="279"/>
+      <c r="D34" s="283" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="151"/>
-      <c r="F34" s="151"/>
-      <c r="G34" s="151"/>
-      <c r="H34" s="151"/>
+      <c r="E34" s="283"/>
+      <c r="F34" s="283"/>
+      <c r="G34" s="283"/>
+      <c r="H34" s="283"/>
       <c r="I34" s="81" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="35" spans="2:9" s="80" customFormat="1" ht="23" customHeight="1">
-      <c r="B35" s="146"/>
-      <c r="C35" s="147"/>
-      <c r="D35" s="151" t="s">
+      <c r="B35" s="278"/>
+      <c r="C35" s="279"/>
+      <c r="D35" s="283" t="s">
         <v>57</v>
       </c>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="151"/>
-      <c r="H35" s="151"/>
+      <c r="E35" s="283"/>
+      <c r="F35" s="283"/>
+      <c r="G35" s="283"/>
+      <c r="H35" s="283"/>
       <c r="I35" s="81" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="36" spans="2:9" s="80" customFormat="1" ht="23" customHeight="1">
-      <c r="B36" s="146"/>
-      <c r="C36" s="147"/>
-      <c r="D36" s="151" t="s">
+      <c r="B36" s="278"/>
+      <c r="C36" s="279"/>
+      <c r="D36" s="283" t="s">
         <v>59</v>
       </c>
-      <c r="E36" s="151"/>
-      <c r="F36" s="151"/>
-      <c r="G36" s="151"/>
-      <c r="H36" s="151"/>
+      <c r="E36" s="283"/>
+      <c r="F36" s="283"/>
+      <c r="G36" s="283"/>
+      <c r="H36" s="283"/>
       <c r="I36" s="81" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="37" spans="2:9" s="80" customFormat="1" ht="23" customHeight="1">
-      <c r="B37" s="148"/>
-      <c r="C37" s="149"/>
-      <c r="D37" s="152" t="s">
+      <c r="B37" s="280"/>
+      <c r="C37" s="281"/>
+      <c r="D37" s="284" t="s">
         <v>61</v>
       </c>
-      <c r="E37" s="152"/>
-      <c r="F37" s="152"/>
-      <c r="G37" s="152"/>
-      <c r="H37" s="152"/>
+      <c r="E37" s="284"/>
+      <c r="F37" s="284"/>
+      <c r="G37" s="284"/>
+      <c r="H37" s="284"/>
       <c r="I37" s="82" t="s">
         <v>62</v>
       </c>
@@ -20143,9 +20050,9 @@
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:H3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D3:I3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="B6:I6"/>
@@ -20482,99 +20389,99 @@
       <c r="F6" s="86"/>
     </row>
     <row r="7" spans="5:24" ht="4" customHeight="1">
-      <c r="E7" s="300" t="s">
+      <c r="E7" s="233" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="301"/>
-      <c r="G7" s="301"/>
-      <c r="H7" s="301"/>
-      <c r="I7" s="301"/>
-      <c r="J7" s="301"/>
-      <c r="K7" s="301"/>
-      <c r="L7" s="301"/>
-      <c r="M7" s="301"/>
-      <c r="N7" s="301"/>
-      <c r="O7" s="301"/>
-      <c r="P7" s="301"/>
-      <c r="Q7" s="301"/>
-      <c r="R7" s="301"/>
-      <c r="S7" s="301"/>
-      <c r="T7" s="301"/>
-      <c r="U7" s="301"/>
-      <c r="V7" s="301"/>
-      <c r="W7" s="301"/>
-      <c r="X7" s="301"/>
+      <c r="F7" s="234"/>
+      <c r="G7" s="234"/>
+      <c r="H7" s="234"/>
+      <c r="I7" s="234"/>
+      <c r="J7" s="234"/>
+      <c r="K7" s="234"/>
+      <c r="L7" s="234"/>
+      <c r="M7" s="234"/>
+      <c r="N7" s="234"/>
+      <c r="O7" s="234"/>
+      <c r="P7" s="234"/>
+      <c r="Q7" s="234"/>
+      <c r="R7" s="234"/>
+      <c r="S7" s="234"/>
+      <c r="T7" s="234"/>
+      <c r="U7" s="234"/>
+      <c r="V7" s="234"/>
+      <c r="W7" s="234"/>
+      <c r="X7" s="234"/>
     </row>
     <row r="8" spans="5:24" ht="66" customHeight="1">
-      <c r="E8" s="302" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="302"/>
-      <c r="G8" s="302"/>
-      <c r="H8" s="302"/>
-      <c r="I8" s="302"/>
-      <c r="J8" s="302"/>
-      <c r="K8" s="302"/>
-      <c r="L8" s="302"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="302"/>
-      <c r="O8" s="302"/>
-      <c r="P8" s="302"/>
-      <c r="Q8" s="302"/>
-      <c r="R8" s="302"/>
-      <c r="S8" s="302"/>
-      <c r="T8" s="302"/>
-      <c r="U8" s="302"/>
-      <c r="V8" s="302"/>
-      <c r="W8" s="302"/>
-      <c r="X8" s="302"/>
+      <c r="E8" s="235" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="235"/>
+      <c r="G8" s="235"/>
+      <c r="H8" s="235"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="235"/>
+      <c r="K8" s="235"/>
+      <c r="L8" s="235"/>
+      <c r="M8" s="235"/>
+      <c r="N8" s="235"/>
+      <c r="O8" s="235"/>
+      <c r="P8" s="235"/>
+      <c r="Q8" s="235"/>
+      <c r="R8" s="235"/>
+      <c r="S8" s="235"/>
+      <c r="T8" s="235"/>
+      <c r="U8" s="235"/>
+      <c r="V8" s="235"/>
+      <c r="W8" s="235"/>
+      <c r="X8" s="235"/>
     </row>
     <row r="9" spans="5:24" ht="44" customHeight="1">
-      <c r="E9" s="303" t="str">
-        <f>갑지!R20</f>
+      <c r="E9" s="236" t="str">
+        <f>갑지!P20</f>
         <v>래미안길음뉴타운9단지아파트</v>
       </c>
-      <c r="F9" s="303"/>
-      <c r="G9" s="303"/>
-      <c r="H9" s="303"/>
-      <c r="I9" s="303"/>
-      <c r="J9" s="303"/>
-      <c r="K9" s="303"/>
-      <c r="L9" s="303"/>
-      <c r="M9" s="303"/>
-      <c r="N9" s="303"/>
-      <c r="O9" s="303"/>
-      <c r="P9" s="303"/>
-      <c r="Q9" s="303"/>
-      <c r="R9" s="303"/>
-      <c r="S9" s="303"/>
-      <c r="T9" s="303"/>
-      <c r="U9" s="303"/>
-      <c r="V9" s="303"/>
-      <c r="W9" s="303"/>
-      <c r="X9" s="303"/>
+      <c r="F9" s="236"/>
+      <c r="G9" s="236"/>
+      <c r="H9" s="236"/>
+      <c r="I9" s="236"/>
+      <c r="J9" s="236"/>
+      <c r="K9" s="236"/>
+      <c r="L9" s="236"/>
+      <c r="M9" s="236"/>
+      <c r="N9" s="236"/>
+      <c r="O9" s="236"/>
+      <c r="P9" s="236"/>
+      <c r="Q9" s="236"/>
+      <c r="R9" s="236"/>
+      <c r="S9" s="236"/>
+      <c r="T9" s="236"/>
+      <c r="U9" s="236"/>
+      <c r="V9" s="236"/>
+      <c r="W9" s="236"/>
+      <c r="X9" s="236"/>
     </row>
     <row r="10" spans="5:24" ht="4" customHeight="1">
-      <c r="E10" s="304"/>
-      <c r="F10" s="305"/>
-      <c r="G10" s="305"/>
-      <c r="H10" s="305"/>
-      <c r="I10" s="305"/>
-      <c r="J10" s="305"/>
-      <c r="K10" s="305"/>
-      <c r="L10" s="305"/>
-      <c r="M10" s="305"/>
-      <c r="N10" s="305"/>
-      <c r="O10" s="305"/>
-      <c r="P10" s="305"/>
-      <c r="Q10" s="305"/>
-      <c r="R10" s="305"/>
-      <c r="S10" s="305"/>
-      <c r="T10" s="305"/>
-      <c r="U10" s="305"/>
-      <c r="V10" s="305"/>
-      <c r="W10" s="305"/>
-      <c r="X10" s="305"/>
+      <c r="E10" s="237"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="238"/>
+      <c r="H10" s="238"/>
+      <c r="I10" s="238"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="238"/>
+      <c r="L10" s="238"/>
+      <c r="M10" s="238"/>
+      <c r="N10" s="238"/>
+      <c r="O10" s="238"/>
+      <c r="P10" s="238"/>
+      <c r="Q10" s="238"/>
+      <c r="R10" s="238"/>
+      <c r="S10" s="238"/>
+      <c r="T10" s="238"/>
+      <c r="U10" s="238"/>
+      <c r="V10" s="238"/>
+      <c r="W10" s="238"/>
+      <c r="X10" s="238"/>
     </row>
     <row r="11" spans="5:24" ht="40" customHeight="1">
       <c r="E11" s="88"/>
@@ -20597,29 +20504,29 @@
       <c r="F15" s="88"/>
     </row>
     <row r="16" spans="5:24" ht="24">
-      <c r="E16" s="306" t="str">
+      <c r="E16" s="239" t="str">
         <f>갑지!J10</f>
         <v xml:space="preserve">2026년 연간 </v>
       </c>
-      <c r="F16" s="306"/>
-      <c r="G16" s="306"/>
-      <c r="H16" s="306"/>
-      <c r="I16" s="306"/>
-      <c r="J16" s="306"/>
-      <c r="K16" s="306"/>
-      <c r="L16" s="306"/>
-      <c r="M16" s="306"/>
-      <c r="N16" s="306"/>
-      <c r="O16" s="306"/>
-      <c r="P16" s="306"/>
-      <c r="Q16" s="306"/>
-      <c r="R16" s="306"/>
-      <c r="S16" s="306"/>
-      <c r="T16" s="306"/>
-      <c r="U16" s="306"/>
-      <c r="V16" s="306"/>
-      <c r="W16" s="306"/>
-      <c r="X16" s="306"/>
+      <c r="F16" s="239"/>
+      <c r="G16" s="239"/>
+      <c r="H16" s="239"/>
+      <c r="I16" s="239"/>
+      <c r="J16" s="239"/>
+      <c r="K16" s="239"/>
+      <c r="L16" s="239"/>
+      <c r="M16" s="239"/>
+      <c r="N16" s="239"/>
+      <c r="O16" s="239"/>
+      <c r="P16" s="239"/>
+      <c r="Q16" s="239"/>
+      <c r="R16" s="239"/>
+      <c r="S16" s="239"/>
+      <c r="T16" s="239"/>
+      <c r="U16" s="239"/>
+      <c r="V16" s="239"/>
+      <c r="W16" s="239"/>
+      <c r="X16" s="239"/>
     </row>
     <row r="17" spans="5:24" ht="40" customHeight="1">
       <c r="E17" s="88"/>
@@ -20644,61 +20551,61 @@
     <row r="22" spans="5:24" ht="53.25" customHeight="1">
       <c r="G22" s="89"/>
       <c r="H22" s="89"/>
-      <c r="L22" s="307" t="s">
+      <c r="L22" s="240" t="s">
         <v>65</v>
       </c>
-      <c r="M22" s="307"/>
-      <c r="N22" s="307"/>
-      <c r="O22" s="307"/>
-      <c r="P22" s="307"/>
-      <c r="Q22" s="307"/>
-      <c r="R22" s="307"/>
-      <c r="S22" s="307"/>
-      <c r="T22" s="307"/>
-      <c r="U22" s="307"/>
-      <c r="V22" s="307"/>
-      <c r="W22" s="307"/>
-      <c r="X22" s="307"/>
+      <c r="M22" s="240"/>
+      <c r="N22" s="240"/>
+      <c r="O22" s="240"/>
+      <c r="P22" s="240"/>
+      <c r="Q22" s="240"/>
+      <c r="R22" s="240"/>
+      <c r="S22" s="240"/>
+      <c r="T22" s="240"/>
+      <c r="U22" s="240"/>
+      <c r="V22" s="240"/>
+      <c r="W22" s="240"/>
+      <c r="X22" s="240"/>
     </row>
     <row r="23" spans="5:24" ht="24" customHeight="1">
       <c r="G23" s="90"/>
       <c r="H23" s="90"/>
       <c r="I23" s="90"/>
-      <c r="L23" s="217" t="s">
+      <c r="L23" s="139" t="s">
         <v>66</v>
       </c>
-      <c r="M23" s="217"/>
-      <c r="N23" s="217"/>
-      <c r="O23" s="217"/>
-      <c r="P23" s="217"/>
-      <c r="Q23" s="217"/>
-      <c r="R23" s="217"/>
-      <c r="S23" s="217"/>
-      <c r="T23" s="217"/>
-      <c r="U23" s="217"/>
-      <c r="V23" s="217"/>
-      <c r="W23" s="217"/>
-      <c r="X23" s="217"/>
+      <c r="M23" s="139"/>
+      <c r="N23" s="139"/>
+      <c r="O23" s="139"/>
+      <c r="P23" s="139"/>
+      <c r="Q23" s="139"/>
+      <c r="R23" s="139"/>
+      <c r="S23" s="139"/>
+      <c r="T23" s="139"/>
+      <c r="U23" s="139"/>
+      <c r="V23" s="139"/>
+      <c r="W23" s="139"/>
+      <c r="X23" s="139"/>
     </row>
     <row r="24" spans="5:24" ht="24" customHeight="1">
       <c r="G24" s="90"/>
       <c r="H24" s="90"/>
       <c r="I24" s="90"/>
-      <c r="L24" s="217" t="s">
+      <c r="L24" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="M24" s="217"/>
-      <c r="N24" s="217"/>
-      <c r="O24" s="217"/>
-      <c r="P24" s="217"/>
-      <c r="Q24" s="217"/>
-      <c r="R24" s="217"/>
-      <c r="S24" s="217"/>
-      <c r="T24" s="217"/>
-      <c r="U24" s="217"/>
-      <c r="V24" s="217"/>
-      <c r="W24" s="217"/>
-      <c r="X24" s="217"/>
+      <c r="M24" s="139"/>
+      <c r="N24" s="139"/>
+      <c r="O24" s="139"/>
+      <c r="P24" s="139"/>
+      <c r="Q24" s="139"/>
+      <c r="R24" s="139"/>
+      <c r="S24" s="139"/>
+      <c r="T24" s="139"/>
+      <c r="U24" s="139"/>
+      <c r="V24" s="139"/>
+      <c r="W24" s="139"/>
+      <c r="X24" s="139"/>
     </row>
     <row r="25" spans="5:24" ht="24" customHeight="1">
       <c r="G25" s="90"/>
@@ -20736,517 +20643,510 @@
       <c r="X26" s="91"/>
     </row>
     <row r="27" spans="5:24" ht="43.5" customHeight="1">
-      <c r="E27" s="308" t="s">
-        <v>130</v>
-      </c>
-      <c r="F27" s="309"/>
-      <c r="G27" s="309"/>
-      <c r="H27" s="309"/>
-      <c r="I27" s="309"/>
-      <c r="J27" s="309"/>
-      <c r="K27" s="309"/>
-      <c r="L27" s="309"/>
-      <c r="M27" s="309"/>
-      <c r="N27" s="309"/>
-      <c r="O27" s="309"/>
-      <c r="P27" s="309"/>
-      <c r="Q27" s="309"/>
-      <c r="R27" s="309"/>
-      <c r="S27" s="309"/>
-      <c r="T27" s="309"/>
-      <c r="U27" s="309"/>
-      <c r="V27" s="309"/>
-      <c r="W27" s="309"/>
-      <c r="X27" s="310"/>
+      <c r="E27" s="241" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" s="242"/>
+      <c r="G27" s="242"/>
+      <c r="H27" s="242"/>
+      <c r="I27" s="242"/>
+      <c r="J27" s="242"/>
+      <c r="K27" s="242"/>
+      <c r="L27" s="242"/>
+      <c r="M27" s="242"/>
+      <c r="N27" s="242"/>
+      <c r="O27" s="242"/>
+      <c r="P27" s="242"/>
+      <c r="Q27" s="242"/>
+      <c r="R27" s="242"/>
+      <c r="S27" s="242"/>
+      <c r="T27" s="242"/>
+      <c r="U27" s="242"/>
+      <c r="V27" s="242"/>
+      <c r="W27" s="242"/>
+      <c r="X27" s="243"/>
     </row>
     <row r="28" spans="5:24" ht="25" customHeight="1">
-      <c r="E28" s="290" t="s">
+      <c r="E28" s="207" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="291"/>
-      <c r="G28" s="294" t="s">
+      <c r="F28" s="208"/>
+      <c r="G28" s="211" t="s">
         <v>69</v>
       </c>
-      <c r="H28" s="294"/>
-      <c r="I28" s="294"/>
-      <c r="J28" s="295" t="str">
+      <c r="H28" s="211"/>
+      <c r="I28" s="211"/>
+      <c r="J28" s="212" t="str">
         <f>E9</f>
         <v>래미안길음뉴타운9단지아파트</v>
       </c>
-      <c r="K28" s="295"/>
-      <c r="L28" s="295"/>
-      <c r="M28" s="295"/>
-      <c r="N28" s="295"/>
-      <c r="O28" s="295"/>
-      <c r="P28" s="295"/>
-      <c r="Q28" s="295"/>
-      <c r="R28" s="295"/>
-      <c r="S28" s="295"/>
-      <c r="T28" s="295"/>
-      <c r="U28" s="295"/>
-      <c r="V28" s="295"/>
-      <c r="W28" s="295"/>
-      <c r="X28" s="296"/>
+      <c r="K28" s="212"/>
+      <c r="L28" s="212"/>
+      <c r="M28" s="212"/>
+      <c r="N28" s="212"/>
+      <c r="O28" s="212"/>
+      <c r="P28" s="212"/>
+      <c r="Q28" s="212"/>
+      <c r="R28" s="212"/>
+      <c r="S28" s="212"/>
+      <c r="T28" s="212"/>
+      <c r="U28" s="212"/>
+      <c r="V28" s="212"/>
+      <c r="W28" s="212"/>
+      <c r="X28" s="213"/>
     </row>
     <row r="29" spans="5:24" ht="25" customHeight="1">
-      <c r="E29" s="292"/>
-      <c r="F29" s="293"/>
-      <c r="G29" s="265" t="s">
+      <c r="E29" s="209"/>
+      <c r="F29" s="210"/>
+      <c r="G29" s="182" t="s">
         <v>70</v>
       </c>
-      <c r="H29" s="265"/>
-      <c r="I29" s="265"/>
-      <c r="J29" s="297" t="s">
+      <c r="H29" s="182"/>
+      <c r="I29" s="182"/>
+      <c r="J29" s="214" t="s">
+        <v>150</v>
+      </c>
+      <c r="K29" s="214"/>
+      <c r="L29" s="214"/>
+      <c r="M29" s="214"/>
+      <c r="N29" s="214"/>
+      <c r="O29" s="214"/>
+      <c r="P29" s="214"/>
+      <c r="Q29" s="214"/>
+      <c r="R29" s="214"/>
+      <c r="S29" s="214"/>
+      <c r="T29" s="214"/>
+      <c r="U29" s="214"/>
+      <c r="V29" s="214"/>
+      <c r="W29" s="214"/>
+      <c r="X29" s="215"/>
+    </row>
+    <row r="30" spans="5:24" ht="25" customHeight="1">
+      <c r="E30" s="209"/>
+      <c r="F30" s="210"/>
+      <c r="G30" s="182"/>
+      <c r="H30" s="182"/>
+      <c r="I30" s="182"/>
+      <c r="J30" s="214" t="s">
+        <v>151</v>
+      </c>
+      <c r="K30" s="214"/>
+      <c r="L30" s="214"/>
+      <c r="M30" s="214"/>
+      <c r="N30" s="214"/>
+      <c r="O30" s="214"/>
+      <c r="P30" s="214"/>
+      <c r="Q30" s="214"/>
+      <c r="R30" s="214"/>
+      <c r="S30" s="214"/>
+      <c r="T30" s="214"/>
+      <c r="U30" s="214"/>
+      <c r="V30" s="214"/>
+      <c r="W30" s="214"/>
+      <c r="X30" s="215"/>
+    </row>
+    <row r="31" spans="5:24" ht="25" customHeight="1">
+      <c r="E31" s="209"/>
+      <c r="F31" s="210"/>
+      <c r="G31" s="182"/>
+      <c r="H31" s="182"/>
+      <c r="I31" s="182"/>
+      <c r="J31" s="214" t="s">
         <v>165</v>
       </c>
-      <c r="K29" s="297"/>
-      <c r="L29" s="297"/>
-      <c r="M29" s="297"/>
-      <c r="N29" s="297"/>
-      <c r="O29" s="297"/>
-      <c r="P29" s="297"/>
-      <c r="Q29" s="297"/>
-      <c r="R29" s="297"/>
-      <c r="S29" s="297"/>
-      <c r="T29" s="297"/>
-      <c r="U29" s="297"/>
-      <c r="V29" s="297"/>
-      <c r="W29" s="297"/>
-      <c r="X29" s="298"/>
-    </row>
-    <row r="30" spans="5:24" ht="25" customHeight="1">
-      <c r="E30" s="292"/>
-      <c r="F30" s="293"/>
-      <c r="G30" s="265"/>
-      <c r="H30" s="265"/>
-      <c r="I30" s="265"/>
-      <c r="J30" s="297" t="s">
-        <v>166</v>
-      </c>
-      <c r="K30" s="297"/>
-      <c r="L30" s="297"/>
-      <c r="M30" s="297"/>
-      <c r="N30" s="297"/>
-      <c r="O30" s="297"/>
-      <c r="P30" s="297"/>
-      <c r="Q30" s="297"/>
-      <c r="R30" s="297"/>
-      <c r="S30" s="297"/>
-      <c r="T30" s="297"/>
-      <c r="U30" s="297"/>
-      <c r="V30" s="297"/>
-      <c r="W30" s="297"/>
-      <c r="X30" s="298"/>
-    </row>
-    <row r="31" spans="5:24" ht="25" customHeight="1">
-      <c r="E31" s="292"/>
-      <c r="F31" s="293"/>
-      <c r="G31" s="265"/>
-      <c r="H31" s="265"/>
-      <c r="I31" s="265"/>
-      <c r="J31" s="297" t="s">
-        <v>181</v>
-      </c>
-      <c r="K31" s="297"/>
-      <c r="L31" s="297"/>
-      <c r="M31" s="297"/>
-      <c r="N31" s="297"/>
-      <c r="O31" s="297"/>
-      <c r="P31" s="297"/>
-      <c r="Q31" s="297"/>
-      <c r="R31" s="297"/>
-      <c r="S31" s="297"/>
-      <c r="T31" s="297"/>
-      <c r="U31" s="297"/>
-      <c r="V31" s="297"/>
-      <c r="W31" s="297"/>
-      <c r="X31" s="298"/>
+      <c r="K31" s="214"/>
+      <c r="L31" s="214"/>
+      <c r="M31" s="214"/>
+      <c r="N31" s="214"/>
+      <c r="O31" s="214"/>
+      <c r="P31" s="214"/>
+      <c r="Q31" s="214"/>
+      <c r="R31" s="214"/>
+      <c r="S31" s="214"/>
+      <c r="T31" s="214"/>
+      <c r="U31" s="214"/>
+      <c r="V31" s="214"/>
+      <c r="W31" s="214"/>
+      <c r="X31" s="215"/>
     </row>
     <row r="32" spans="5:24" ht="25" customHeight="1">
-      <c r="E32" s="292"/>
-      <c r="F32" s="293"/>
-      <c r="G32" s="265"/>
-      <c r="H32" s="265"/>
-      <c r="I32" s="265"/>
-      <c r="J32" s="297" t="s">
-        <v>167</v>
-      </c>
-      <c r="K32" s="297"/>
-      <c r="L32" s="297"/>
-      <c r="M32" s="297"/>
-      <c r="N32" s="297"/>
-      <c r="O32" s="297"/>
-      <c r="P32" s="297"/>
-      <c r="Q32" s="297"/>
-      <c r="R32" s="297"/>
-      <c r="S32" s="297"/>
-      <c r="T32" s="297"/>
-      <c r="U32" s="297"/>
-      <c r="V32" s="297"/>
-      <c r="W32" s="297"/>
-      <c r="X32" s="298"/>
+      <c r="E32" s="209"/>
+      <c r="F32" s="210"/>
+      <c r="G32" s="182"/>
+      <c r="H32" s="182"/>
+      <c r="I32" s="182"/>
+      <c r="J32" s="214" t="s">
+        <v>152</v>
+      </c>
+      <c r="K32" s="214"/>
+      <c r="L32" s="214"/>
+      <c r="M32" s="214"/>
+      <c r="N32" s="214"/>
+      <c r="O32" s="214"/>
+      <c r="P32" s="214"/>
+      <c r="Q32" s="214"/>
+      <c r="R32" s="214"/>
+      <c r="S32" s="214"/>
+      <c r="T32" s="214"/>
+      <c r="U32" s="214"/>
+      <c r="V32" s="214"/>
+      <c r="W32" s="214"/>
+      <c r="X32" s="215"/>
     </row>
     <row r="33" spans="5:24" ht="25" customHeight="1">
-      <c r="E33" s="292"/>
-      <c r="F33" s="293"/>
-      <c r="G33" s="265"/>
-      <c r="H33" s="265"/>
-      <c r="I33" s="265"/>
-      <c r="J33" s="311" t="s">
-        <v>168</v>
-      </c>
-      <c r="K33" s="311"/>
-      <c r="L33" s="311"/>
-      <c r="M33" s="311"/>
-      <c r="N33" s="311"/>
-      <c r="O33" s="311"/>
-      <c r="P33" s="311"/>
-      <c r="Q33" s="311"/>
-      <c r="R33" s="311"/>
-      <c r="S33" s="311"/>
-      <c r="T33" s="311"/>
-      <c r="U33" s="311"/>
-      <c r="V33" s="311"/>
-      <c r="W33" s="311"/>
-      <c r="X33" s="312"/>
+      <c r="E33" s="209"/>
+      <c r="F33" s="210"/>
+      <c r="G33" s="182"/>
+      <c r="H33" s="182"/>
+      <c r="I33" s="182"/>
+      <c r="J33" s="217" t="s">
+        <v>153</v>
+      </c>
+      <c r="K33" s="217"/>
+      <c r="L33" s="217"/>
+      <c r="M33" s="217"/>
+      <c r="N33" s="217"/>
+      <c r="O33" s="217"/>
+      <c r="P33" s="217"/>
+      <c r="Q33" s="217"/>
+      <c r="R33" s="217"/>
+      <c r="S33" s="217"/>
+      <c r="T33" s="217"/>
+      <c r="U33" s="217"/>
+      <c r="V33" s="217"/>
+      <c r="W33" s="217"/>
+      <c r="X33" s="218"/>
     </row>
     <row r="34" spans="5:24" ht="25" customHeight="1">
-      <c r="E34" s="254" t="s">
+      <c r="E34" s="175" t="s">
         <v>71</v>
       </c>
-      <c r="F34" s="255"/>
-      <c r="G34" s="260" t="s">
+      <c r="F34" s="176"/>
+      <c r="G34" s="181" t="s">
         <v>72</v>
       </c>
-      <c r="H34" s="260"/>
-      <c r="I34" s="260"/>
-      <c r="J34" s="261" t="str">
-        <f>J28</f>
-        <v>래미안길음뉴타운9단지아파트</v>
-      </c>
-      <c r="K34" s="262"/>
-      <c r="L34" s="262"/>
-      <c r="M34" s="262"/>
-      <c r="N34" s="262"/>
-      <c r="O34" s="262"/>
-      <c r="P34" s="262"/>
-      <c r="Q34" s="262"/>
-      <c r="R34" s="263" t="s">
-        <v>139</v>
-      </c>
-      <c r="S34" s="263"/>
-      <c r="T34" s="263"/>
-      <c r="U34" s="263"/>
-      <c r="V34" s="263"/>
-      <c r="W34" s="263"/>
-      <c r="X34" s="264"/>
+      <c r="H34" s="181"/>
+      <c r="I34" s="181"/>
+      <c r="J34" s="135" t="str">
+        <f>J28&amp;" 점검프로그램 사용"</f>
+        <v>래미안길음뉴타운9단지아파트 점검프로그램 사용</v>
+      </c>
+      <c r="K34" s="136"/>
+      <c r="L34" s="136"/>
+      <c r="M34" s="136"/>
+      <c r="N34" s="136"/>
+      <c r="O34" s="136"/>
+      <c r="P34" s="136"/>
+      <c r="Q34" s="136"/>
+      <c r="R34" s="136"/>
+      <c r="S34" s="136"/>
+      <c r="T34" s="136"/>
+      <c r="U34" s="136"/>
+      <c r="V34" s="136"/>
+      <c r="W34" s="136"/>
+      <c r="X34" s="137"/>
     </row>
     <row r="35" spans="5:24" ht="25" customHeight="1">
-      <c r="E35" s="256"/>
-      <c r="F35" s="257"/>
-      <c r="G35" s="265" t="s">
+      <c r="E35" s="177"/>
+      <c r="F35" s="178"/>
+      <c r="G35" s="182" t="s">
         <v>73</v>
       </c>
-      <c r="H35" s="265"/>
-      <c r="I35" s="265"/>
-      <c r="J35" s="278" t="str">
+      <c r="H35" s="182"/>
+      <c r="I35" s="182"/>
+      <c r="J35" s="227" t="str">
         <f>대가산출!D4</f>
         <v>일금일백사십만원정 (₩1,400,000) - VAT별도</v>
       </c>
-      <c r="K35" s="279"/>
-      <c r="L35" s="279"/>
-      <c r="M35" s="279"/>
-      <c r="N35" s="279"/>
-      <c r="O35" s="279"/>
-      <c r="P35" s="279"/>
-      <c r="Q35" s="279"/>
-      <c r="R35" s="279"/>
-      <c r="S35" s="279"/>
-      <c r="T35" s="279"/>
-      <c r="U35" s="279"/>
-      <c r="V35" s="279"/>
-      <c r="W35" s="279"/>
-      <c r="X35" s="280"/>
+      <c r="K35" s="228"/>
+      <c r="L35" s="228"/>
+      <c r="M35" s="228"/>
+      <c r="N35" s="228"/>
+      <c r="O35" s="228"/>
+      <c r="P35" s="228"/>
+      <c r="Q35" s="228"/>
+      <c r="R35" s="228"/>
+      <c r="S35" s="228"/>
+      <c r="T35" s="228"/>
+      <c r="U35" s="228"/>
+      <c r="V35" s="228"/>
+      <c r="W35" s="228"/>
+      <c r="X35" s="229"/>
     </row>
     <row r="36" spans="5:24" ht="25" customHeight="1">
-      <c r="E36" s="256"/>
-      <c r="F36" s="257"/>
-      <c r="G36" s="265" t="s">
+      <c r="E36" s="177"/>
+      <c r="F36" s="178"/>
+      <c r="G36" s="182" t="s">
         <v>74</v>
       </c>
-      <c r="H36" s="265"/>
-      <c r="I36" s="265"/>
-      <c r="J36" s="266" t="str">
+      <c r="H36" s="182"/>
+      <c r="I36" s="182"/>
+      <c r="J36" s="183" t="str">
         <f>J35</f>
         <v>일금일백사십만원정 (₩1,400,000) - VAT별도</v>
       </c>
-      <c r="K36" s="266"/>
-      <c r="L36" s="266"/>
-      <c r="M36" s="266"/>
-      <c r="N36" s="266"/>
-      <c r="O36" s="266"/>
-      <c r="P36" s="266"/>
-      <c r="Q36" s="266"/>
-      <c r="R36" s="266"/>
-      <c r="S36" s="266"/>
-      <c r="T36" s="266"/>
-      <c r="U36" s="266"/>
-      <c r="V36" s="266"/>
-      <c r="W36" s="266"/>
-      <c r="X36" s="267"/>
+      <c r="K36" s="183"/>
+      <c r="L36" s="183"/>
+      <c r="M36" s="183"/>
+      <c r="N36" s="183"/>
+      <c r="O36" s="183"/>
+      <c r="P36" s="183"/>
+      <c r="Q36" s="183"/>
+      <c r="R36" s="183"/>
+      <c r="S36" s="183"/>
+      <c r="T36" s="183"/>
+      <c r="U36" s="183"/>
+      <c r="V36" s="183"/>
+      <c r="W36" s="183"/>
+      <c r="X36" s="184"/>
     </row>
     <row r="37" spans="5:24" ht="25" customHeight="1">
-      <c r="E37" s="256"/>
-      <c r="F37" s="257"/>
-      <c r="G37" s="265" t="s">
+      <c r="E37" s="177"/>
+      <c r="F37" s="178"/>
+      <c r="G37" s="182" t="s">
         <v>75</v>
       </c>
-      <c r="H37" s="265"/>
-      <c r="I37" s="265"/>
-      <c r="J37" s="268" t="s">
+      <c r="H37" s="182"/>
+      <c r="I37" s="182"/>
+      <c r="J37" s="185" t="s">
         <v>76</v>
       </c>
-      <c r="K37" s="268"/>
-      <c r="L37" s="268"/>
-      <c r="M37" s="268"/>
-      <c r="N37" s="268"/>
-      <c r="O37" s="268"/>
-      <c r="P37" s="268"/>
-      <c r="Q37" s="268"/>
-      <c r="R37" s="268"/>
-      <c r="S37" s="268"/>
-      <c r="T37" s="268"/>
-      <c r="U37" s="268"/>
-      <c r="V37" s="268"/>
-      <c r="W37" s="268"/>
-      <c r="X37" s="269"/>
+      <c r="K37" s="185"/>
+      <c r="L37" s="185"/>
+      <c r="M37" s="185"/>
+      <c r="N37" s="185"/>
+      <c r="O37" s="185"/>
+      <c r="P37" s="185"/>
+      <c r="Q37" s="185"/>
+      <c r="R37" s="185"/>
+      <c r="S37" s="185"/>
+      <c r="T37" s="185"/>
+      <c r="U37" s="185"/>
+      <c r="V37" s="185"/>
+      <c r="W37" s="185"/>
+      <c r="X37" s="186"/>
     </row>
     <row r="38" spans="5:24" ht="25" customHeight="1">
-      <c r="E38" s="256"/>
-      <c r="F38" s="257"/>
-      <c r="G38" s="265" t="s">
+      <c r="E38" s="177"/>
+      <c r="F38" s="178"/>
+      <c r="G38" s="182" t="s">
         <v>77</v>
       </c>
-      <c r="H38" s="265"/>
-      <c r="I38" s="265"/>
-      <c r="J38" s="268" t="s">
+      <c r="H38" s="182"/>
+      <c r="I38" s="182"/>
+      <c r="J38" s="185" t="s">
         <v>78</v>
       </c>
-      <c r="K38" s="268"/>
-      <c r="L38" s="268"/>
-      <c r="M38" s="268"/>
-      <c r="N38" s="268"/>
-      <c r="O38" s="268"/>
-      <c r="P38" s="268"/>
-      <c r="Q38" s="268"/>
-      <c r="R38" s="268"/>
-      <c r="S38" s="268"/>
-      <c r="T38" s="268"/>
-      <c r="U38" s="268"/>
-      <c r="V38" s="268"/>
-      <c r="W38" s="268"/>
-      <c r="X38" s="269"/>
+      <c r="K38" s="185"/>
+      <c r="L38" s="185"/>
+      <c r="M38" s="185"/>
+      <c r="N38" s="185"/>
+      <c r="O38" s="185"/>
+      <c r="P38" s="185"/>
+      <c r="Q38" s="185"/>
+      <c r="R38" s="185"/>
+      <c r="S38" s="185"/>
+      <c r="T38" s="185"/>
+      <c r="U38" s="185"/>
+      <c r="V38" s="185"/>
+      <c r="W38" s="185"/>
+      <c r="X38" s="186"/>
     </row>
     <row r="39" spans="5:24" ht="25" customHeight="1">
-      <c r="E39" s="256"/>
-      <c r="F39" s="257"/>
-      <c r="G39" s="265" t="s">
+      <c r="E39" s="177"/>
+      <c r="F39" s="178"/>
+      <c r="G39" s="182" t="s">
         <v>79</v>
       </c>
-      <c r="H39" s="265"/>
-      <c r="I39" s="265"/>
-      <c r="J39" s="270" t="str">
-        <f>갑지!R21</f>
+      <c r="H39" s="182"/>
+      <c r="I39" s="182"/>
+      <c r="J39" s="187" t="str">
+        <f>갑지!P21</f>
         <v>서울 성북구 길음로9길 50 (길음동)</v>
       </c>
-      <c r="K39" s="270"/>
-      <c r="L39" s="270"/>
-      <c r="M39" s="270"/>
-      <c r="N39" s="270"/>
-      <c r="O39" s="270"/>
-      <c r="P39" s="270"/>
-      <c r="Q39" s="270"/>
-      <c r="R39" s="270"/>
-      <c r="S39" s="270"/>
-      <c r="T39" s="270"/>
-      <c r="U39" s="270"/>
-      <c r="V39" s="270"/>
-      <c r="W39" s="270"/>
-      <c r="X39" s="271"/>
+      <c r="K39" s="187"/>
+      <c r="L39" s="187"/>
+      <c r="M39" s="187"/>
+      <c r="N39" s="187"/>
+      <c r="O39" s="187"/>
+      <c r="P39" s="187"/>
+      <c r="Q39" s="187"/>
+      <c r="R39" s="187"/>
+      <c r="S39" s="187"/>
+      <c r="T39" s="187"/>
+      <c r="U39" s="187"/>
+      <c r="V39" s="187"/>
+      <c r="W39" s="187"/>
+      <c r="X39" s="188"/>
     </row>
     <row r="40" spans="5:24" ht="25" customHeight="1">
-      <c r="E40" s="256"/>
-      <c r="F40" s="257"/>
-      <c r="G40" s="265"/>
-      <c r="H40" s="265"/>
-      <c r="I40" s="265"/>
-      <c r="J40" s="272" t="s">
+      <c r="E40" s="177"/>
+      <c r="F40" s="178"/>
+      <c r="G40" s="182"/>
+      <c r="H40" s="182"/>
+      <c r="I40" s="182"/>
+      <c r="J40" s="189" t="s">
         <v>80</v>
       </c>
-      <c r="K40" s="273"/>
-      <c r="L40" s="273" t="s">
-        <v>194</v>
-      </c>
-      <c r="M40" s="273"/>
-      <c r="N40" s="273"/>
-      <c r="O40" s="273"/>
-      <c r="P40" s="273"/>
-      <c r="Q40" s="137" t="s">
+      <c r="K40" s="190"/>
+      <c r="L40" s="190" t="s">
+        <v>177</v>
+      </c>
+      <c r="M40" s="190"/>
+      <c r="N40" s="190"/>
+      <c r="O40" s="190"/>
+      <c r="P40" s="190"/>
+      <c r="Q40" s="133" t="s">
         <v>15</v>
       </c>
-      <c r="R40" s="273" t="s">
+      <c r="R40" s="190" t="s">
         <v>81</v>
       </c>
-      <c r="S40" s="273"/>
-      <c r="T40" s="273" t="s">
-        <v>194</v>
-      </c>
-      <c r="U40" s="273"/>
-      <c r="V40" s="273"/>
-      <c r="W40" s="273"/>
-      <c r="X40" s="274"/>
+      <c r="S40" s="190"/>
+      <c r="T40" s="190" t="s">
+        <v>177</v>
+      </c>
+      <c r="U40" s="190"/>
+      <c r="V40" s="190"/>
+      <c r="W40" s="190"/>
+      <c r="X40" s="191"/>
     </row>
     <row r="41" spans="5:24" ht="25" customHeight="1">
-      <c r="E41" s="256"/>
-      <c r="F41" s="257"/>
-      <c r="G41" s="275" t="s">
+      <c r="E41" s="177"/>
+      <c r="F41" s="178"/>
+      <c r="G41" s="192" t="s">
         <v>82</v>
       </c>
-      <c r="H41" s="276"/>
-      <c r="I41" s="277"/>
-      <c r="J41" s="278" t="s">
+      <c r="H41" s="193"/>
+      <c r="I41" s="194"/>
+      <c r="J41" s="195" t="s">
+        <v>192</v>
+      </c>
+      <c r="K41" s="196"/>
+      <c r="L41" s="196"/>
+      <c r="M41" s="196"/>
+      <c r="N41" s="196"/>
+      <c r="O41" s="196"/>
+      <c r="P41" s="196"/>
+      <c r="Q41" s="196"/>
+      <c r="R41" s="196"/>
+      <c r="S41" s="196"/>
+      <c r="T41" s="196"/>
+      <c r="U41" s="196"/>
+      <c r="V41" s="196"/>
+      <c r="W41" s="196"/>
+      <c r="X41" s="197"/>
+    </row>
+    <row r="42" spans="5:24" ht="25" customHeight="1">
+      <c r="E42" s="177"/>
+      <c r="F42" s="178"/>
+      <c r="G42" s="198" t="s">
         <v>83</v>
       </c>
-      <c r="K41" s="279"/>
-      <c r="L41" s="279"/>
-      <c r="M41" s="279"/>
-      <c r="N41" s="279"/>
-      <c r="O41" s="279"/>
-      <c r="P41" s="279"/>
-      <c r="Q41" s="279"/>
-      <c r="R41" s="279"/>
-      <c r="S41" s="279"/>
-      <c r="T41" s="279"/>
-      <c r="U41" s="279"/>
-      <c r="V41" s="279"/>
-      <c r="W41" s="279"/>
-      <c r="X41" s="280"/>
-    </row>
-    <row r="42" spans="5:24" ht="25" customHeight="1">
-      <c r="E42" s="256"/>
-      <c r="F42" s="257"/>
-      <c r="G42" s="281" t="s">
-        <v>84</v>
-      </c>
-      <c r="H42" s="282"/>
-      <c r="I42" s="283"/>
-      <c r="J42" s="313" t="s">
-        <v>128</v>
-      </c>
-      <c r="K42" s="314"/>
-      <c r="L42" s="314"/>
-      <c r="M42" s="314" t="str">
-        <f>갑지!J10</f>
-        <v xml:space="preserve">2026년 연간 </v>
-      </c>
-      <c r="N42" s="314"/>
-      <c r="O42" s="314"/>
-      <c r="P42" s="314"/>
-      <c r="Q42" s="315" t="s">
-        <v>131</v>
-      </c>
-      <c r="R42" s="315"/>
-      <c r="S42" s="315"/>
-      <c r="T42" s="315"/>
-      <c r="U42" s="315"/>
-      <c r="V42" s="315"/>
-      <c r="W42" s="315"/>
-      <c r="X42" s="316"/>
+      <c r="H42" s="199"/>
+      <c r="I42" s="200"/>
+      <c r="J42" s="230" t="s">
+        <v>120</v>
+      </c>
+      <c r="K42" s="231"/>
+      <c r="L42" s="231"/>
+      <c r="M42" s="231"/>
+      <c r="N42" s="231"/>
+      <c r="O42" s="231"/>
+      <c r="P42" s="231"/>
+      <c r="Q42" s="231"/>
+      <c r="R42" s="231"/>
+      <c r="S42" s="231"/>
+      <c r="T42" s="231"/>
+      <c r="U42" s="231"/>
+      <c r="V42" s="231"/>
+      <c r="W42" s="231"/>
+      <c r="X42" s="232"/>
     </row>
     <row r="43" spans="5:24" ht="25" customHeight="1">
-      <c r="E43" s="256"/>
-      <c r="F43" s="257"/>
-      <c r="G43" s="284"/>
-      <c r="H43" s="285"/>
-      <c r="I43" s="286"/>
-      <c r="J43" s="317" t="s">
-        <v>132</v>
-      </c>
-      <c r="K43" s="318"/>
-      <c r="L43" s="318"/>
-      <c r="M43" s="319" t="str">
+      <c r="E43" s="177"/>
+      <c r="F43" s="178"/>
+      <c r="G43" s="201"/>
+      <c r="H43" s="202"/>
+      <c r="I43" s="203"/>
+      <c r="J43" s="219" t="s">
+        <v>122</v>
+      </c>
+      <c r="K43" s="220"/>
+      <c r="L43" s="220"/>
+      <c r="M43" s="221" t="str">
         <f>대가산출!D4</f>
         <v>일금일백사십만원정 (₩1,400,000) - VAT별도</v>
       </c>
-      <c r="N43" s="320"/>
-      <c r="O43" s="320"/>
-      <c r="P43" s="320"/>
-      <c r="Q43" s="320"/>
-      <c r="R43" s="320"/>
-      <c r="S43" s="320"/>
-      <c r="T43" s="320"/>
-      <c r="U43" s="320"/>
-      <c r="V43" s="320"/>
-      <c r="W43" s="320"/>
-      <c r="X43" s="321"/>
+      <c r="N43" s="221"/>
+      <c r="O43" s="221"/>
+      <c r="P43" s="221"/>
+      <c r="Q43" s="221"/>
+      <c r="R43" s="221"/>
+      <c r="S43" s="221"/>
+      <c r="T43" s="221"/>
+      <c r="U43" s="221"/>
+      <c r="V43" s="221"/>
+      <c r="W43" s="221"/>
+      <c r="X43" s="222"/>
     </row>
     <row r="44" spans="5:24" ht="25" customHeight="1">
-      <c r="E44" s="258"/>
-      <c r="F44" s="259"/>
-      <c r="G44" s="287"/>
-      <c r="H44" s="288"/>
-      <c r="I44" s="289"/>
-      <c r="J44" s="322" t="s">
-        <v>195</v>
-      </c>
-      <c r="K44" s="323"/>
-      <c r="L44" s="323"/>
-      <c r="M44" s="324" t="str">
+      <c r="E44" s="179"/>
+      <c r="F44" s="180"/>
+      <c r="G44" s="204"/>
+      <c r="H44" s="205"/>
+      <c r="I44" s="206"/>
+      <c r="J44" s="223" t="s">
+        <v>178</v>
+      </c>
+      <c r="K44" s="224"/>
+      <c r="L44" s="224"/>
+      <c r="M44" s="225" t="str">
         <f>대가산출!D3&amp;U35</f>
-        <v>일금칠십만원정 (₩700,000)</v>
-      </c>
-      <c r="N44" s="324"/>
-      <c r="O44" s="324"/>
-      <c r="P44" s="324"/>
-      <c r="Q44" s="324"/>
-      <c r="R44" s="324"/>
-      <c r="S44" s="324"/>
-      <c r="T44" s="324"/>
-      <c r="U44" s="324"/>
-      <c r="V44" s="324"/>
-      <c r="W44" s="324"/>
-      <c r="X44" s="325"/>
+        <v>일금칠십만원정 (₩700,000) - VAT별도</v>
+      </c>
+      <c r="N44" s="225"/>
+      <c r="O44" s="225"/>
+      <c r="P44" s="225"/>
+      <c r="Q44" s="225"/>
+      <c r="R44" s="225"/>
+      <c r="S44" s="225"/>
+      <c r="T44" s="225"/>
+      <c r="U44" s="225"/>
+      <c r="V44" s="225"/>
+      <c r="W44" s="225"/>
+      <c r="X44" s="226"/>
     </row>
     <row r="45" spans="5:24">
-      <c r="E45" s="241"/>
-      <c r="F45" s="242"/>
-      <c r="G45" s="242"/>
-      <c r="H45" s="242"/>
+      <c r="E45" s="161"/>
+      <c r="F45" s="162"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="162"/>
       <c r="X45" s="92"/>
     </row>
     <row r="46" spans="5:24" ht="53" customHeight="1">
-      <c r="E46" s="299" t="s">
-        <v>85</v>
-      </c>
-      <c r="F46" s="217"/>
-      <c r="G46" s="217"/>
-      <c r="H46" s="217"/>
-      <c r="I46" s="217"/>
-      <c r="J46" s="217"/>
-      <c r="K46" s="217"/>
-      <c r="L46" s="217"/>
-      <c r="M46" s="217"/>
-      <c r="N46" s="217"/>
-      <c r="O46" s="217"/>
-      <c r="P46" s="217"/>
-      <c r="Q46" s="217"/>
-      <c r="R46" s="217"/>
-      <c r="S46" s="217"/>
-      <c r="T46" s="217"/>
-      <c r="U46" s="217"/>
-      <c r="V46" s="217"/>
-      <c r="W46" s="217"/>
-      <c r="X46" s="240"/>
+      <c r="E46" s="216" t="s">
+        <v>84</v>
+      </c>
+      <c r="F46" s="139"/>
+      <c r="G46" s="139"/>
+      <c r="H46" s="139"/>
+      <c r="I46" s="139"/>
+      <c r="J46" s="139"/>
+      <c r="K46" s="139"/>
+      <c r="L46" s="139"/>
+      <c r="M46" s="139"/>
+      <c r="N46" s="139"/>
+      <c r="O46" s="139"/>
+      <c r="P46" s="139"/>
+      <c r="Q46" s="139"/>
+      <c r="R46" s="139"/>
+      <c r="S46" s="139"/>
+      <c r="T46" s="139"/>
+      <c r="U46" s="139"/>
+      <c r="V46" s="139"/>
+      <c r="W46" s="139"/>
+      <c r="X46" s="160"/>
     </row>
     <row r="47" spans="5:24">
       <c r="E47" s="93"/>
@@ -21256,273 +21156,273 @@
       <c r="X47" s="92"/>
     </row>
     <row r="48" spans="5:24" ht="25" customHeight="1">
-      <c r="E48" s="253" t="s">
-        <v>86</v>
-      </c>
-      <c r="F48" s="223"/>
-      <c r="G48" s="223"/>
-      <c r="H48" s="217" t="s">
-        <v>106</v>
-      </c>
-      <c r="I48" s="217"/>
-      <c r="J48" s="217"/>
-      <c r="K48" s="217"/>
-      <c r="L48" s="217"/>
-      <c r="M48" s="217"/>
-      <c r="N48" s="217"/>
-      <c r="O48" s="217"/>
-      <c r="P48" s="217"/>
-      <c r="Q48" s="217"/>
-      <c r="R48" s="217"/>
-      <c r="S48" s="217"/>
-      <c r="T48" s="217"/>
-      <c r="U48" s="217"/>
-      <c r="V48" s="217"/>
-      <c r="W48" s="217"/>
-      <c r="X48" s="240"/>
+      <c r="E48" s="173" t="s">
+        <v>85</v>
+      </c>
+      <c r="F48" s="174"/>
+      <c r="G48" s="174"/>
+      <c r="H48" s="139" t="s">
+        <v>101</v>
+      </c>
+      <c r="I48" s="139"/>
+      <c r="J48" s="139"/>
+      <c r="K48" s="139"/>
+      <c r="L48" s="139"/>
+      <c r="M48" s="139"/>
+      <c r="N48" s="139"/>
+      <c r="O48" s="139"/>
+      <c r="P48" s="139"/>
+      <c r="Q48" s="139"/>
+      <c r="R48" s="139"/>
+      <c r="S48" s="139"/>
+      <c r="T48" s="139"/>
+      <c r="U48" s="139"/>
+      <c r="V48" s="139"/>
+      <c r="W48" s="139"/>
+      <c r="X48" s="160"/>
     </row>
     <row r="49" spans="5:24" ht="25" customHeight="1">
       <c r="E49" s="95"/>
       <c r="F49" s="90"/>
       <c r="G49" s="90"/>
-      <c r="H49" s="217"/>
-      <c r="I49" s="217"/>
-      <c r="J49" s="217"/>
-      <c r="K49" s="217"/>
-      <c r="L49" s="217"/>
-      <c r="M49" s="217"/>
-      <c r="N49" s="217"/>
-      <c r="O49" s="217"/>
-      <c r="P49" s="217"/>
-      <c r="Q49" s="217"/>
-      <c r="R49" s="217"/>
-      <c r="S49" s="217"/>
-      <c r="T49" s="217"/>
-      <c r="U49" s="217"/>
-      <c r="V49" s="217"/>
-      <c r="W49" s="217"/>
-      <c r="X49" s="240"/>
+      <c r="H49" s="139"/>
+      <c r="I49" s="139"/>
+      <c r="J49" s="139"/>
+      <c r="K49" s="139"/>
+      <c r="L49" s="139"/>
+      <c r="M49" s="139"/>
+      <c r="N49" s="139"/>
+      <c r="O49" s="139"/>
+      <c r="P49" s="139"/>
+      <c r="Q49" s="139"/>
+      <c r="R49" s="139"/>
+      <c r="S49" s="139"/>
+      <c r="T49" s="139"/>
+      <c r="U49" s="139"/>
+      <c r="V49" s="139"/>
+      <c r="W49" s="139"/>
+      <c r="X49" s="160"/>
     </row>
     <row r="50" spans="5:24" ht="25" hidden="1" customHeight="1">
       <c r="E50" s="95"/>
       <c r="F50" s="90"/>
       <c r="G50" s="90"/>
-      <c r="H50" s="217"/>
-      <c r="I50" s="217"/>
-      <c r="J50" s="217"/>
-      <c r="K50" s="217"/>
-      <c r="L50" s="217"/>
-      <c r="M50" s="217"/>
-      <c r="N50" s="217"/>
-      <c r="O50" s="217"/>
-      <c r="P50" s="217"/>
-      <c r="Q50" s="217"/>
-      <c r="R50" s="217"/>
-      <c r="S50" s="217"/>
-      <c r="T50" s="217"/>
-      <c r="U50" s="217"/>
-      <c r="V50" s="217"/>
-      <c r="W50" s="217"/>
-      <c r="X50" s="240"/>
+      <c r="H50" s="139"/>
+      <c r="I50" s="139"/>
+      <c r="J50" s="139"/>
+      <c r="K50" s="139"/>
+      <c r="L50" s="139"/>
+      <c r="M50" s="139"/>
+      <c r="N50" s="139"/>
+      <c r="O50" s="139"/>
+      <c r="P50" s="139"/>
+      <c r="Q50" s="139"/>
+      <c r="R50" s="139"/>
+      <c r="S50" s="139"/>
+      <c r="T50" s="139"/>
+      <c r="U50" s="139"/>
+      <c r="V50" s="139"/>
+      <c r="W50" s="139"/>
+      <c r="X50" s="160"/>
     </row>
     <row r="51" spans="5:24">
-      <c r="E51" s="241"/>
-      <c r="F51" s="242"/>
-      <c r="G51" s="242"/>
-      <c r="H51" s="242"/>
+      <c r="E51" s="161"/>
+      <c r="F51" s="162"/>
+      <c r="G51" s="162"/>
+      <c r="H51" s="162"/>
       <c r="X51" s="92"/>
     </row>
     <row r="52" spans="5:24" ht="25" customHeight="1">
-      <c r="E52" s="243" t="s">
+      <c r="E52" s="163" t="s">
+        <v>86</v>
+      </c>
+      <c r="F52" s="164"/>
+      <c r="G52" s="164"/>
+      <c r="H52" s="165" t="s">
+        <v>131</v>
+      </c>
+      <c r="I52" s="165"/>
+      <c r="J52" s="165"/>
+      <c r="K52" s="165"/>
+      <c r="L52" s="165"/>
+      <c r="M52" s="165"/>
+      <c r="N52" s="165"/>
+      <c r="O52" s="165"/>
+      <c r="P52" s="165"/>
+      <c r="Q52" s="165"/>
+      <c r="R52" s="165"/>
+      <c r="S52" s="165"/>
+      <c r="T52" s="165"/>
+      <c r="U52" s="165"/>
+      <c r="V52" s="165"/>
+      <c r="W52" s="165"/>
+      <c r="X52" s="166"/>
+    </row>
+    <row r="53" spans="5:24" ht="26.25" customHeight="1">
+      <c r="E53" s="146" t="s">
+        <v>103</v>
+      </c>
+      <c r="F53" s="147"/>
+      <c r="G53" s="147"/>
+      <c r="H53" s="147"/>
+      <c r="I53" s="147"/>
+      <c r="J53" s="147"/>
+      <c r="K53" s="147"/>
+      <c r="L53" s="147"/>
+      <c r="M53" s="147"/>
+      <c r="N53" s="147"/>
+      <c r="O53" s="147" t="s">
+        <v>104</v>
+      </c>
+      <c r="P53" s="147"/>
+      <c r="Q53" s="147"/>
+      <c r="R53" s="147"/>
+      <c r="S53" s="147"/>
+      <c r="T53" s="147"/>
+      <c r="U53" s="147"/>
+      <c r="V53" s="147"/>
+      <c r="W53" s="147"/>
+      <c r="X53" s="167"/>
+    </row>
+    <row r="54" spans="5:24" ht="40.5" customHeight="1">
+      <c r="E54" s="168" t="s">
         <v>87</v>
       </c>
-      <c r="F52" s="244"/>
-      <c r="G52" s="244"/>
-      <c r="H52" s="245" t="s">
-        <v>143</v>
-      </c>
-      <c r="I52" s="245"/>
-      <c r="J52" s="245"/>
-      <c r="K52" s="245"/>
-      <c r="L52" s="245"/>
-      <c r="M52" s="245"/>
-      <c r="N52" s="245"/>
-      <c r="O52" s="245"/>
-      <c r="P52" s="245"/>
-      <c r="Q52" s="245"/>
-      <c r="R52" s="245"/>
-      <c r="S52" s="245"/>
-      <c r="T52" s="245"/>
-      <c r="U52" s="245"/>
-      <c r="V52" s="245"/>
-      <c r="W52" s="245"/>
-      <c r="X52" s="246"/>
-    </row>
-    <row r="53" spans="5:24" ht="26.25" customHeight="1">
-      <c r="E53" s="226" t="s">
-        <v>108</v>
-      </c>
-      <c r="F53" s="227"/>
-      <c r="G53" s="227"/>
-      <c r="H53" s="227"/>
-      <c r="I53" s="227"/>
-      <c r="J53" s="227"/>
-      <c r="K53" s="227"/>
-      <c r="L53" s="227"/>
-      <c r="M53" s="227"/>
-      <c r="N53" s="227"/>
-      <c r="O53" s="227" t="s">
-        <v>109</v>
-      </c>
-      <c r="P53" s="227"/>
-      <c r="Q53" s="227"/>
-      <c r="R53" s="227"/>
-      <c r="S53" s="227"/>
-      <c r="T53" s="227"/>
-      <c r="U53" s="227"/>
-      <c r="V53" s="227"/>
-      <c r="W53" s="227"/>
-      <c r="X53" s="247"/>
-    </row>
-    <row r="54" spans="5:24" ht="40.5" customHeight="1">
-      <c r="E54" s="248" t="s">
-        <v>88</v>
-      </c>
-      <c r="F54" s="249"/>
-      <c r="G54" s="249"/>
-      <c r="H54" s="250" t="str">
+      <c r="F54" s="169"/>
+      <c r="G54" s="169"/>
+      <c r="H54" s="170" t="str">
         <f>E9</f>
         <v>래미안길음뉴타운9단지아파트</v>
       </c>
-      <c r="I54" s="250"/>
-      <c r="J54" s="250"/>
-      <c r="K54" s="250"/>
-      <c r="L54" s="250"/>
-      <c r="M54" s="250"/>
-      <c r="N54" s="250"/>
-      <c r="O54" s="249" t="s">
+      <c r="I54" s="170"/>
+      <c r="J54" s="170"/>
+      <c r="K54" s="170"/>
+      <c r="L54" s="170"/>
+      <c r="M54" s="170"/>
+      <c r="N54" s="170"/>
+      <c r="O54" s="169" t="s">
+        <v>88</v>
+      </c>
+      <c r="P54" s="169"/>
+      <c r="Q54" s="169"/>
+      <c r="R54" s="171" t="s">
         <v>89</v>
       </c>
-      <c r="P54" s="249"/>
-      <c r="Q54" s="249"/>
-      <c r="R54" s="251" t="s">
+      <c r="S54" s="171"/>
+      <c r="T54" s="171"/>
+      <c r="U54" s="171"/>
+      <c r="V54" s="171"/>
+      <c r="W54" s="171"/>
+      <c r="X54" s="172"/>
+    </row>
+    <row r="55" spans="5:24" ht="40.5" customHeight="1">
+      <c r="E55" s="146" t="s">
         <v>90</v>
       </c>
-      <c r="S54" s="251"/>
-      <c r="T54" s="251"/>
-      <c r="U54" s="251"/>
-      <c r="V54" s="251"/>
-      <c r="W54" s="251"/>
-      <c r="X54" s="252"/>
-    </row>
-    <row r="55" spans="5:24" ht="40.5" customHeight="1">
-      <c r="E55" s="226" t="s">
-        <v>91</v>
-      </c>
-      <c r="F55" s="227"/>
-      <c r="G55" s="227"/>
-      <c r="H55" s="228" t="str">
+      <c r="F55" s="147"/>
+      <c r="G55" s="147"/>
+      <c r="H55" s="148" t="str">
         <f>J39</f>
         <v>서울 성북구 길음로9길 50 (길음동)</v>
       </c>
-      <c r="I55" s="229"/>
-      <c r="J55" s="229"/>
-      <c r="K55" s="229"/>
-      <c r="L55" s="229"/>
-      <c r="M55" s="229"/>
-      <c r="N55" s="230"/>
-      <c r="O55" s="227" t="s">
+      <c r="I55" s="149"/>
+      <c r="J55" s="149"/>
+      <c r="K55" s="149"/>
+      <c r="L55" s="149"/>
+      <c r="M55" s="149"/>
+      <c r="N55" s="150"/>
+      <c r="O55" s="147" t="s">
+        <v>91</v>
+      </c>
+      <c r="P55" s="147"/>
+      <c r="Q55" s="147"/>
+      <c r="R55" s="151" t="s">
         <v>92</v>
       </c>
-      <c r="P55" s="227"/>
-      <c r="Q55" s="227"/>
-      <c r="R55" s="231" t="s">
+      <c r="S55" s="152"/>
+      <c r="T55" s="152"/>
+      <c r="U55" s="152"/>
+      <c r="V55" s="152"/>
+      <c r="W55" s="152"/>
+      <c r="X55" s="153"/>
+    </row>
+    <row r="56" spans="5:24" ht="40.5" customHeight="1">
+      <c r="E56" s="154" t="s">
         <v>93</v>
       </c>
-      <c r="S55" s="232"/>
-      <c r="T55" s="232"/>
-      <c r="U55" s="232"/>
-      <c r="V55" s="232"/>
-      <c r="W55" s="232"/>
-      <c r="X55" s="233"/>
-    </row>
-    <row r="56" spans="5:24" ht="40.5" customHeight="1">
-      <c r="E56" s="234" t="s">
+      <c r="F56" s="155"/>
+      <c r="G56" s="155"/>
+      <c r="H56" s="156" t="s">
         <v>94</v>
       </c>
-      <c r="F56" s="235"/>
-      <c r="G56" s="235"/>
-      <c r="H56" s="236" t="s">
+      <c r="I56" s="156"/>
+      <c r="J56" s="156"/>
+      <c r="K56" s="156"/>
+      <c r="L56" s="156"/>
+      <c r="M56" s="156"/>
+      <c r="N56" s="156"/>
+      <c r="O56" s="155" t="s">
         <v>95</v>
       </c>
-      <c r="I56" s="236"/>
-      <c r="J56" s="236"/>
-      <c r="K56" s="236"/>
-      <c r="L56" s="236"/>
-      <c r="M56" s="236"/>
-      <c r="N56" s="236"/>
-      <c r="O56" s="235" t="s">
+      <c r="P56" s="155"/>
+      <c r="Q56" s="155"/>
+      <c r="R56" s="157" t="s">
         <v>96</v>
       </c>
-      <c r="P56" s="235"/>
-      <c r="Q56" s="235"/>
-      <c r="R56" s="237" t="s">
+      <c r="S56" s="157"/>
+      <c r="T56" s="157"/>
+      <c r="U56" s="157"/>
+      <c r="V56" s="157"/>
+      <c r="W56" s="157"/>
+      <c r="X56" s="158"/>
+    </row>
+    <row r="57" spans="5:24" ht="16">
+      <c r="E57" s="159" t="s">
         <v>97</v>
       </c>
-      <c r="S56" s="237"/>
-      <c r="T56" s="237"/>
-      <c r="U56" s="237"/>
-      <c r="V56" s="237"/>
-      <c r="W56" s="237"/>
-      <c r="X56" s="238"/>
-    </row>
-    <row r="57" spans="5:24" ht="16">
-      <c r="E57" s="239" t="s">
-        <v>98</v>
-      </c>
-      <c r="F57" s="239"/>
-      <c r="G57" s="239"/>
-      <c r="H57" s="239"/>
-      <c r="I57" s="239"/>
-      <c r="J57" s="239"/>
-      <c r="K57" s="239"/>
-      <c r="L57" s="239"/>
-      <c r="M57" s="239"/>
-      <c r="N57" s="239"/>
-      <c r="O57" s="239"/>
-      <c r="P57" s="239"/>
-      <c r="Q57" s="239"/>
-      <c r="R57" s="239"/>
-      <c r="S57" s="239"/>
-      <c r="T57" s="239"/>
-      <c r="U57" s="239"/>
-      <c r="V57" s="239"/>
-      <c r="W57" s="239"/>
-      <c r="X57" s="239"/>
+      <c r="F57" s="159"/>
+      <c r="G57" s="159"/>
+      <c r="H57" s="159"/>
+      <c r="I57" s="159"/>
+      <c r="J57" s="159"/>
+      <c r="K57" s="159"/>
+      <c r="L57" s="159"/>
+      <c r="M57" s="159"/>
+      <c r="N57" s="159"/>
+      <c r="O57" s="159"/>
+      <c r="P57" s="159"/>
+      <c r="Q57" s="159"/>
+      <c r="R57" s="159"/>
+      <c r="S57" s="159"/>
+      <c r="T57" s="159"/>
+      <c r="U57" s="159"/>
+      <c r="V57" s="159"/>
+      <c r="W57" s="159"/>
+      <c r="X57" s="159"/>
     </row>
     <row r="58" spans="5:24" ht="26">
-      <c r="E58" s="222" t="s">
-        <v>107</v>
-      </c>
-      <c r="F58" s="222"/>
-      <c r="G58" s="222"/>
-      <c r="H58" s="222"/>
-      <c r="I58" s="222"/>
-      <c r="J58" s="222"/>
-      <c r="K58" s="222"/>
-      <c r="L58" s="222"/>
-      <c r="M58" s="222"/>
-      <c r="N58" s="222"/>
-      <c r="O58" s="222"/>
-      <c r="P58" s="222"/>
-      <c r="Q58" s="222"/>
-      <c r="R58" s="222"/>
-      <c r="S58" s="222"/>
-      <c r="T58" s="222"/>
-      <c r="U58" s="222"/>
-      <c r="V58" s="222"/>
-      <c r="W58" s="222"/>
-      <c r="X58" s="222"/>
+      <c r="E58" s="144" t="s">
+        <v>102</v>
+      </c>
+      <c r="F58" s="144"/>
+      <c r="G58" s="144"/>
+      <c r="H58" s="144"/>
+      <c r="I58" s="144"/>
+      <c r="J58" s="144"/>
+      <c r="K58" s="144"/>
+      <c r="L58" s="144"/>
+      <c r="M58" s="144"/>
+      <c r="N58" s="144"/>
+      <c r="O58" s="144"/>
+      <c r="P58" s="144"/>
+      <c r="Q58" s="144"/>
+      <c r="R58" s="144"/>
+      <c r="S58" s="144"/>
+      <c r="T58" s="144"/>
+      <c r="U58" s="144"/>
+      <c r="V58" s="144"/>
+      <c r="W58" s="144"/>
+      <c r="X58" s="144"/>
     </row>
     <row r="59" spans="5:24" ht="15">
       <c r="E59" s="96"/>
@@ -21531,57 +21431,52 @@
       <c r="L59" s="85"/>
     </row>
     <row r="60" spans="5:24" ht="25" customHeight="1">
-      <c r="E60" s="132"/>
-      <c r="F60" s="223" t="s">
-        <v>160</v>
-      </c>
-      <c r="G60" s="223"/>
-      <c r="H60" s="225" t="str">
-        <f>H54</f>
-        <v>래미안길음뉴타운9단지아파트</v>
-      </c>
-      <c r="I60" s="225"/>
-      <c r="J60" s="225"/>
-      <c r="K60" s="225"/>
-      <c r="L60" s="225"/>
-      <c r="M60" s="225"/>
-      <c r="N60" s="225"/>
-      <c r="O60" s="225"/>
-      <c r="P60" s="223" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q60" s="223"/>
-      <c r="R60" s="223"/>
-      <c r="S60" s="223"/>
-      <c r="T60" s="223"/>
-      <c r="U60" s="223"/>
-      <c r="V60" s="223"/>
-      <c r="W60" s="223"/>
-      <c r="X60" s="223"/>
+      <c r="E60" s="130"/>
+      <c r="F60" s="145" t="str">
+        <f>"사용자 "&amp;H54&amp;" 입주자대표회의(이하 ""사용자""라 한다) 와 점검프로그램"</f>
+        <v>사용자 래미안길음뉴타운9단지아파트 입주자대표회의(이하 "사용자"라 한다) 와 점검프로그램</v>
+      </c>
+      <c r="G60" s="145"/>
+      <c r="H60" s="145"/>
+      <c r="I60" s="145"/>
+      <c r="J60" s="145"/>
+      <c r="K60" s="145"/>
+      <c r="L60" s="145"/>
+      <c r="M60" s="145"/>
+      <c r="N60" s="145"/>
+      <c r="O60" s="145"/>
+      <c r="P60" s="145"/>
+      <c r="Q60" s="145"/>
+      <c r="R60" s="145"/>
+      <c r="S60" s="145"/>
+      <c r="T60" s="145"/>
+      <c r="U60" s="145"/>
+      <c r="V60" s="145"/>
+      <c r="W60" s="145"/>
+      <c r="X60" s="145"/>
     </row>
     <row r="61" spans="5:24" ht="25" customHeight="1">
-      <c r="E61" s="221" t="s">
-        <v>159</v>
-      </c>
-      <c r="F61" s="221"/>
-      <c r="G61" s="221"/>
-      <c r="H61" s="221"/>
-      <c r="I61" s="221"/>
-      <c r="J61" s="221"/>
-      <c r="K61" s="221"/>
-      <c r="L61" s="221"/>
-      <c r="M61" s="221"/>
-      <c r="N61" s="221"/>
-      <c r="O61" s="221"/>
-      <c r="P61" s="221"/>
-      <c r="Q61" s="221"/>
-      <c r="R61" s="221"/>
-      <c r="S61" s="221"/>
-      <c r="T61" s="221"/>
-      <c r="U61" s="221"/>
-      <c r="V61" s="221"/>
-      <c r="W61" s="221"/>
-      <c r="X61" s="221"/>
+      <c r="F61" s="143" t="s">
+        <v>195</v>
+      </c>
+      <c r="G61" s="143"/>
+      <c r="H61" s="143"/>
+      <c r="I61" s="143"/>
+      <c r="J61" s="143"/>
+      <c r="K61" s="143"/>
+      <c r="L61" s="143"/>
+      <c r="M61" s="143"/>
+      <c r="N61" s="143"/>
+      <c r="O61" s="143"/>
+      <c r="P61" s="143"/>
+      <c r="Q61" s="143"/>
+      <c r="R61" s="143"/>
+      <c r="S61" s="143"/>
+      <c r="T61" s="143"/>
+      <c r="U61" s="143"/>
+      <c r="V61" s="143"/>
+      <c r="W61" s="143"/>
+      <c r="X61" s="143"/>
     </row>
     <row r="62" spans="5:24" ht="20" customHeight="1">
       <c r="E62" s="97"/>
@@ -21595,40 +21490,40 @@
       <c r="M62" s="97"/>
     </row>
     <row r="63" spans="5:24" ht="20" customHeight="1">
-      <c r="E63" s="216" t="s">
-        <v>169</v>
-      </c>
-      <c r="F63" s="216"/>
-      <c r="G63" s="216"/>
-      <c r="H63" s="216"/>
-      <c r="I63" s="216"/>
-      <c r="J63" s="216"/>
-      <c r="K63" s="216"/>
-      <c r="L63" s="216"/>
-      <c r="M63" s="216"/>
-    </row>
-    <row r="64" spans="5:24" ht="56" customHeight="1">
-      <c r="F64" s="217" t="s">
-        <v>196</v>
-      </c>
-      <c r="G64" s="217"/>
-      <c r="H64" s="217"/>
-      <c r="I64" s="217"/>
-      <c r="J64" s="217"/>
-      <c r="K64" s="217"/>
-      <c r="L64" s="217"/>
-      <c r="M64" s="217"/>
-      <c r="N64" s="217"/>
-      <c r="O64" s="217"/>
-      <c r="P64" s="217"/>
-      <c r="Q64" s="217"/>
-      <c r="R64" s="217"/>
-      <c r="S64" s="217"/>
-      <c r="T64" s="217"/>
-      <c r="U64" s="217"/>
-      <c r="V64" s="217"/>
-      <c r="W64" s="217"/>
-      <c r="X64" s="217"/>
+      <c r="E63" s="138" t="s">
+        <v>154</v>
+      </c>
+      <c r="F63" s="138"/>
+      <c r="G63" s="138"/>
+      <c r="H63" s="138"/>
+      <c r="I63" s="138"/>
+      <c r="J63" s="138"/>
+      <c r="K63" s="138"/>
+      <c r="L63" s="138"/>
+      <c r="M63" s="138"/>
+    </row>
+    <row r="64" spans="5:24" ht="61" customHeight="1">
+      <c r="F64" s="139" t="s">
+        <v>179</v>
+      </c>
+      <c r="G64" s="139"/>
+      <c r="H64" s="139"/>
+      <c r="I64" s="139"/>
+      <c r="J64" s="139"/>
+      <c r="K64" s="139"/>
+      <c r="L64" s="139"/>
+      <c r="M64" s="139"/>
+      <c r="N64" s="139"/>
+      <c r="O64" s="139"/>
+      <c r="P64" s="139"/>
+      <c r="Q64" s="139"/>
+      <c r="R64" s="139"/>
+      <c r="S64" s="139"/>
+      <c r="T64" s="139"/>
+      <c r="U64" s="139"/>
+      <c r="V64" s="139"/>
+      <c r="W64" s="139"/>
+      <c r="X64" s="139"/>
     </row>
     <row r="65" spans="5:24" ht="20" customHeight="1">
       <c r="E65" s="98"/>
@@ -21637,70 +21532,66 @@
       <c r="L65" s="85"/>
     </row>
     <row r="66" spans="5:24" ht="20" customHeight="1">
-      <c r="E66" s="216" t="s">
-        <v>170</v>
-      </c>
-      <c r="F66" s="216"/>
-      <c r="G66" s="216"/>
-      <c r="H66" s="216"/>
-      <c r="I66" s="216"/>
-      <c r="J66" s="216"/>
-      <c r="K66" s="216"/>
-      <c r="L66" s="216"/>
-      <c r="M66" s="216"/>
-      <c r="N66" s="216"/>
-      <c r="O66" s="216"/>
-      <c r="P66" s="216"/>
-      <c r="Q66" s="216"/>
-      <c r="R66" s="216"/>
-      <c r="S66" s="216"/>
-      <c r="T66" s="216"/>
-      <c r="U66" s="216"/>
-      <c r="V66" s="216"/>
-      <c r="W66" s="216"/>
-      <c r="X66" s="216"/>
+      <c r="E66" s="138" t="s">
+        <v>155</v>
+      </c>
+      <c r="F66" s="138"/>
+      <c r="G66" s="138"/>
+      <c r="H66" s="138"/>
+      <c r="I66" s="138"/>
+      <c r="J66" s="138"/>
+      <c r="K66" s="138"/>
+      <c r="L66" s="138"/>
+      <c r="M66" s="138"/>
+      <c r="N66" s="138"/>
+      <c r="O66" s="138"/>
+      <c r="P66" s="138"/>
+      <c r="Q66" s="138"/>
+      <c r="R66" s="138"/>
+      <c r="S66" s="138"/>
+      <c r="T66" s="138"/>
+      <c r="U66" s="138"/>
+      <c r="V66" s="138"/>
+      <c r="W66" s="138"/>
+      <c r="X66" s="138"/>
     </row>
     <row r="67" spans="5:24" ht="20" customHeight="1">
-      <c r="F67" s="99" t="s">
-        <v>99</v>
-      </c>
-      <c r="G67" s="99"/>
-      <c r="H67" s="99"/>
-      <c r="I67" s="224" t="str">
-        <f>E9</f>
-        <v>래미안길음뉴타운9단지아파트</v>
-      </c>
-      <c r="J67" s="224"/>
-      <c r="K67" s="224"/>
-      <c r="L67" s="224"/>
-      <c r="M67" s="224"/>
-      <c r="N67" s="224"/>
-      <c r="O67" s="224"/>
-      <c r="P67" s="224"/>
-      <c r="Q67" s="224"/>
-      <c r="R67" s="224"/>
-      <c r="S67" s="224"/>
-      <c r="T67" s="224"/>
-      <c r="U67" s="224"/>
-      <c r="V67" s="224"/>
-      <c r="W67" s="224"/>
-      <c r="X67" s="224"/>
+      <c r="F67" s="134" t="str">
+        <f>"① 시설물명 : "&amp;H54</f>
+        <v>① 시설물명 : 래미안길음뉴타운9단지아파트</v>
+      </c>
+      <c r="G67" s="134"/>
+      <c r="H67" s="134"/>
+      <c r="I67" s="134"/>
+      <c r="J67" s="134"/>
+      <c r="K67" s="134"/>
+      <c r="L67" s="134"/>
+      <c r="M67" s="134"/>
+      <c r="N67" s="134"/>
+      <c r="O67" s="134"/>
+      <c r="P67" s="134"/>
+      <c r="Q67" s="134"/>
+      <c r="R67" s="134"/>
+      <c r="S67" s="134"/>
+      <c r="T67" s="134"/>
+      <c r="U67" s="134"/>
+      <c r="V67" s="134"/>
+      <c r="W67" s="134"/>
+      <c r="X67" s="134"/>
     </row>
     <row r="68" spans="5:24" ht="20" customHeight="1">
-      <c r="F68" s="99" t="s">
-        <v>100</v>
-      </c>
-      <c r="G68" s="99"/>
-      <c r="H68" s="99"/>
-      <c r="I68" s="116" t="str">
-        <f>J39</f>
-        <v>서울 성북구 길음로9길 50 (길음동)</v>
-      </c>
-      <c r="J68" s="116"/>
-      <c r="K68" s="116"/>
-      <c r="L68" s="116"/>
-      <c r="M68" s="116"/>
-      <c r="N68" s="133"/>
+      <c r="F68" s="134" t="str">
+        <f>"② 위      치 : "&amp;H55</f>
+        <v>② 위      치 : 서울 성북구 길음로9길 50 (길음동)</v>
+      </c>
+      <c r="G68" s="134"/>
+      <c r="H68" s="134"/>
+      <c r="I68" s="134"/>
+      <c r="J68" s="134"/>
+      <c r="K68" s="134"/>
+      <c r="L68" s="134"/>
+      <c r="M68" s="134"/>
+      <c r="N68" s="134"/>
       <c r="O68" s="134"/>
       <c r="P68" s="134"/>
       <c r="Q68" s="134"/>
@@ -21713,19 +21604,17 @@
       <c r="X68" s="134"/>
     </row>
     <row r="69" spans="5:24" ht="20" customHeight="1">
-      <c r="F69" s="99" t="s">
-        <v>101</v>
-      </c>
-      <c r="G69" s="99"/>
-      <c r="H69" s="99"/>
-      <c r="I69" s="116" t="s">
-        <v>102</v>
-      </c>
-      <c r="J69" s="116"/>
-      <c r="K69" s="116"/>
-      <c r="L69" s="116"/>
-      <c r="M69" s="116"/>
-      <c r="N69" s="133"/>
+      <c r="F69" s="134" t="s">
+        <v>193</v>
+      </c>
+      <c r="G69" s="134"/>
+      <c r="H69" s="134"/>
+      <c r="I69" s="134"/>
+      <c r="J69" s="134"/>
+      <c r="K69" s="134"/>
+      <c r="L69" s="134"/>
+      <c r="M69" s="134"/>
+      <c r="N69" s="134"/>
       <c r="O69" s="134"/>
       <c r="P69" s="134"/>
       <c r="Q69" s="134"/>
@@ -21738,20 +21627,18 @@
       <c r="X69" s="134"/>
     </row>
     <row r="70" spans="5:24" ht="20" customHeight="1">
-      <c r="F70" s="215" t="s">
-        <v>133</v>
-      </c>
-      <c r="G70" s="215"/>
-      <c r="H70" s="215"/>
-      <c r="I70" s="215"/>
-      <c r="J70" s="215"/>
-      <c r="K70" s="215"/>
-      <c r="L70" s="99" t="str">
-        <f>갑지!R22</f>
-        <v>아파트 15개동 1012세대 (해당동 : 15개동)</v>
-      </c>
-      <c r="M70" s="116"/>
-      <c r="N70" s="133"/>
+      <c r="F70" s="134" t="str">
+        <f>"④ 점검프로그램 대상시설물의 범위 : "&amp;갑지!P22</f>
+        <v>④ 점검프로그램 대상시설물의 범위 : 아파트 15개동 1012세대 (해당동 : 15개동)</v>
+      </c>
+      <c r="G70" s="134"/>
+      <c r="H70" s="134"/>
+      <c r="I70" s="134"/>
+      <c r="J70" s="134"/>
+      <c r="K70" s="134"/>
+      <c r="L70" s="134"/>
+      <c r="M70" s="134"/>
+      <c r="N70" s="134"/>
       <c r="O70" s="134"/>
       <c r="P70" s="134"/>
       <c r="Q70" s="134"/>
@@ -21770,110 +21657,110 @@
       <c r="L71" s="85"/>
     </row>
     <row r="72" spans="5:24" ht="20" customHeight="1">
-      <c r="E72" s="216" t="s">
-        <v>171</v>
-      </c>
-      <c r="F72" s="216"/>
-      <c r="G72" s="216"/>
-      <c r="H72" s="216"/>
-      <c r="I72" s="216"/>
-      <c r="J72" s="216"/>
-      <c r="K72" s="216"/>
-      <c r="L72" s="216"/>
-      <c r="M72" s="216"/>
+      <c r="E72" s="138" t="s">
+        <v>156</v>
+      </c>
+      <c r="F72" s="138"/>
+      <c r="G72" s="138"/>
+      <c r="H72" s="138"/>
+      <c r="I72" s="138"/>
+      <c r="J72" s="138"/>
+      <c r="K72" s="138"/>
+      <c r="L72" s="138"/>
+      <c r="M72" s="138"/>
     </row>
     <row r="73" spans="5:24" ht="32.25" customHeight="1">
-      <c r="F73" s="217" t="s">
-        <v>110</v>
-      </c>
-      <c r="G73" s="217"/>
-      <c r="H73" s="217"/>
-      <c r="I73" s="217"/>
-      <c r="J73" s="217"/>
-      <c r="K73" s="217"/>
-      <c r="L73" s="217"/>
-      <c r="M73" s="217"/>
-      <c r="N73" s="217"/>
-      <c r="O73" s="217"/>
-      <c r="P73" s="217"/>
-      <c r="Q73" s="217"/>
-      <c r="R73" s="217"/>
-      <c r="S73" s="217"/>
-      <c r="T73" s="217"/>
-      <c r="U73" s="217"/>
-      <c r="V73" s="217"/>
-      <c r="W73" s="217"/>
-      <c r="X73" s="217"/>
+      <c r="F73" s="139" t="s">
+        <v>105</v>
+      </c>
+      <c r="G73" s="139"/>
+      <c r="H73" s="139"/>
+      <c r="I73" s="139"/>
+      <c r="J73" s="139"/>
+      <c r="K73" s="139"/>
+      <c r="L73" s="139"/>
+      <c r="M73" s="139"/>
+      <c r="N73" s="139"/>
+      <c r="O73" s="139"/>
+      <c r="P73" s="139"/>
+      <c r="Q73" s="139"/>
+      <c r="R73" s="139"/>
+      <c r="S73" s="139"/>
+      <c r="T73" s="139"/>
+      <c r="U73" s="139"/>
+      <c r="V73" s="139"/>
+      <c r="W73" s="139"/>
+      <c r="X73" s="139"/>
     </row>
     <row r="74" spans="5:24" ht="49.5" customHeight="1">
-      <c r="F74" s="217" t="s">
-        <v>111</v>
-      </c>
-      <c r="G74" s="217"/>
-      <c r="H74" s="217"/>
-      <c r="I74" s="217"/>
-      <c r="J74" s="217"/>
-      <c r="K74" s="217"/>
-      <c r="L74" s="217"/>
-      <c r="M74" s="217"/>
-      <c r="N74" s="217"/>
-      <c r="O74" s="217"/>
-      <c r="P74" s="217"/>
-      <c r="Q74" s="217"/>
-      <c r="R74" s="217"/>
-      <c r="S74" s="217"/>
-      <c r="T74" s="217"/>
-      <c r="U74" s="217"/>
-      <c r="V74" s="217"/>
-      <c r="W74" s="217"/>
-      <c r="X74" s="217"/>
+      <c r="F74" s="139" t="s">
+        <v>106</v>
+      </c>
+      <c r="G74" s="139"/>
+      <c r="H74" s="139"/>
+      <c r="I74" s="139"/>
+      <c r="J74" s="139"/>
+      <c r="K74" s="139"/>
+      <c r="L74" s="139"/>
+      <c r="M74" s="139"/>
+      <c r="N74" s="139"/>
+      <c r="O74" s="139"/>
+      <c r="P74" s="139"/>
+      <c r="Q74" s="139"/>
+      <c r="R74" s="139"/>
+      <c r="S74" s="139"/>
+      <c r="T74" s="139"/>
+      <c r="U74" s="139"/>
+      <c r="V74" s="139"/>
+      <c r="W74" s="139"/>
+      <c r="X74" s="139"/>
     </row>
     <row r="75" spans="5:24" ht="49.5" customHeight="1">
-      <c r="F75" s="217" t="s">
-        <v>112</v>
-      </c>
-      <c r="G75" s="217"/>
-      <c r="H75" s="217"/>
-      <c r="I75" s="217"/>
-      <c r="J75" s="217"/>
-      <c r="K75" s="217"/>
-      <c r="L75" s="217"/>
-      <c r="M75" s="217"/>
-      <c r="N75" s="217"/>
-      <c r="O75" s="217"/>
-      <c r="P75" s="217"/>
-      <c r="Q75" s="217"/>
-      <c r="R75" s="217"/>
-      <c r="S75" s="217"/>
-      <c r="T75" s="217"/>
-      <c r="U75" s="217"/>
-      <c r="V75" s="217"/>
-      <c r="W75" s="217"/>
-      <c r="X75" s="217"/>
+      <c r="F75" s="139" t="s">
+        <v>107</v>
+      </c>
+      <c r="G75" s="139"/>
+      <c r="H75" s="139"/>
+      <c r="I75" s="139"/>
+      <c r="J75" s="139"/>
+      <c r="K75" s="139"/>
+      <c r="L75" s="139"/>
+      <c r="M75" s="139"/>
+      <c r="N75" s="139"/>
+      <c r="O75" s="139"/>
+      <c r="P75" s="139"/>
+      <c r="Q75" s="139"/>
+      <c r="R75" s="139"/>
+      <c r="S75" s="139"/>
+      <c r="T75" s="139"/>
+      <c r="U75" s="139"/>
+      <c r="V75" s="139"/>
+      <c r="W75" s="139"/>
+      <c r="X75" s="139"/>
     </row>
     <row r="76" spans="5:24" ht="52.5" customHeight="1">
       <c r="E76" s="98"/>
-      <c r="F76" s="217" t="s">
-        <v>147</v>
-      </c>
-      <c r="G76" s="217"/>
-      <c r="H76" s="217"/>
-      <c r="I76" s="217"/>
-      <c r="J76" s="217"/>
-      <c r="K76" s="217"/>
-      <c r="L76" s="217"/>
-      <c r="M76" s="217"/>
-      <c r="N76" s="217"/>
-      <c r="O76" s="217"/>
-      <c r="P76" s="217"/>
-      <c r="Q76" s="217"/>
-      <c r="R76" s="217"/>
-      <c r="S76" s="217"/>
-      <c r="T76" s="217"/>
-      <c r="U76" s="217"/>
-      <c r="V76" s="217"/>
-      <c r="W76" s="217"/>
-      <c r="X76" s="217"/>
+      <c r="F76" s="139" t="s">
+        <v>135</v>
+      </c>
+      <c r="G76" s="139"/>
+      <c r="H76" s="139"/>
+      <c r="I76" s="139"/>
+      <c r="J76" s="139"/>
+      <c r="K76" s="139"/>
+      <c r="L76" s="139"/>
+      <c r="M76" s="139"/>
+      <c r="N76" s="139"/>
+      <c r="O76" s="139"/>
+      <c r="P76" s="139"/>
+      <c r="Q76" s="139"/>
+      <c r="R76" s="139"/>
+      <c r="S76" s="139"/>
+      <c r="T76" s="139"/>
+      <c r="U76" s="139"/>
+      <c r="V76" s="139"/>
+      <c r="W76" s="139"/>
+      <c r="X76" s="139"/>
     </row>
     <row r="77" spans="5:24" ht="20" customHeight="1">
       <c r="E77" s="98"/>
@@ -21882,21 +21769,21 @@
       <c r="L77" s="85"/>
     </row>
     <row r="78" spans="5:24" ht="21" customHeight="1">
-      <c r="E78" s="216" t="s">
-        <v>172</v>
-      </c>
-      <c r="F78" s="216"/>
-      <c r="G78" s="216"/>
-      <c r="H78" s="216"/>
-      <c r="I78" s="216"/>
-      <c r="J78" s="216"/>
-      <c r="K78" s="216"/>
-      <c r="L78" s="216"/>
-      <c r="M78" s="216"/>
+      <c r="E78" s="138" t="s">
+        <v>157</v>
+      </c>
+      <c r="F78" s="138"/>
+      <c r="G78" s="138"/>
+      <c r="H78" s="138"/>
+      <c r="I78" s="138"/>
+      <c r="J78" s="138"/>
+      <c r="K78" s="138"/>
+      <c r="L78" s="138"/>
+      <c r="M78" s="138"/>
     </row>
     <row r="79" spans="5:24" ht="20" customHeight="1">
       <c r="F79" s="116" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="G79" s="99"/>
       <c r="H79" s="99"/>
@@ -21907,27 +21794,27 @@
       <c r="M79" s="99"/>
     </row>
     <row r="80" spans="5:24" ht="40" customHeight="1">
-      <c r="F80" s="217" t="s">
-        <v>113</v>
-      </c>
-      <c r="G80" s="217"/>
-      <c r="H80" s="217"/>
-      <c r="I80" s="217"/>
-      <c r="J80" s="217"/>
-      <c r="K80" s="217"/>
-      <c r="L80" s="217"/>
-      <c r="M80" s="217"/>
-      <c r="N80" s="217"/>
-      <c r="O80" s="217"/>
-      <c r="P80" s="217"/>
-      <c r="Q80" s="217"/>
-      <c r="R80" s="217"/>
-      <c r="S80" s="217"/>
-      <c r="T80" s="217"/>
-      <c r="U80" s="217"/>
-      <c r="V80" s="217"/>
-      <c r="W80" s="217"/>
-      <c r="X80" s="217"/>
+      <c r="F80" s="139" t="s">
+        <v>108</v>
+      </c>
+      <c r="G80" s="139"/>
+      <c r="H80" s="139"/>
+      <c r="I80" s="139"/>
+      <c r="J80" s="139"/>
+      <c r="K80" s="139"/>
+      <c r="L80" s="139"/>
+      <c r="M80" s="139"/>
+      <c r="N80" s="139"/>
+      <c r="O80" s="139"/>
+      <c r="P80" s="139"/>
+      <c r="Q80" s="139"/>
+      <c r="R80" s="139"/>
+      <c r="S80" s="139"/>
+      <c r="T80" s="139"/>
+      <c r="U80" s="139"/>
+      <c r="V80" s="139"/>
+      <c r="W80" s="139"/>
+      <c r="X80" s="139"/>
     </row>
     <row r="81" spans="5:24" ht="20" customHeight="1">
       <c r="E81" s="98"/>
@@ -21936,191 +21823,191 @@
       <c r="L81" s="85"/>
     </row>
     <row r="82" spans="5:24" ht="22" customHeight="1">
-      <c r="E82" s="216" t="s">
-        <v>173</v>
-      </c>
-      <c r="F82" s="216"/>
-      <c r="G82" s="216"/>
-      <c r="H82" s="216"/>
-      <c r="I82" s="216"/>
-      <c r="J82" s="216"/>
-      <c r="K82" s="216"/>
-      <c r="L82" s="216"/>
-      <c r="M82" s="216"/>
+      <c r="E82" s="138" t="s">
+        <v>158</v>
+      </c>
+      <c r="F82" s="138"/>
+      <c r="G82" s="138"/>
+      <c r="H82" s="138"/>
+      <c r="I82" s="138"/>
+      <c r="J82" s="138"/>
+      <c r="K82" s="138"/>
+      <c r="L82" s="138"/>
+      <c r="M82" s="138"/>
     </row>
     <row r="83" spans="5:24" ht="20" customHeight="1">
-      <c r="F83" s="217" t="s">
-        <v>114</v>
-      </c>
-      <c r="G83" s="217"/>
-      <c r="H83" s="217"/>
-      <c r="I83" s="217"/>
-      <c r="J83" s="217"/>
-      <c r="K83" s="217"/>
-      <c r="L83" s="217"/>
-      <c r="M83" s="217"/>
-      <c r="N83" s="217"/>
-      <c r="O83" s="217"/>
-      <c r="P83" s="217"/>
-      <c r="Q83" s="217"/>
-      <c r="R83" s="217"/>
-      <c r="S83" s="217"/>
-      <c r="T83" s="217"/>
-      <c r="U83" s="217"/>
-      <c r="V83" s="217"/>
-      <c r="W83" s="217"/>
-      <c r="X83" s="217"/>
+      <c r="F83" s="139" t="s">
+        <v>109</v>
+      </c>
+      <c r="G83" s="139"/>
+      <c r="H83" s="139"/>
+      <c r="I83" s="139"/>
+      <c r="J83" s="139"/>
+      <c r="K83" s="139"/>
+      <c r="L83" s="139"/>
+      <c r="M83" s="139"/>
+      <c r="N83" s="139"/>
+      <c r="O83" s="139"/>
+      <c r="P83" s="139"/>
+      <c r="Q83" s="139"/>
+      <c r="R83" s="139"/>
+      <c r="S83" s="139"/>
+      <c r="T83" s="139"/>
+      <c r="U83" s="139"/>
+      <c r="V83" s="139"/>
+      <c r="W83" s="139"/>
+      <c r="X83" s="139"/>
     </row>
     <row r="84" spans="5:24" ht="20" customHeight="1">
       <c r="E84" s="100"/>
-      <c r="F84" s="217" t="s">
-        <v>146</v>
-      </c>
-      <c r="G84" s="217"/>
-      <c r="H84" s="217"/>
-      <c r="I84" s="217"/>
-      <c r="J84" s="217"/>
-      <c r="K84" s="217"/>
-      <c r="L84" s="217"/>
-      <c r="M84" s="217"/>
-      <c r="N84" s="217"/>
-      <c r="O84" s="217"/>
-      <c r="P84" s="217"/>
-      <c r="Q84" s="217"/>
-      <c r="R84" s="217"/>
-      <c r="S84" s="217"/>
-      <c r="T84" s="217"/>
-      <c r="U84" s="217"/>
-      <c r="V84" s="217"/>
-      <c r="W84" s="217"/>
-      <c r="X84" s="217"/>
+      <c r="F84" s="139" t="s">
+        <v>134</v>
+      </c>
+      <c r="G84" s="139"/>
+      <c r="H84" s="139"/>
+      <c r="I84" s="139"/>
+      <c r="J84" s="139"/>
+      <c r="K84" s="139"/>
+      <c r="L84" s="139"/>
+      <c r="M84" s="139"/>
+      <c r="N84" s="139"/>
+      <c r="O84" s="139"/>
+      <c r="P84" s="139"/>
+      <c r="Q84" s="139"/>
+      <c r="R84" s="139"/>
+      <c r="S84" s="139"/>
+      <c r="T84" s="139"/>
+      <c r="U84" s="139"/>
+      <c r="V84" s="139"/>
+      <c r="W84" s="139"/>
+      <c r="X84" s="139"/>
     </row>
     <row r="85" spans="5:24" ht="40" customHeight="1">
       <c r="E85" s="101"/>
-      <c r="F85" s="217" t="s">
-        <v>103</v>
-      </c>
-      <c r="G85" s="217"/>
-      <c r="H85" s="217"/>
-      <c r="I85" s="217"/>
-      <c r="J85" s="217"/>
-      <c r="K85" s="217"/>
-      <c r="L85" s="217"/>
-      <c r="M85" s="217"/>
-      <c r="N85" s="217"/>
-      <c r="O85" s="217"/>
-      <c r="P85" s="217"/>
-      <c r="Q85" s="217"/>
-      <c r="R85" s="217"/>
-      <c r="S85" s="217"/>
-      <c r="T85" s="217"/>
-      <c r="U85" s="217"/>
-      <c r="V85" s="217"/>
-      <c r="W85" s="217"/>
-      <c r="X85" s="217"/>
+      <c r="F85" s="139" t="s">
+        <v>98</v>
+      </c>
+      <c r="G85" s="139"/>
+      <c r="H85" s="139"/>
+      <c r="I85" s="139"/>
+      <c r="J85" s="139"/>
+      <c r="K85" s="139"/>
+      <c r="L85" s="139"/>
+      <c r="M85" s="139"/>
+      <c r="N85" s="139"/>
+      <c r="O85" s="139"/>
+      <c r="P85" s="139"/>
+      <c r="Q85" s="139"/>
+      <c r="R85" s="139"/>
+      <c r="S85" s="139"/>
+      <c r="T85" s="139"/>
+      <c r="U85" s="139"/>
+      <c r="V85" s="139"/>
+      <c r="W85" s="139"/>
+      <c r="X85" s="139"/>
     </row>
     <row r="86" spans="5:24" ht="20" customHeight="1">
-      <c r="F86" s="221"/>
-      <c r="G86" s="221"/>
-      <c r="H86" s="221"/>
-      <c r="I86" s="221"/>
-      <c r="J86" s="221"/>
-      <c r="K86" s="221"/>
-      <c r="L86" s="221"/>
-      <c r="M86" s="221"/>
-      <c r="N86" s="221"/>
-      <c r="O86" s="221"/>
-      <c r="P86" s="221"/>
-      <c r="Q86" s="221"/>
-      <c r="R86" s="221"/>
-      <c r="S86" s="221"/>
-      <c r="T86" s="221"/>
-      <c r="U86" s="221"/>
-      <c r="V86" s="221"/>
-      <c r="W86" s="221"/>
-      <c r="X86" s="221"/>
+      <c r="F86" s="143"/>
+      <c r="G86" s="143"/>
+      <c r="H86" s="143"/>
+      <c r="I86" s="143"/>
+      <c r="J86" s="143"/>
+      <c r="K86" s="143"/>
+      <c r="L86" s="143"/>
+      <c r="M86" s="143"/>
+      <c r="N86" s="143"/>
+      <c r="O86" s="143"/>
+      <c r="P86" s="143"/>
+      <c r="Q86" s="143"/>
+      <c r="R86" s="143"/>
+      <c r="S86" s="143"/>
+      <c r="T86" s="143"/>
+      <c r="U86" s="143"/>
+      <c r="V86" s="143"/>
+      <c r="W86" s="143"/>
+      <c r="X86" s="143"/>
     </row>
     <row r="87" spans="5:24" ht="20" customHeight="1">
-      <c r="E87" s="216" t="s">
-        <v>174</v>
-      </c>
-      <c r="F87" s="216"/>
-      <c r="G87" s="216"/>
-      <c r="H87" s="216"/>
-      <c r="I87" s="216"/>
-      <c r="J87" s="216"/>
-      <c r="K87" s="216"/>
-      <c r="L87" s="216"/>
-      <c r="M87" s="216"/>
+      <c r="E87" s="138" t="s">
+        <v>159</v>
+      </c>
+      <c r="F87" s="138"/>
+      <c r="G87" s="138"/>
+      <c r="H87" s="138"/>
+      <c r="I87" s="138"/>
+      <c r="J87" s="138"/>
+      <c r="K87" s="138"/>
+      <c r="L87" s="138"/>
+      <c r="M87" s="138"/>
     </row>
     <row r="88" spans="5:24" ht="40" customHeight="1">
-      <c r="F88" s="217" t="s">
-        <v>116</v>
-      </c>
-      <c r="G88" s="217"/>
-      <c r="H88" s="217"/>
-      <c r="I88" s="217"/>
-      <c r="J88" s="217"/>
-      <c r="K88" s="217"/>
-      <c r="L88" s="217"/>
-      <c r="M88" s="217"/>
-      <c r="N88" s="217"/>
-      <c r="O88" s="217"/>
-      <c r="P88" s="217"/>
-      <c r="Q88" s="217"/>
-      <c r="R88" s="217"/>
-      <c r="S88" s="217"/>
-      <c r="T88" s="217"/>
-      <c r="U88" s="217"/>
-      <c r="V88" s="217"/>
-      <c r="W88" s="217"/>
-      <c r="X88" s="217"/>
+      <c r="F88" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="G88" s="139"/>
+      <c r="H88" s="139"/>
+      <c r="I88" s="139"/>
+      <c r="J88" s="139"/>
+      <c r="K88" s="139"/>
+      <c r="L88" s="139"/>
+      <c r="M88" s="139"/>
+      <c r="N88" s="139"/>
+      <c r="O88" s="139"/>
+      <c r="P88" s="139"/>
+      <c r="Q88" s="139"/>
+      <c r="R88" s="139"/>
+      <c r="S88" s="139"/>
+      <c r="T88" s="139"/>
+      <c r="U88" s="139"/>
+      <c r="V88" s="139"/>
+      <c r="W88" s="139"/>
+      <c r="X88" s="139"/>
     </row>
     <row r="89" spans="5:24" ht="40" customHeight="1">
-      <c r="F89" s="217" t="s">
-        <v>117</v>
-      </c>
-      <c r="G89" s="217"/>
-      <c r="H89" s="217"/>
-      <c r="I89" s="217"/>
-      <c r="J89" s="217"/>
-      <c r="K89" s="217"/>
-      <c r="L89" s="217"/>
-      <c r="M89" s="217"/>
-      <c r="N89" s="217"/>
-      <c r="O89" s="217"/>
-      <c r="P89" s="217"/>
-      <c r="Q89" s="217"/>
-      <c r="R89" s="217"/>
-      <c r="S89" s="217"/>
-      <c r="T89" s="217"/>
-      <c r="U89" s="217"/>
-      <c r="V89" s="217"/>
-      <c r="W89" s="217"/>
-      <c r="X89" s="217"/>
+      <c r="F89" s="139" t="s">
+        <v>112</v>
+      </c>
+      <c r="G89" s="139"/>
+      <c r="H89" s="139"/>
+      <c r="I89" s="139"/>
+      <c r="J89" s="139"/>
+      <c r="K89" s="139"/>
+      <c r="L89" s="139"/>
+      <c r="M89" s="139"/>
+      <c r="N89" s="139"/>
+      <c r="O89" s="139"/>
+      <c r="P89" s="139"/>
+      <c r="Q89" s="139"/>
+      <c r="R89" s="139"/>
+      <c r="S89" s="139"/>
+      <c r="T89" s="139"/>
+      <c r="U89" s="139"/>
+      <c r="V89" s="139"/>
+      <c r="W89" s="139"/>
+      <c r="X89" s="139"/>
     </row>
     <row r="90" spans="5:24" ht="34.5" customHeight="1">
-      <c r="F90" s="217" t="s">
-        <v>118</v>
-      </c>
-      <c r="G90" s="217"/>
-      <c r="H90" s="217"/>
-      <c r="I90" s="217"/>
-      <c r="J90" s="217"/>
-      <c r="K90" s="217"/>
-      <c r="L90" s="217"/>
-      <c r="M90" s="217"/>
-      <c r="N90" s="217"/>
-      <c r="O90" s="217"/>
-      <c r="P90" s="217"/>
-      <c r="Q90" s="217"/>
-      <c r="R90" s="217"/>
-      <c r="S90" s="217"/>
-      <c r="T90" s="217"/>
-      <c r="U90" s="217"/>
-      <c r="V90" s="217"/>
-      <c r="W90" s="217"/>
-      <c r="X90" s="217"/>
+      <c r="F90" s="139" t="s">
+        <v>113</v>
+      </c>
+      <c r="G90" s="139"/>
+      <c r="H90" s="139"/>
+      <c r="I90" s="139"/>
+      <c r="J90" s="139"/>
+      <c r="K90" s="139"/>
+      <c r="L90" s="139"/>
+      <c r="M90" s="139"/>
+      <c r="N90" s="139"/>
+      <c r="O90" s="139"/>
+      <c r="P90" s="139"/>
+      <c r="Q90" s="139"/>
+      <c r="R90" s="139"/>
+      <c r="S90" s="139"/>
+      <c r="T90" s="139"/>
+      <c r="U90" s="139"/>
+      <c r="V90" s="139"/>
+      <c r="W90" s="139"/>
+      <c r="X90" s="139"/>
     </row>
     <row r="91" spans="5:24" ht="20" customHeight="1">
       <c r="E91" s="98"/>
@@ -22129,63 +22016,63 @@
       <c r="L91" s="85"/>
     </row>
     <row r="92" spans="5:24" ht="20" customHeight="1">
-      <c r="E92" s="216" t="s">
-        <v>175</v>
-      </c>
-      <c r="F92" s="216"/>
-      <c r="G92" s="216"/>
-      <c r="H92" s="216"/>
-      <c r="I92" s="216"/>
-      <c r="J92" s="216"/>
-      <c r="K92" s="216"/>
-      <c r="L92" s="216"/>
-      <c r="M92" s="216"/>
+      <c r="E92" s="138" t="s">
+        <v>160</v>
+      </c>
+      <c r="F92" s="138"/>
+      <c r="G92" s="138"/>
+      <c r="H92" s="138"/>
+      <c r="I92" s="138"/>
+      <c r="J92" s="138"/>
+      <c r="K92" s="138"/>
+      <c r="L92" s="138"/>
+      <c r="M92" s="138"/>
     </row>
     <row r="93" spans="5:24" ht="40" customHeight="1">
-      <c r="F93" s="217" t="s">
-        <v>151</v>
-      </c>
-      <c r="G93" s="217"/>
-      <c r="H93" s="217"/>
-      <c r="I93" s="217"/>
-      <c r="J93" s="217"/>
-      <c r="K93" s="217"/>
-      <c r="L93" s="217"/>
-      <c r="M93" s="217"/>
-      <c r="N93" s="217"/>
-      <c r="O93" s="217"/>
-      <c r="P93" s="217"/>
-      <c r="Q93" s="217"/>
-      <c r="R93" s="217"/>
-      <c r="S93" s="217"/>
-      <c r="T93" s="217"/>
-      <c r="U93" s="217"/>
-      <c r="V93" s="217"/>
-      <c r="W93" s="217"/>
-      <c r="X93" s="217"/>
+      <c r="F93" s="139" t="s">
+        <v>138</v>
+      </c>
+      <c r="G93" s="139"/>
+      <c r="H93" s="139"/>
+      <c r="I93" s="139"/>
+      <c r="J93" s="139"/>
+      <c r="K93" s="139"/>
+      <c r="L93" s="139"/>
+      <c r="M93" s="139"/>
+      <c r="N93" s="139"/>
+      <c r="O93" s="139"/>
+      <c r="P93" s="139"/>
+      <c r="Q93" s="139"/>
+      <c r="R93" s="139"/>
+      <c r="S93" s="139"/>
+      <c r="T93" s="139"/>
+      <c r="U93" s="139"/>
+      <c r="V93" s="139"/>
+      <c r="W93" s="139"/>
+      <c r="X93" s="139"/>
     </row>
     <row r="94" spans="5:24" ht="40" customHeight="1">
-      <c r="F94" s="217" t="s">
-        <v>145</v>
-      </c>
-      <c r="G94" s="217"/>
-      <c r="H94" s="217"/>
-      <c r="I94" s="217"/>
-      <c r="J94" s="217"/>
-      <c r="K94" s="217"/>
-      <c r="L94" s="217"/>
-      <c r="M94" s="217"/>
-      <c r="N94" s="217"/>
-      <c r="O94" s="217"/>
-      <c r="P94" s="217"/>
-      <c r="Q94" s="217"/>
-      <c r="R94" s="217"/>
-      <c r="S94" s="217"/>
-      <c r="T94" s="217"/>
-      <c r="U94" s="217"/>
-      <c r="V94" s="217"/>
-      <c r="W94" s="217"/>
-      <c r="X94" s="217"/>
+      <c r="F94" s="139" t="s">
+        <v>133</v>
+      </c>
+      <c r="G94" s="139"/>
+      <c r="H94" s="139"/>
+      <c r="I94" s="139"/>
+      <c r="J94" s="139"/>
+      <c r="K94" s="139"/>
+      <c r="L94" s="139"/>
+      <c r="M94" s="139"/>
+      <c r="N94" s="139"/>
+      <c r="O94" s="139"/>
+      <c r="P94" s="139"/>
+      <c r="Q94" s="139"/>
+      <c r="R94" s="139"/>
+      <c r="S94" s="139"/>
+      <c r="T94" s="139"/>
+      <c r="U94" s="139"/>
+      <c r="V94" s="139"/>
+      <c r="W94" s="139"/>
+      <c r="X94" s="139"/>
     </row>
     <row r="95" spans="5:24" ht="20" customHeight="1">
       <c r="E95" s="98"/>
@@ -22194,40 +22081,40 @@
       <c r="L95" s="85"/>
     </row>
     <row r="96" spans="5:24" ht="20" customHeight="1">
-      <c r="E96" s="216" t="s">
-        <v>176</v>
-      </c>
-      <c r="F96" s="216"/>
-      <c r="G96" s="216"/>
-      <c r="H96" s="216"/>
-      <c r="I96" s="216"/>
-      <c r="J96" s="216"/>
-      <c r="K96" s="216"/>
-      <c r="L96" s="216"/>
-      <c r="M96" s="216"/>
+      <c r="E96" s="138" t="s">
+        <v>161</v>
+      </c>
+      <c r="F96" s="138"/>
+      <c r="G96" s="138"/>
+      <c r="H96" s="138"/>
+      <c r="I96" s="138"/>
+      <c r="J96" s="138"/>
+      <c r="K96" s="138"/>
+      <c r="L96" s="138"/>
+      <c r="M96" s="138"/>
     </row>
     <row r="97" spans="5:24" ht="40" customHeight="1">
-      <c r="F97" s="217" t="s">
-        <v>119</v>
-      </c>
-      <c r="G97" s="217"/>
-      <c r="H97" s="217"/>
-      <c r="I97" s="217"/>
-      <c r="J97" s="217"/>
-      <c r="K97" s="217"/>
-      <c r="L97" s="217"/>
-      <c r="M97" s="217"/>
-      <c r="N97" s="217"/>
-      <c r="O97" s="217"/>
-      <c r="P97" s="217"/>
-      <c r="Q97" s="217"/>
-      <c r="R97" s="217"/>
-      <c r="S97" s="217"/>
-      <c r="T97" s="217"/>
-      <c r="U97" s="217"/>
-      <c r="V97" s="217"/>
-      <c r="W97" s="217"/>
-      <c r="X97" s="217"/>
+      <c r="F97" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="G97" s="139"/>
+      <c r="H97" s="139"/>
+      <c r="I97" s="139"/>
+      <c r="J97" s="139"/>
+      <c r="K97" s="139"/>
+      <c r="L97" s="139"/>
+      <c r="M97" s="139"/>
+      <c r="N97" s="139"/>
+      <c r="O97" s="139"/>
+      <c r="P97" s="139"/>
+      <c r="Q97" s="139"/>
+      <c r="R97" s="139"/>
+      <c r="S97" s="139"/>
+      <c r="T97" s="139"/>
+      <c r="U97" s="139"/>
+      <c r="V97" s="139"/>
+      <c r="W97" s="139"/>
+      <c r="X97" s="139"/>
     </row>
     <row r="98" spans="5:24" ht="20" customHeight="1">
       <c r="E98" s="98"/>
@@ -22236,8 +22123,8 @@
       <c r="L98" s="85"/>
     </row>
     <row r="99" spans="5:24" ht="20" customHeight="1">
-      <c r="E99" s="135" t="s">
-        <v>177</v>
+      <c r="E99" s="131" t="s">
+        <v>162</v>
       </c>
       <c r="F99" s="102"/>
       <c r="G99" s="102"/>
@@ -22249,123 +22136,123 @@
       <c r="M99" s="102"/>
     </row>
     <row r="100" spans="5:24" ht="20" customHeight="1">
-      <c r="F100" s="215" t="s">
-        <v>104</v>
-      </c>
-      <c r="G100" s="215"/>
-      <c r="H100" s="215"/>
-      <c r="I100" s="215"/>
-      <c r="J100" s="215"/>
-      <c r="K100" s="215"/>
-      <c r="L100" s="215"/>
-      <c r="M100" s="215"/>
-      <c r="N100" s="215"/>
-      <c r="O100" s="215"/>
-      <c r="P100" s="215"/>
-      <c r="Q100" s="215"/>
-      <c r="R100" s="215"/>
-      <c r="S100" s="215"/>
-      <c r="T100" s="215"/>
-      <c r="U100" s="215"/>
-      <c r="V100" s="215"/>
-      <c r="W100" s="215"/>
-      <c r="X100" s="215"/>
+      <c r="F100" s="134" t="s">
+        <v>99</v>
+      </c>
+      <c r="G100" s="134"/>
+      <c r="H100" s="134"/>
+      <c r="I100" s="134"/>
+      <c r="J100" s="134"/>
+      <c r="K100" s="134"/>
+      <c r="L100" s="134"/>
+      <c r="M100" s="134"/>
+      <c r="N100" s="134"/>
+      <c r="O100" s="134"/>
+      <c r="P100" s="134"/>
+      <c r="Q100" s="134"/>
+      <c r="R100" s="134"/>
+      <c r="S100" s="134"/>
+      <c r="T100" s="134"/>
+      <c r="U100" s="134"/>
+      <c r="V100" s="134"/>
+      <c r="W100" s="134"/>
+      <c r="X100" s="134"/>
     </row>
     <row r="101" spans="5:24" ht="20" customHeight="1">
       <c r="E101" s="103"/>
-      <c r="F101" s="221" t="s">
-        <v>161</v>
-      </c>
-      <c r="G101" s="221"/>
-      <c r="H101" s="221"/>
-      <c r="I101" s="221"/>
-      <c r="J101" s="221"/>
-      <c r="K101" s="221"/>
-      <c r="L101" s="221"/>
-      <c r="M101" s="221"/>
-      <c r="N101" s="221"/>
-      <c r="O101" s="221"/>
-      <c r="P101" s="221"/>
-      <c r="Q101" s="221"/>
-      <c r="R101" s="221"/>
-      <c r="S101" s="221"/>
-      <c r="T101" s="221"/>
-      <c r="U101" s="221"/>
-      <c r="V101" s="221"/>
-      <c r="W101" s="221"/>
-      <c r="X101" s="221"/>
+      <c r="F101" s="143" t="s">
+        <v>146</v>
+      </c>
+      <c r="G101" s="143"/>
+      <c r="H101" s="143"/>
+      <c r="I101" s="143"/>
+      <c r="J101" s="143"/>
+      <c r="K101" s="143"/>
+      <c r="L101" s="143"/>
+      <c r="M101" s="143"/>
+      <c r="N101" s="143"/>
+      <c r="O101" s="143"/>
+      <c r="P101" s="143"/>
+      <c r="Q101" s="143"/>
+      <c r="R101" s="143"/>
+      <c r="S101" s="143"/>
+      <c r="T101" s="143"/>
+      <c r="U101" s="143"/>
+      <c r="V101" s="143"/>
+      <c r="W101" s="143"/>
+      <c r="X101" s="143"/>
     </row>
     <row r="102" spans="5:24" ht="20" customHeight="1">
       <c r="E102" s="103"/>
-      <c r="F102" s="221" t="s">
-        <v>162</v>
-      </c>
-      <c r="G102" s="221"/>
-      <c r="H102" s="221"/>
-      <c r="I102" s="221"/>
-      <c r="J102" s="221"/>
-      <c r="K102" s="221"/>
-      <c r="L102" s="221"/>
-      <c r="M102" s="221"/>
-      <c r="N102" s="221"/>
-      <c r="O102" s="221"/>
-      <c r="P102" s="221"/>
-      <c r="Q102" s="221"/>
-      <c r="R102" s="221"/>
-      <c r="S102" s="221"/>
-      <c r="T102" s="221"/>
-      <c r="U102" s="221"/>
-      <c r="V102" s="221"/>
-      <c r="W102" s="221"/>
-      <c r="X102" s="221"/>
+      <c r="F102" s="143" t="s">
+        <v>147</v>
+      </c>
+      <c r="G102" s="143"/>
+      <c r="H102" s="143"/>
+      <c r="I102" s="143"/>
+      <c r="J102" s="143"/>
+      <c r="K102" s="143"/>
+      <c r="L102" s="143"/>
+      <c r="M102" s="143"/>
+      <c r="N102" s="143"/>
+      <c r="O102" s="143"/>
+      <c r="P102" s="143"/>
+      <c r="Q102" s="143"/>
+      <c r="R102" s="143"/>
+      <c r="S102" s="143"/>
+      <c r="T102" s="143"/>
+      <c r="U102" s="143"/>
+      <c r="V102" s="143"/>
+      <c r="W102" s="143"/>
+      <c r="X102" s="143"/>
     </row>
     <row r="103" spans="5:24" ht="20" customHeight="1">
       <c r="E103" s="103"/>
-      <c r="F103" s="221" t="s">
-        <v>163</v>
-      </c>
-      <c r="G103" s="221"/>
-      <c r="H103" s="221"/>
-      <c r="I103" s="221"/>
-      <c r="J103" s="221"/>
-      <c r="K103" s="221"/>
-      <c r="L103" s="221"/>
-      <c r="M103" s="221"/>
-      <c r="N103" s="221"/>
-      <c r="O103" s="221"/>
-      <c r="P103" s="221"/>
-      <c r="Q103" s="221"/>
-      <c r="R103" s="221"/>
-      <c r="S103" s="221"/>
-      <c r="T103" s="221"/>
-      <c r="U103" s="221"/>
-      <c r="V103" s="221"/>
-      <c r="W103" s="221"/>
-      <c r="X103" s="221"/>
+      <c r="F103" s="143" t="s">
+        <v>148</v>
+      </c>
+      <c r="G103" s="143"/>
+      <c r="H103" s="143"/>
+      <c r="I103" s="143"/>
+      <c r="J103" s="143"/>
+      <c r="K103" s="143"/>
+      <c r="L103" s="143"/>
+      <c r="M103" s="143"/>
+      <c r="N103" s="143"/>
+      <c r="O103" s="143"/>
+      <c r="P103" s="143"/>
+      <c r="Q103" s="143"/>
+      <c r="R103" s="143"/>
+      <c r="S103" s="143"/>
+      <c r="T103" s="143"/>
+      <c r="U103" s="143"/>
+      <c r="V103" s="143"/>
+      <c r="W103" s="143"/>
+      <c r="X103" s="143"/>
     </row>
     <row r="104" spans="5:24" ht="20" customHeight="1">
       <c r="E104" s="103"/>
-      <c r="F104" s="221" t="s">
-        <v>164</v>
-      </c>
-      <c r="G104" s="221"/>
-      <c r="H104" s="221"/>
-      <c r="I104" s="221"/>
-      <c r="J104" s="221"/>
-      <c r="K104" s="221"/>
-      <c r="L104" s="221"/>
-      <c r="M104" s="221"/>
-      <c r="N104" s="221"/>
-      <c r="O104" s="221"/>
-      <c r="P104" s="221"/>
-      <c r="Q104" s="221"/>
-      <c r="R104" s="221"/>
-      <c r="S104" s="221"/>
-      <c r="T104" s="221"/>
-      <c r="U104" s="221"/>
-      <c r="V104" s="221"/>
-      <c r="W104" s="221"/>
-      <c r="X104" s="221"/>
+      <c r="F104" s="143" t="s">
+        <v>149</v>
+      </c>
+      <c r="G104" s="143"/>
+      <c r="H104" s="143"/>
+      <c r="I104" s="143"/>
+      <c r="J104" s="143"/>
+      <c r="K104" s="143"/>
+      <c r="L104" s="143"/>
+      <c r="M104" s="143"/>
+      <c r="N104" s="143"/>
+      <c r="O104" s="143"/>
+      <c r="P104" s="143"/>
+      <c r="Q104" s="143"/>
+      <c r="R104" s="143"/>
+      <c r="S104" s="143"/>
+      <c r="T104" s="143"/>
+      <c r="U104" s="143"/>
+      <c r="V104" s="143"/>
+      <c r="W104" s="143"/>
+      <c r="X104" s="143"/>
     </row>
     <row r="105" spans="5:24" ht="20" customHeight="1">
       <c r="E105" s="98"/>
@@ -22374,8 +22261,8 @@
       <c r="L105" s="85"/>
     </row>
     <row r="106" spans="5:24" ht="20" customHeight="1">
-      <c r="E106" s="135" t="s">
-        <v>178</v>
+      <c r="E106" s="131" t="s">
+        <v>163</v>
       </c>
       <c r="F106" s="102"/>
       <c r="G106" s="102"/>
@@ -22387,27 +22274,27 @@
       <c r="M106" s="102"/>
     </row>
     <row r="107" spans="5:24" ht="40" customHeight="1">
-      <c r="F107" s="217" t="s">
-        <v>120</v>
-      </c>
-      <c r="G107" s="217"/>
-      <c r="H107" s="217"/>
-      <c r="I107" s="217"/>
-      <c r="J107" s="217"/>
-      <c r="K107" s="217"/>
-      <c r="L107" s="217"/>
-      <c r="M107" s="217"/>
-      <c r="N107" s="217"/>
-      <c r="O107" s="217"/>
-      <c r="P107" s="217"/>
-      <c r="Q107" s="217"/>
-      <c r="R107" s="217"/>
-      <c r="S107" s="217"/>
-      <c r="T107" s="217"/>
-      <c r="U107" s="217"/>
-      <c r="V107" s="217"/>
-      <c r="W107" s="217"/>
-      <c r="X107" s="217"/>
+      <c r="F107" s="139" t="s">
+        <v>194</v>
+      </c>
+      <c r="G107" s="139"/>
+      <c r="H107" s="139"/>
+      <c r="I107" s="139"/>
+      <c r="J107" s="139"/>
+      <c r="K107" s="139"/>
+      <c r="L107" s="139"/>
+      <c r="M107" s="139"/>
+      <c r="N107" s="139"/>
+      <c r="O107" s="139"/>
+      <c r="P107" s="139"/>
+      <c r="Q107" s="139"/>
+      <c r="R107" s="139"/>
+      <c r="S107" s="139"/>
+      <c r="T107" s="139"/>
+      <c r="U107" s="139"/>
+      <c r="V107" s="139"/>
+      <c r="W107" s="139"/>
+      <c r="X107" s="139"/>
     </row>
     <row r="108" spans="5:24" ht="20" customHeight="1">
       <c r="E108" s="98"/>
@@ -22416,77 +22303,77 @@
       <c r="L108" s="85"/>
     </row>
     <row r="109" spans="5:24" ht="20" customHeight="1">
-      <c r="E109" s="216" t="s">
-        <v>179</v>
-      </c>
-      <c r="F109" s="216"/>
-      <c r="G109" s="216"/>
-      <c r="H109" s="216"/>
-      <c r="I109" s="216"/>
-      <c r="J109" s="216"/>
-      <c r="K109" s="216"/>
-      <c r="L109" s="216"/>
-      <c r="M109" s="216"/>
+      <c r="E109" s="138" t="s">
+        <v>164</v>
+      </c>
+      <c r="F109" s="138"/>
+      <c r="G109" s="138"/>
+      <c r="H109" s="138"/>
+      <c r="I109" s="138"/>
+      <c r="J109" s="138"/>
+      <c r="K109" s="138"/>
+      <c r="L109" s="138"/>
+      <c r="M109" s="138"/>
     </row>
     <row r="110" spans="5:24" ht="40" customHeight="1">
-      <c r="F110" s="217" t="s">
+      <c r="F110" s="139" t="s">
+        <v>110</v>
+      </c>
+      <c r="G110" s="139"/>
+      <c r="H110" s="139"/>
+      <c r="I110" s="139"/>
+      <c r="J110" s="139"/>
+      <c r="K110" s="139"/>
+      <c r="L110" s="139"/>
+      <c r="M110" s="139"/>
+      <c r="N110" s="139"/>
+      <c r="O110" s="139"/>
+      <c r="P110" s="139"/>
+      <c r="Q110" s="139"/>
+      <c r="R110" s="139"/>
+      <c r="S110" s="139"/>
+      <c r="T110" s="139"/>
+      <c r="U110" s="139"/>
+      <c r="V110" s="139"/>
+      <c r="W110" s="139"/>
+      <c r="X110" s="139"/>
+    </row>
+    <row r="111" spans="5:24" ht="40" customHeight="1">
+      <c r="F111" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="G110" s="217"/>
-      <c r="H110" s="217"/>
-      <c r="I110" s="217"/>
-      <c r="J110" s="217"/>
-      <c r="K110" s="217"/>
-      <c r="L110" s="217"/>
-      <c r="M110" s="217"/>
-      <c r="N110" s="217"/>
-      <c r="O110" s="217"/>
-      <c r="P110" s="217"/>
-      <c r="Q110" s="217"/>
-      <c r="R110" s="217"/>
-      <c r="S110" s="217"/>
-      <c r="T110" s="217"/>
-      <c r="U110" s="217"/>
-      <c r="V110" s="217"/>
-      <c r="W110" s="217"/>
-      <c r="X110" s="217"/>
-    </row>
-    <row r="111" spans="5:24" ht="40" customHeight="1">
-      <c r="F111" s="217" t="s">
-        <v>121</v>
-      </c>
-      <c r="G111" s="217"/>
-      <c r="H111" s="217"/>
-      <c r="I111" s="217"/>
-      <c r="J111" s="217"/>
-      <c r="K111" s="217"/>
-      <c r="L111" s="217"/>
-      <c r="M111" s="217"/>
-      <c r="N111" s="217"/>
-      <c r="O111" s="217"/>
-      <c r="P111" s="217"/>
-      <c r="Q111" s="217"/>
-      <c r="R111" s="217"/>
-      <c r="S111" s="217"/>
-      <c r="T111" s="217"/>
-      <c r="U111" s="217"/>
-      <c r="V111" s="217"/>
-      <c r="W111" s="217"/>
-      <c r="X111" s="217"/>
+      <c r="G111" s="139"/>
+      <c r="H111" s="139"/>
+      <c r="I111" s="139"/>
+      <c r="J111" s="139"/>
+      <c r="K111" s="139"/>
+      <c r="L111" s="139"/>
+      <c r="M111" s="139"/>
+      <c r="N111" s="139"/>
+      <c r="O111" s="139"/>
+      <c r="P111" s="139"/>
+      <c r="Q111" s="139"/>
+      <c r="R111" s="139"/>
+      <c r="S111" s="139"/>
+      <c r="T111" s="139"/>
+      <c r="U111" s="139"/>
+      <c r="V111" s="139"/>
+      <c r="W111" s="139"/>
+      <c r="X111" s="139"/>
     </row>
     <row r="112" spans="5:24" ht="20" customHeight="1"/>
     <row r="113" spans="5:24" ht="20" customHeight="1">
-      <c r="E113" s="218" t="s">
-        <v>152</v>
-      </c>
-      <c r="F113" s="219"/>
-      <c r="G113" s="219"/>
-      <c r="H113" s="219"/>
-      <c r="I113" s="219"/>
-      <c r="J113" s="219"/>
-      <c r="K113" s="219"/>
-      <c r="L113" s="219"/>
-      <c r="M113" s="219"/>
+      <c r="E113" s="140" t="s">
+        <v>139</v>
+      </c>
+      <c r="F113" s="141"/>
+      <c r="G113" s="141"/>
+      <c r="H113" s="141"/>
+      <c r="I113" s="141"/>
+      <c r="J113" s="141"/>
+      <c r="K113" s="141"/>
+      <c r="L113" s="141"/>
+      <c r="M113" s="141"/>
       <c r="N113" s="114"/>
       <c r="O113" s="114"/>
       <c r="P113" s="114"/>
@@ -22501,33 +22388,33 @@
     </row>
     <row r="114" spans="5:24" ht="43.75" customHeight="1">
       <c r="E114" s="115"/>
-      <c r="F114" s="220" t="s">
-        <v>150</v>
-      </c>
-      <c r="G114" s="220"/>
-      <c r="H114" s="220"/>
-      <c r="I114" s="220"/>
-      <c r="J114" s="220"/>
-      <c r="K114" s="220"/>
-      <c r="L114" s="220"/>
-      <c r="M114" s="220"/>
-      <c r="N114" s="220"/>
-      <c r="O114" s="220"/>
-      <c r="P114" s="220"/>
-      <c r="Q114" s="220"/>
-      <c r="R114" s="220"/>
-      <c r="S114" s="220"/>
-      <c r="T114" s="220"/>
-      <c r="U114" s="220"/>
-      <c r="V114" s="220"/>
-      <c r="W114" s="220"/>
-      <c r="X114" s="220"/>
+      <c r="F114" s="142" t="s">
+        <v>137</v>
+      </c>
+      <c r="G114" s="142"/>
+      <c r="H114" s="142"/>
+      <c r="I114" s="142"/>
+      <c r="J114" s="142"/>
+      <c r="K114" s="142"/>
+      <c r="L114" s="142"/>
+      <c r="M114" s="142"/>
+      <c r="N114" s="142"/>
+      <c r="O114" s="142"/>
+      <c r="P114" s="142"/>
+      <c r="Q114" s="142"/>
+      <c r="R114" s="142"/>
+      <c r="S114" s="142"/>
+      <c r="T114" s="142"/>
+      <c r="U114" s="142"/>
+      <c r="V114" s="142"/>
+      <c r="W114" s="142"/>
+      <c r="X114" s="142"/>
     </row>
     <row r="115" spans="5:24" ht="25" customHeight="1"/>
     <row r="116" spans="5:24" ht="13.5" customHeight="1"/>
     <row r="117" spans="5:24" ht="13.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="109">
     <mergeCell ref="E7:X7"/>
     <mergeCell ref="E8:X8"/>
     <mergeCell ref="E9:X9"/>
@@ -22548,20 +22435,16 @@
     <mergeCell ref="E46:X46"/>
     <mergeCell ref="J32:X32"/>
     <mergeCell ref="J33:X33"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="Q42:X42"/>
     <mergeCell ref="J43:L43"/>
     <mergeCell ref="M43:X43"/>
     <mergeCell ref="J44:L44"/>
     <mergeCell ref="M44:X44"/>
     <mergeCell ref="J35:X35"/>
+    <mergeCell ref="J42:X42"/>
     <mergeCell ref="E48:G48"/>
     <mergeCell ref="H48:X48"/>
     <mergeCell ref="E34:F44"/>
     <mergeCell ref="G34:I34"/>
-    <mergeCell ref="J34:Q34"/>
-    <mergeCell ref="R34:X34"/>
     <mergeCell ref="G35:I35"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="J36:X36"/>
@@ -22589,6 +22472,13 @@
     <mergeCell ref="H54:N54"/>
     <mergeCell ref="O54:Q54"/>
     <mergeCell ref="R54:X54"/>
+    <mergeCell ref="E58:X58"/>
+    <mergeCell ref="E63:M63"/>
+    <mergeCell ref="F64:X64"/>
+    <mergeCell ref="E66:X66"/>
+    <mergeCell ref="F60:X60"/>
+    <mergeCell ref="F61:X61"/>
+    <mergeCell ref="F67:X67"/>
     <mergeCell ref="E55:G55"/>
     <mergeCell ref="H55:N55"/>
     <mergeCell ref="O55:Q55"/>
@@ -22598,15 +22488,9 @@
     <mergeCell ref="O56:Q56"/>
     <mergeCell ref="R56:X56"/>
     <mergeCell ref="E57:X57"/>
-    <mergeCell ref="E58:X58"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="E61:X61"/>
-    <mergeCell ref="E63:M63"/>
-    <mergeCell ref="F64:X64"/>
-    <mergeCell ref="E66:X66"/>
-    <mergeCell ref="I67:X67"/>
-    <mergeCell ref="H60:O60"/>
-    <mergeCell ref="P60:X60"/>
+    <mergeCell ref="F90:X90"/>
+    <mergeCell ref="E92:M92"/>
+    <mergeCell ref="F93:X93"/>
     <mergeCell ref="E72:M72"/>
     <mergeCell ref="F73:X73"/>
     <mergeCell ref="F74:X74"/>
@@ -22616,7 +22500,10 @@
     <mergeCell ref="F80:X80"/>
     <mergeCell ref="E82:M82"/>
     <mergeCell ref="F83:X83"/>
-    <mergeCell ref="F70:K70"/>
+    <mergeCell ref="F68:X68"/>
+    <mergeCell ref="F69:X69"/>
+    <mergeCell ref="F70:X70"/>
+    <mergeCell ref="J34:X34"/>
     <mergeCell ref="E109:M109"/>
     <mergeCell ref="F110:X110"/>
     <mergeCell ref="F111:X111"/>
@@ -22637,9 +22524,6 @@
     <mergeCell ref="E87:M87"/>
     <mergeCell ref="F88:X88"/>
     <mergeCell ref="F89:X89"/>
-    <mergeCell ref="F90:X90"/>
-    <mergeCell ref="E92:M92"/>
-    <mergeCell ref="F93:X93"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/repair/back/doc/estimate/program-periodic2.xlsx
+++ b/repair/back/doc/estimate/program-periodic2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild=""/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="1" r:id="rId1"/>
@@ -1349,7 +1349,7 @@
     <numFmt numFmtId="243" formatCode="_-&quot;₩&quot;* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0.00_-;_-&quot;₩&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="244" formatCode="&quot;₩&quot;#,##0.00;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-#,##0.00"/>
   </numFmts>
-  <fonts count="136">
+  <fonts count="143">
     <font>
       <sz val="10.0"/>
       <name val="바탕"/>
@@ -2083,6 +2083,46 @@
       <name val="맑은 고딕"/>
       <color theme="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="20.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
   </fonts>
   <fills count="42">
     <fill>
@@ -3203,7 +3243,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3212,7 +3251,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3221,7 +3259,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3230,7 +3267,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -3245,7 +3281,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -3260,7 +3295,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -3275,7 +3309,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3284,7 +3317,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -3295,7 +3327,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3162">
@@ -17706,9 +17737,6 @@
       <c r="AF9" s="116"/>
       <c r="AG9" s="116"/>
       <c r="AH9" s="1"/>
-      <c r="AI9" s="2"/>
-      <c r="AJ9" s="2"/>
-      <c r="AK9" s="2"/>
     </row>
     <row r="10" spans="6:34" s="2" customFormat="1" ht="22.000000" customHeight="1">
       <c r="F10" s="235" t="s">
@@ -19653,8 +19681,7 @@
     <col min="8" max="8" style="82" width="13.43357168" customWidth="1" outlineLevel="0"/>
     <col min="9" max="9" style="84" width="13.43357168" customWidth="1" outlineLevel="0"/>
     <col min="10" max="256" style="82" width="11.29071413" customWidth="1" outlineLevel="0"/>
-    <col min="257" max="257" style="82" width="14.86214243" customWidth="1" outlineLevel="0"/>
-    <col min="258" max="16384" style="82" width="14.86214243" customWidth="1" outlineLevel="0"/>
+    <col min="257" max="16384" style="82" width="14.86214243" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" s="16" customFormat="1" ht="39.000000" customHeight="1">
@@ -19716,9 +19743,9 @@
         <v>19</v>
       </c>
       <c r="C5" s="269"/>
-      <c r="D5" s="270" t="e">
+      <c r="D5" s="270">
         <f>"일금 "&amp;NUMBERSTRING(H26,1)&amp;"원정"&amp;TEXT(H26,"(￦ #,##0)")&amp;" "</f>
-        <v>일금 #VALUE!원정</v>
+        <v/>
       </c>
       <c r="E5" s="270"/>
       <c r="F5" s="270"/>
@@ -21335,7 +21362,7 @@
       <c r="W44" s="167"/>
       <c r="X44" s="168"/>
     </row>
-    <row r="45" spans="5:24">
+    <row r="45" spans="5:24" ht="13.500000">
       <c r="E45" s="155"/>
       <c r="F45" s="156"/>
       <c r="G45" s="156"/>
@@ -21366,7 +21393,7 @@
       <c r="W46" s="96"/>
       <c r="X46" s="158"/>
     </row>
-    <row r="47" spans="5:24">
+    <row r="47" spans="5:24" ht="13.500000">
       <c r="E47" s="92"/>
       <c r="F47" s="93"/>
       <c r="G47" s="93"/>
@@ -21443,7 +21470,7 @@
       <c r="W50" s="96"/>
       <c r="X50" s="158"/>
     </row>
-    <row r="51" spans="5:24">
+    <row r="51" spans="5:24" ht="13.500000">
       <c r="E51" s="155"/>
       <c r="F51" s="156"/>
       <c r="G51" s="156"/>
@@ -21803,7 +21830,7 @@
     </row>
     <row r="68" spans="5:24" ht="20.000000" customHeight="1">
       <c r="F68" s="101" t="str">
-        <f>"② 위      치 : "&amp;H55</f>
+        <f>"② 위      치 : "&amp;갑지!P21</f>
         <v>② 위      치 : 서울 성북구 길음로9길 50 (길음동)</v>
       </c>
       <c r="G68" s="101"/>
